--- a/data/MetalliCan/sites_for_lci.xlsx
+++ b/data/MetalliCan/sites_for_lci.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/regionalized_lci_mineral/data/MetalliCan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2922" documentId="13_ncr:1_{965BE886-D2C4-44D2-937F-E901E74C4ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA3BD32E-0904-45A1-85E6-D9DFE59C1DE1}"/>
+  <xr:revisionPtr revIDLastSave="2961" documentId="13_ncr:1_{965BE886-D2C4-44D2-937F-E901E74C4ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E197436-D085-44A6-842A-AEDCFBD749A5}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{9D292A65-B8C8-46CC-8162-88CB3EA3ABC7}"/>
   </bookViews>
@@ -131,7 +131,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8597" uniqueCount="1672">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8603" uniqueCount="1672">
   <si>
     <t>main_id</t>
   </si>
@@ -5465,60 +5465,15 @@
     <t>Cu-Zn Porphyry sulfide, flotation-based</t>
   </si>
   <si>
-    <t>Cu concentrates with Au and Ag credits</t>
-  </si>
-  <si>
-    <t>Ni-Cu bulk concentrates</t>
-  </si>
-  <si>
     <t>Au (Cu, Ag)</t>
   </si>
   <si>
-    <t>Au-Ag dore, Cu concentrates</t>
-  </si>
-  <si>
-    <t>Au-Ag dore</t>
-  </si>
-  <si>
-    <t>Cu and Mo concentrates</t>
-  </si>
-  <si>
-    <t>Cu and Zn concentrates with Ag credits</t>
-  </si>
-  <si>
-    <t>Au-Ag dore, Cu and Zn concentrates</t>
-  </si>
-  <si>
     <t>Ag (Zn, Pb)</t>
   </si>
   <si>
-    <t>Pb and Zn concentrates with Ag credits</t>
-  </si>
-  <si>
-    <t>PGM bulk concentrate</t>
-  </si>
-  <si>
-    <t>Cu-PGM concentrate and Ni-Cu concentrate</t>
-  </si>
-  <si>
-    <t>Cu concentrates with Au credits</t>
-  </si>
-  <si>
-    <t>Fe concentrate</t>
-  </si>
-  <si>
-    <t>Nb concentrate</t>
-  </si>
-  <si>
-    <t>Fe concentrate, Fe pellets</t>
-  </si>
-  <si>
     <t>Stream</t>
   </si>
   <si>
-    <t>Au-Ag dore, Cu and Zn concentrate with Au-Ag credits</t>
-  </si>
-  <si>
     <t>For dore we assume 88% of Au, 10% of Si and 2% impurities</t>
   </si>
   <si>
@@ -5823,6 +5778,51 @@
   </si>
   <si>
     <t>Yellowcake</t>
+  </si>
+  <si>
+    <t>Ag polymetallic</t>
+  </si>
+  <si>
+    <t>Not sure</t>
+  </si>
+  <si>
+    <t>Au-Ag doré</t>
+  </si>
+  <si>
+    <t>Ni-Cu bulk conc.</t>
+  </si>
+  <si>
+    <t>Cu and Mo conc.</t>
+  </si>
+  <si>
+    <t>Au-Ag doré, Cu conc.</t>
+  </si>
+  <si>
+    <t>Au-Ag doré, Cu and Zn conc.</t>
+  </si>
+  <si>
+    <t>Fe conc.</t>
+  </si>
+  <si>
+    <t>Fe conc., Fe pellets</t>
+  </si>
+  <si>
+    <t>PGM bulk conc.</t>
+  </si>
+  <si>
+    <t>Cu-PGM conc. and Ni-Cu conc.</t>
+  </si>
+  <si>
+    <t>Nb conc.</t>
+  </si>
+  <si>
+    <t>Pb and Zn conc.</t>
+  </si>
+  <si>
+    <t>Cu and Zn conc.</t>
+  </si>
+  <si>
+    <t>Cu conc.</t>
   </si>
 </sst>
 </file>
@@ -9555,7 +9555,7 @@
         <v>65</v>
       </c>
       <c r="M21" t="s">
-        <v>1554</v>
+        <v>1552</v>
       </c>
       <c r="N21" s="51">
         <f>prod_table_raw!N86</f>
@@ -9668,7 +9668,7 @@
         <v>1.1845712827941936E-3</v>
       </c>
       <c r="BF21" t="s">
-        <v>1554</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="22" spans="1:58" x14ac:dyDescent="0.25">
@@ -22535,7 +22535,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1570</v>
+        <v>1555</v>
       </c>
     </row>
   </sheetData>
@@ -26852,13 +26852,13 @@
         <v>16</v>
       </c>
       <c r="H1" s="19" t="s">
-        <v>1627</v>
+        <v>1612</v>
       </c>
       <c r="I1" s="19" t="s">
         <v>1247</v>
       </c>
       <c r="J1" s="19" t="s">
-        <v>1636</v>
+        <v>1621</v>
       </c>
       <c r="K1" s="19" t="s">
         <v>1501</v>
@@ -26870,49 +26870,49 @@
         <v>1070</v>
       </c>
       <c r="N1" s="19" t="s">
-        <v>1585</v>
+        <v>1570</v>
       </c>
       <c r="O1" s="19" t="s">
-        <v>1621</v>
+        <v>1606</v>
       </c>
       <c r="P1" s="19" t="s">
-        <v>1622</v>
+        <v>1607</v>
       </c>
       <c r="Q1" s="19" t="s">
-        <v>1623</v>
+        <v>1608</v>
       </c>
       <c r="R1" s="19" t="s">
-        <v>1626</v>
+        <v>1611</v>
       </c>
       <c r="S1" s="19" t="s">
-        <v>1634</v>
+        <v>1619</v>
       </c>
       <c r="T1" s="20" t="s">
         <v>17</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>1572</v>
+        <v>1557</v>
       </c>
       <c r="V1" s="1" t="s">
         <v>1159</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>1568</v>
+        <v>1554</v>
       </c>
       <c r="X1" s="18" t="s">
         <v>907</v>
       </c>
       <c r="Y1" s="19" t="s">
-        <v>1573</v>
+        <v>1558</v>
       </c>
       <c r="Z1" s="19" t="s">
-        <v>1614</v>
+        <v>1599</v>
       </c>
       <c r="AA1" s="19" t="s">
-        <v>1574</v>
+        <v>1559</v>
       </c>
       <c r="AB1" s="19" t="s">
-        <v>1571</v>
+        <v>1556</v>
       </c>
       <c r="AC1" s="19" t="s">
         <v>1009</v>
@@ -26954,37 +26954,37 @@
         <v>1466</v>
       </c>
       <c r="AP1" s="19" t="s">
-        <v>1575</v>
+        <v>1560</v>
       </c>
       <c r="AQ1" s="19" t="s">
-        <v>1576</v>
+        <v>1561</v>
       </c>
       <c r="AR1" s="19" t="s">
-        <v>1577</v>
+        <v>1562</v>
       </c>
       <c r="AS1" s="19" t="s">
-        <v>1578</v>
+        <v>1563</v>
       </c>
       <c r="AT1" s="19" t="s">
-        <v>1579</v>
+        <v>1564</v>
       </c>
       <c r="AU1" s="19" t="s">
-        <v>1580</v>
+        <v>1565</v>
       </c>
       <c r="AV1" s="19" t="s">
-        <v>1581</v>
+        <v>1566</v>
       </c>
       <c r="AW1" s="19" t="s">
-        <v>1582</v>
+        <v>1567</v>
       </c>
       <c r="AX1" s="19" t="s">
-        <v>1583</v>
+        <v>1568</v>
       </c>
       <c r="AY1" s="19" t="s">
-        <v>1584</v>
+        <v>1569</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>1613</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="2" spans="1:52" x14ac:dyDescent="0.25">
@@ -27009,13 +27009,13 @@
         <v>1282</v>
       </c>
       <c r="J2" t="s">
-        <v>1642</v>
+        <v>1627</v>
       </c>
       <c r="K2" t="s">
         <v>1518</v>
       </c>
       <c r="L2" t="s">
-        <v>1617</v>
+        <v>1602</v>
       </c>
       <c r="M2">
         <v>15702687.604910901</v>
@@ -27039,13 +27039,13 @@
         <v>49</v>
       </c>
       <c r="U2" t="s">
-        <v>1651</v>
+        <v>1636</v>
       </c>
       <c r="V2" s="1" t="s">
         <v>1160</v>
       </c>
       <c r="W2" t="s">
-        <v>1565</v>
+        <v>1664</v>
       </c>
       <c r="X2" s="21">
         <f>prod_table_raw!N11</f>
@@ -27054,7 +27054,7 @@
       <c r="Y2"/>
       <c r="Z2"/>
       <c r="AA2">
-        <f>X2-Y2-Z2</f>
+        <f t="shared" ref="AA2:AA33" si="0">X2-Y2-Z2</f>
         <v>11187000</v>
       </c>
       <c r="AB2" s="54">
@@ -27103,7 +27103,7 @@
         <v>0</v>
       </c>
       <c r="AZ2">
-        <f>Y2</f>
+        <f t="shared" ref="AZ2:AZ33" si="1">Y2</f>
         <v>0</v>
       </c>
     </row>
@@ -27124,13 +27124,13 @@
         <v>64</v>
       </c>
       <c r="H3" t="s">
-        <v>1630</v>
+        <v>1615</v>
       </c>
       <c r="I3" t="s">
-        <v>1664</v>
+        <v>1649</v>
       </c>
       <c r="J3" t="s">
-        <v>1650</v>
+        <v>1635</v>
       </c>
       <c r="K3" t="s">
         <v>1511</v>
@@ -27139,7 +27139,7 @@
         <v>1508</v>
       </c>
       <c r="N3" t="s">
-        <v>1586</v>
+        <v>1571</v>
       </c>
       <c r="P3" t="s">
         <v>1205</v>
@@ -27163,7 +27163,7 @@
         <v>997</v>
       </c>
       <c r="W3" t="s">
-        <v>1556</v>
+        <v>1659</v>
       </c>
       <c r="X3" s="21">
         <f>prod_table_raw!N13</f>
@@ -27175,7 +27175,7 @@
       </c>
       <c r="Z3"/>
       <c r="AA3">
-        <f>X3-Y3-Z3</f>
+        <f t="shared" si="0"/>
         <v>165999.07959030612</v>
       </c>
       <c r="AB3" s="54">
@@ -27227,7 +27227,7 @@
         <v>0</v>
       </c>
       <c r="AZ3">
-        <f>Y3</f>
+        <f t="shared" si="1"/>
         <v>0.92040969387755101</v>
       </c>
     </row>
@@ -27253,8 +27253,8 @@
       <c r="K4" t="s">
         <v>1516</v>
       </c>
-      <c r="M4" t="s">
-        <v>1205</v>
+      <c r="M4">
+        <v>1248584.6715172599</v>
       </c>
       <c r="Q4" t="s">
         <v>1205</v>
@@ -27275,7 +27275,7 @@
       <c r="Y4"/>
       <c r="Z4"/>
       <c r="AA4">
-        <f>X4-Y4-Z4</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AB4"/>
@@ -27321,7 +27321,7 @@
       <c r="AX4" s="34"/>
       <c r="AY4" s="34"/>
       <c r="AZ4">
-        <f>Y4</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -27342,13 +27342,13 @@
         <v>78</v>
       </c>
       <c r="H5" t="s">
-        <v>1632</v>
+        <v>1617</v>
       </c>
       <c r="I5" t="s">
-        <v>1664</v>
+        <v>1649</v>
       </c>
       <c r="J5" t="s">
-        <v>1640</v>
+        <v>1625</v>
       </c>
       <c r="K5" t="s">
         <v>1518</v>
@@ -27360,7 +27360,7 @@
         <v>19028718.451565798</v>
       </c>
       <c r="N5" t="s">
-        <v>1594</v>
+        <v>1579</v>
       </c>
       <c r="Q5" t="s">
         <v>1205</v>
@@ -27369,7 +27369,7 @@
         <v>1205</v>
       </c>
       <c r="S5" t="s">
-        <v>1635</v>
+        <v>1620</v>
       </c>
       <c r="T5" s="22" t="s">
         <v>65</v>
@@ -27381,7 +27381,7 @@
         <v>1167</v>
       </c>
       <c r="W5" t="s">
-        <v>1556</v>
+        <v>1659</v>
       </c>
       <c r="X5" s="21">
         <f>prod_table_raw!N17</f>
@@ -27393,7 +27393,7 @@
       </c>
       <c r="Z5"/>
       <c r="AA5">
-        <f>X5-Y5-Z5</f>
+        <f t="shared" si="0"/>
         <v>17332870.960915469</v>
       </c>
       <c r="AB5" s="54">
@@ -27448,7 +27448,7 @@
         <v>0</v>
       </c>
       <c r="AZ5">
-        <f>Y5</f>
+        <f t="shared" si="1"/>
         <v>29.039084533163262</v>
       </c>
     </row>
@@ -27469,7 +27469,7 @@
         <v>78</v>
       </c>
       <c r="H6" t="s">
-        <v>1628</v>
+        <v>1613</v>
       </c>
       <c r="I6" t="s">
         <v>1496</v>
@@ -27496,13 +27496,13 @@
         <v>49</v>
       </c>
       <c r="U6" t="s">
-        <v>1651</v>
+        <v>1636</v>
       </c>
       <c r="V6" t="s">
         <v>1160</v>
       </c>
       <c r="W6" t="s">
-        <v>1567</v>
+        <v>1665</v>
       </c>
       <c r="X6" s="21">
         <f>prod_table_raw!N21</f>
@@ -27511,7 +27511,7 @@
       <c r="Y6"/>
       <c r="Z6"/>
       <c r="AA6">
-        <f>X6-Y6-Z6</f>
+        <f t="shared" si="0"/>
         <v>16478000</v>
       </c>
       <c r="AB6" s="54">
@@ -27560,7 +27560,7 @@
         <v>0</v>
       </c>
       <c r="AZ6">
-        <f>Y6</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -27581,22 +27581,22 @@
         <v>91</v>
       </c>
       <c r="H7" t="s">
-        <v>1632</v>
+        <v>1617</v>
       </c>
       <c r="I7" t="s">
-        <v>1664</v>
+        <v>1649</v>
       </c>
       <c r="K7" t="s">
         <v>1518</v>
       </c>
       <c r="L7" t="s">
-        <v>1615</v>
+        <v>1600</v>
       </c>
       <c r="M7">
         <v>6202897.0171400001</v>
       </c>
       <c r="N7" t="s">
-        <v>1587</v>
+        <v>1572</v>
       </c>
       <c r="S7" t="s">
         <v>1205</v>
@@ -27611,7 +27611,7 @@
         <v>997</v>
       </c>
       <c r="W7" t="s">
-        <v>1556</v>
+        <v>1659</v>
       </c>
       <c r="X7" s="21">
         <f>prod_table_raw!N24</f>
@@ -27623,7 +27623,7 @@
       </c>
       <c r="Z7"/>
       <c r="AA7">
-        <f>X7-Y7-Z7</f>
+        <f t="shared" si="0"/>
         <v>1361446.483400204</v>
       </c>
       <c r="AB7" s="54">
@@ -27678,7 +27678,7 @@
         <v>0</v>
       </c>
       <c r="AZ7">
-        <f>Y7</f>
+        <f t="shared" si="1"/>
         <v>3.5165997959183577</v>
       </c>
     </row>
@@ -27705,13 +27705,13 @@
         <v>98</v>
       </c>
       <c r="H8" t="s">
-        <v>1632</v>
+        <v>1617</v>
       </c>
       <c r="I8" t="s">
-        <v>1669</v>
+        <v>1654</v>
       </c>
       <c r="J8" t="s">
-        <v>1642</v>
+        <v>1627</v>
       </c>
       <c r="K8" t="s">
         <v>1519</v>
@@ -27732,13 +27732,13 @@
         <v>373</v>
       </c>
       <c r="U8" t="s">
-        <v>1661</v>
+        <v>1646</v>
       </c>
       <c r="V8" t="s">
         <v>1488</v>
       </c>
       <c r="W8" t="s">
-        <v>1553</v>
+        <v>1660</v>
       </c>
       <c r="X8" s="21">
         <f>prod_table_raw!N30</f>
@@ -27750,7 +27750,7 @@
         <v>54693.75</v>
       </c>
       <c r="AA8">
-        <f>X8-Y8-Z8</f>
+        <f t="shared" si="0"/>
         <v>693306.25</v>
       </c>
       <c r="AB8" s="54">
@@ -27802,7 +27802,7 @@
         <v>0</v>
       </c>
       <c r="AZ8">
-        <f>Y8</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -27829,7 +27829,7 @@
         <v>411</v>
       </c>
       <c r="H9" t="s">
-        <v>1632</v>
+        <v>1617</v>
       </c>
       <c r="I9" t="s">
         <v>1503</v>
@@ -27838,10 +27838,10 @@
         <v>1518</v>
       </c>
       <c r="L9" t="s">
-        <v>1617</v>
-      </c>
-      <c r="M9" t="s">
-        <v>1205</v>
+        <v>1602</v>
+      </c>
+      <c r="M9">
+        <v>3963061.6444813549</v>
       </c>
       <c r="O9" t="s">
         <v>1205</v>
@@ -27856,19 +27856,19 @@
         <v>551</v>
       </c>
       <c r="U9" t="s">
-        <v>1661</v>
+        <v>1646</v>
       </c>
       <c r="V9" t="s">
         <v>1488</v>
       </c>
       <c r="W9" t="s">
-        <v>1647</v>
+        <v>1632</v>
       </c>
       <c r="X9" s="21"/>
       <c r="Y9"/>
       <c r="Z9"/>
       <c r="AA9">
-        <f>X9-Y9-Z9</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AB9"/>
@@ -27908,7 +27908,7 @@
       <c r="AX9" s="34"/>
       <c r="AY9" s="34"/>
       <c r="AZ9">
-        <f>Y9</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -27929,22 +27929,25 @@
         <v>78</v>
       </c>
       <c r="H10" t="s">
-        <v>1629</v>
+        <v>1614</v>
       </c>
       <c r="I10" t="s">
-        <v>1667</v>
+        <v>1652</v>
       </c>
       <c r="K10" t="s">
         <v>1518</v>
       </c>
       <c r="L10" t="s">
-        <v>1624</v>
+        <v>1609</v>
       </c>
       <c r="M10">
         <v>13233210.388599999</v>
       </c>
       <c r="N10" t="s">
-        <v>1593</v>
+        <v>1578</v>
+      </c>
+      <c r="O10" t="s">
+        <v>1205</v>
       </c>
       <c r="Q10" t="s">
         <v>1205</v>
@@ -27965,7 +27968,7 @@
         <v>1168</v>
       </c>
       <c r="W10" t="s">
-        <v>1552</v>
+        <v>1671</v>
       </c>
       <c r="X10" s="21">
         <f>prod_table_raw!N36</f>
@@ -27977,11 +27980,11 @@
         <v>63500</v>
       </c>
       <c r="AA10">
-        <f>X10-Y10-Z10</f>
+        <f t="shared" si="0"/>
         <v>6798652</v>
       </c>
       <c r="AB10" s="54">
-        <f>1-(Y10+Z10)/AA10</f>
+        <f t="shared" ref="AB10:AB22" si="2">1-(Y10+Z10)/AA10</f>
         <v>0.99065991317102275</v>
       </c>
       <c r="AC10" s="34">
@@ -28035,7 +28038,7 @@
         <v>0</v>
       </c>
       <c r="AZ10">
-        <f>Y10</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -28062,13 +28065,13 @@
         <v>98</v>
       </c>
       <c r="H11" t="s">
-        <v>1632</v>
+        <v>1617</v>
       </c>
       <c r="I11" t="s">
-        <v>1669</v>
+        <v>1654</v>
       </c>
       <c r="J11" t="s">
-        <v>1642</v>
+        <v>1627</v>
       </c>
       <c r="K11" t="s">
         <v>1515</v>
@@ -28077,7 +28080,7 @@
         <v>1929968.1763706871</v>
       </c>
       <c r="N11" t="s">
-        <v>1587</v>
+        <v>1572</v>
       </c>
       <c r="Q11" t="s">
         <v>1205</v>
@@ -28092,13 +28095,13 @@
         <v>373</v>
       </c>
       <c r="U11" t="s">
-        <v>1661</v>
+        <v>1646</v>
       </c>
       <c r="V11" t="s">
         <v>1488</v>
       </c>
       <c r="W11" t="s">
-        <v>1553</v>
+        <v>1660</v>
       </c>
       <c r="X11" s="21">
         <f>prod_table_raw!N44</f>
@@ -28110,11 +28113,11 @@
         <v>70900</v>
       </c>
       <c r="AA11">
-        <f>X11-Y11-Z11</f>
+        <f t="shared" si="0"/>
         <v>362100</v>
       </c>
       <c r="AB11" s="54">
-        <f>1-(Y11+Z11)/AA11</f>
+        <f t="shared" si="2"/>
         <v>0.80419773543220108</v>
       </c>
       <c r="AC11" s="34"/>
@@ -28162,7 +28165,7 @@
         <v>0</v>
       </c>
       <c r="AZ11">
-        <f>Y11</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -28183,10 +28186,10 @@
         <v>78</v>
       </c>
       <c r="H12" t="s">
-        <v>1629</v>
+        <v>1614</v>
       </c>
       <c r="I12" t="s">
-        <v>1664</v>
+        <v>1649</v>
       </c>
       <c r="K12" t="s">
         <v>1518</v>
@@ -28198,7 +28201,7 @@
         <v>10276967.100669291</v>
       </c>
       <c r="N12" t="s">
-        <v>1591</v>
+        <v>1576</v>
       </c>
       <c r="Q12" t="s">
         <v>1205</v>
@@ -28207,7 +28210,7 @@
         <v>1205</v>
       </c>
       <c r="S12" t="s">
-        <v>1635</v>
+        <v>1620</v>
       </c>
       <c r="T12" s="22" t="s">
         <v>115</v>
@@ -28219,7 +28222,7 @@
         <v>1167</v>
       </c>
       <c r="W12" t="s">
-        <v>1556</v>
+        <v>1659</v>
       </c>
       <c r="X12" s="21">
         <f>prod_table_raw!N48</f>
@@ -28231,11 +28234,11 @@
       </c>
       <c r="Z12"/>
       <c r="AA12">
-        <f>X12-Y12-Z12</f>
+        <f t="shared" si="0"/>
         <v>25434829.49413256</v>
       </c>
       <c r="AB12" s="54">
-        <f>1-(Y12+Z12)/AA12</f>
+        <f t="shared" si="2"/>
         <v>0.99999905608630701</v>
       </c>
       <c r="AC12" s="34">
@@ -28286,7 +28289,7 @@
         <v>0</v>
       </c>
       <c r="AZ12">
-        <f>Y12</f>
+        <f t="shared" si="1"/>
         <v>24.008283837755101</v>
       </c>
     </row>
@@ -28307,25 +28310,28 @@
         <v>64</v>
       </c>
       <c r="H13" t="s">
-        <v>1632</v>
+        <v>1617</v>
       </c>
       <c r="I13" t="s">
-        <v>1664</v>
+        <v>1649</v>
       </c>
       <c r="K13" t="s">
         <v>1510</v>
       </c>
       <c r="L13" t="s">
-        <v>1625</v>
+        <v>1610</v>
       </c>
       <c r="M13">
         <v>352884.57374953461</v>
       </c>
       <c r="N13" t="s">
-        <v>1590</v>
+        <v>1575</v>
+      </c>
+      <c r="O13" t="s">
+        <v>1205</v>
       </c>
       <c r="S13" t="s">
-        <v>1635</v>
+        <v>1620</v>
       </c>
       <c r="T13" s="22" t="s">
         <v>115</v>
@@ -28337,7 +28343,7 @@
         <v>997</v>
       </c>
       <c r="W13" t="s">
-        <v>1556</v>
+        <v>1659</v>
       </c>
       <c r="X13" s="21">
         <f>prod_table_raw!N55</f>
@@ -28349,11 +28355,11 @@
       </c>
       <c r="Z13"/>
       <c r="AA13">
-        <f>X13-Y13-Z13</f>
+        <f t="shared" si="0"/>
         <v>222624.22394914847</v>
       </c>
       <c r="AB13" s="54">
-        <f>1-(Y13+Z13)/AA13</f>
+        <f t="shared" si="2"/>
         <v>0.99998753032890009</v>
       </c>
       <c r="AC13" s="34">
@@ -28401,7 +28407,7 @@
         <v>0</v>
       </c>
       <c r="AZ13">
-        <f>Y13</f>
+        <f t="shared" si="1"/>
         <v>2.7760508515306124</v>
       </c>
     </row>
@@ -28422,10 +28428,10 @@
         <v>64</v>
       </c>
       <c r="H14" t="s">
-        <v>1628</v>
+        <v>1613</v>
       </c>
       <c r="I14" t="s">
-        <v>1664</v>
+        <v>1649</v>
       </c>
       <c r="K14" t="s">
         <v>1510</v>
@@ -28437,7 +28443,7 @@
         <v>1445491.9253398541</v>
       </c>
       <c r="N14" t="s">
-        <v>1590</v>
+        <v>1575</v>
       </c>
       <c r="R14" t="s">
         <v>1205</v>
@@ -28455,7 +28461,7 @@
         <v>1167</v>
       </c>
       <c r="W14" t="s">
-        <v>1556</v>
+        <v>1659</v>
       </c>
       <c r="X14" s="21">
         <f>prod_table_raw!N62</f>
@@ -28467,11 +28473,11 @@
       </c>
       <c r="Z14"/>
       <c r="AA14">
-        <f>X14-Y14-Z14</f>
+        <f t="shared" si="0"/>
         <v>1660992.2611000792</v>
       </c>
       <c r="AB14" s="54">
-        <f>1-(Y14+Z14)/AA14</f>
+        <f t="shared" si="2"/>
         <v>0.99999534079712338</v>
       </c>
       <c r="AC14" s="34">
@@ -28522,7 +28528,7 @@
         <v>0</v>
       </c>
       <c r="AZ14">
-        <f>Y14</f>
+        <f t="shared" si="1"/>
         <v>7.7388999209183664</v>
       </c>
     </row>
@@ -28543,13 +28549,13 @@
         <v>57</v>
       </c>
       <c r="H15" t="s">
-        <v>1628</v>
+        <v>1613</v>
       </c>
       <c r="I15" t="s">
-        <v>1664</v>
+        <v>1649</v>
       </c>
       <c r="J15" t="s">
-        <v>1642</v>
+        <v>1627</v>
       </c>
       <c r="K15" t="s">
         <v>1516</v>
@@ -28558,7 +28564,7 @@
         <v>416736.86034155951</v>
       </c>
       <c r="N15" t="s">
-        <v>1589</v>
+        <v>1574</v>
       </c>
       <c r="Q15" t="s">
         <v>1205</v>
@@ -28573,13 +28579,13 @@
         <v>115</v>
       </c>
       <c r="U15" t="s">
-        <v>1610</v>
+        <v>1595</v>
       </c>
       <c r="V15" t="s">
         <v>997</v>
       </c>
       <c r="W15" t="s">
-        <v>1556</v>
+        <v>1659</v>
       </c>
       <c r="X15" s="21">
         <f>prod_table_raw!N64</f>
@@ -28591,11 +28597,11 @@
       </c>
       <c r="Z15"/>
       <c r="AA15">
-        <f>X15-Y15-Z15</f>
+        <f t="shared" si="0"/>
         <v>33244.875712953064</v>
       </c>
       <c r="AB15" s="54">
-        <f>1-(Y15+Z15)/AA15</f>
+        <f t="shared" si="2"/>
         <v>0.99999626146754128</v>
       </c>
       <c r="AC15" s="34">
@@ -28643,7 +28649,7 @@
         <v>0</v>
       </c>
       <c r="AZ15">
-        <f>Y15</f>
+        <f t="shared" si="1"/>
         <v>0.12428704693877551</v>
       </c>
     </row>
@@ -28664,10 +28670,10 @@
         <v>91</v>
       </c>
       <c r="H16" t="s">
-        <v>1632</v>
+        <v>1617</v>
       </c>
       <c r="I16" t="s">
-        <v>1664</v>
+        <v>1649</v>
       </c>
       <c r="K16" t="s">
         <v>1515</v>
@@ -28676,7 +28682,7 @@
         <v>7405086.2285420913</v>
       </c>
       <c r="N16" t="s">
-        <v>1592</v>
+        <v>1577</v>
       </c>
       <c r="Q16" t="s">
         <v>1205</v>
@@ -28691,13 +28697,13 @@
         <v>115</v>
       </c>
       <c r="U16" t="s">
-        <v>1612</v>
+        <v>1597</v>
       </c>
       <c r="V16" t="s">
         <v>997</v>
       </c>
       <c r="W16" t="s">
-        <v>1556</v>
+        <v>1659</v>
       </c>
       <c r="X16" s="21">
         <f>prod_table_raw!N70</f>
@@ -28709,11 +28715,11 @@
       </c>
       <c r="Z16"/>
       <c r="AA16">
-        <f>X16-Y16-Z16</f>
+        <f t="shared" si="0"/>
         <v>456998.54638744897</v>
       </c>
       <c r="AB16" s="54">
-        <f>1-(Y16+Z16)/AA16</f>
+        <f t="shared" si="2"/>
         <v>0.99999681921843619</v>
       </c>
       <c r="AC16" s="34">
@@ -28764,7 +28770,7 @@
         <v>0</v>
       </c>
       <c r="AZ16">
-        <f>Y16</f>
+        <f t="shared" si="1"/>
         <v>1.4536125510204081</v>
       </c>
     </row>
@@ -28791,13 +28797,13 @@
         <v>98</v>
       </c>
       <c r="H17" t="s">
-        <v>1632</v>
+        <v>1617</v>
       </c>
       <c r="I17" t="s">
-        <v>1669</v>
+        <v>1654</v>
       </c>
       <c r="J17" t="s">
-        <v>1642</v>
+        <v>1627</v>
       </c>
       <c r="K17" t="s">
         <v>1516</v>
@@ -28824,7 +28830,7 @@
         <v>1488</v>
       </c>
       <c r="W17" t="s">
-        <v>1553</v>
+        <v>1660</v>
       </c>
       <c r="X17" s="21">
         <f>prod_table_raw!N73</f>
@@ -28836,11 +28842,11 @@
         <v>0</v>
       </c>
       <c r="AA17">
-        <f>X17-Y17-Z17</f>
+        <f t="shared" si="0"/>
         <v>553033</v>
       </c>
       <c r="AB17" s="54">
-        <f>1-(Y17+Z17)/AA17</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="AC17" s="34"/>
@@ -28882,7 +28888,7 @@
         <v>0</v>
       </c>
       <c r="AZ17">
-        <f>Y17</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -28909,13 +28915,13 @@
         <v>98</v>
       </c>
       <c r="H18" t="s">
-        <v>1632</v>
+        <v>1617</v>
       </c>
       <c r="I18" t="s">
-        <v>1669</v>
+        <v>1654</v>
       </c>
       <c r="J18" t="s">
-        <v>1642</v>
+        <v>1627</v>
       </c>
       <c r="K18" t="s">
         <v>1519</v>
@@ -28924,7 +28930,7 @@
         <v>2161806.0909095029</v>
       </c>
       <c r="N18" t="s">
-        <v>1587</v>
+        <v>1572</v>
       </c>
       <c r="Q18" t="s">
         <v>1205</v>
@@ -28939,13 +28945,13 @@
         <v>373</v>
       </c>
       <c r="U18" t="s">
-        <v>1661</v>
+        <v>1646</v>
       </c>
       <c r="V18" t="s">
         <v>1488</v>
       </c>
       <c r="W18" t="s">
-        <v>1553</v>
+        <v>1660</v>
       </c>
       <c r="X18" s="21">
         <f>prod_table_raw!N76</f>
@@ -28957,11 +28963,11 @@
         <v>49662.5</v>
       </c>
       <c r="AA18">
-        <f>X18-Y18-Z18</f>
+        <f t="shared" si="0"/>
         <v>566337.5</v>
       </c>
       <c r="AB18" s="54">
-        <f>1-(Y18+Z18)/AA18</f>
+        <f t="shared" si="2"/>
         <v>0.91230935617012821</v>
       </c>
       <c r="AC18" s="34"/>
@@ -29009,7 +29015,7 @@
         <v>0</v>
       </c>
       <c r="AZ18">
-        <f>Y18</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -29030,10 +29036,10 @@
         <v>78</v>
       </c>
       <c r="H19" t="s">
-        <v>1628</v>
+        <v>1613</v>
       </c>
       <c r="I19" t="s">
-        <v>1668</v>
+        <v>1653</v>
       </c>
       <c r="K19" t="s">
         <v>1517</v>
@@ -29045,7 +29051,7 @@
         <v>22527998.6785</v>
       </c>
       <c r="N19" t="s">
-        <v>1595</v>
+        <v>1580</v>
       </c>
       <c r="Q19" t="s">
         <v>1205</v>
@@ -29063,10 +29069,10 @@
         <v>1205</v>
       </c>
       <c r="V19" t="s">
-        <v>1659</v>
+        <v>1644</v>
       </c>
       <c r="W19" t="s">
-        <v>1557</v>
+        <v>1661</v>
       </c>
       <c r="X19" s="21">
         <f>prod_table_raw!N80</f>
@@ -29078,11 +29084,11 @@
         <v>186436.98475294118</v>
       </c>
       <c r="AA19">
-        <f>X19-Y19-Z19</f>
+        <f t="shared" si="0"/>
         <v>29813563.015247058</v>
       </c>
       <c r="AB19" s="54">
-        <f>1-(Y19+Z19)/AA19</f>
+        <f t="shared" si="2"/>
         <v>0.9937465714964161</v>
       </c>
       <c r="AC19" s="34"/>
@@ -29133,7 +29139,7 @@
         <v>0</v>
       </c>
       <c r="AZ19">
-        <f>Y19</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -29154,10 +29160,10 @@
         <v>64</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>1666</v>
+        <v>1651</v>
       </c>
       <c r="J20" t="s">
-        <v>1638</v>
+        <v>1623</v>
       </c>
       <c r="K20" t="s">
         <v>1518</v>
@@ -29169,7 +29175,7 @@
         <v>1341835.17078</v>
       </c>
       <c r="N20" t="s">
-        <v>1586</v>
+        <v>1571</v>
       </c>
       <c r="Q20" t="s">
         <v>1205</v>
@@ -29178,7 +29184,7 @@
         <v>1205</v>
       </c>
       <c r="S20" t="s">
-        <v>1635</v>
+        <v>1620</v>
       </c>
       <c r="T20" s="22" t="s">
         <v>65</v>
@@ -29187,10 +29193,10 @@
         <v>1205</v>
       </c>
       <c r="V20" t="s">
-        <v>1657</v>
+        <v>1642</v>
       </c>
       <c r="W20" t="s">
-        <v>1555</v>
+        <v>1662</v>
       </c>
       <c r="X20" s="21">
         <f>prod_table_raw!N86</f>
@@ -29205,11 +29211,11 @@
         <v>130.12252666666666</v>
       </c>
       <c r="AA20">
-        <f>X20-Y20-Z20</f>
+        <f t="shared" si="0"/>
         <v>2886792.7316552154</v>
       </c>
       <c r="AB20" s="54">
-        <f>1-(Y20+Z20)/AA20</f>
+        <f t="shared" si="2"/>
         <v>0.9999533748761007</v>
       </c>
       <c r="AC20" s="34">
@@ -29260,7 +29266,7 @@
         <v>0</v>
       </c>
       <c r="AZ20">
-        <f>Y20</f>
+        <f t="shared" si="1"/>
         <v>4.4745421183166938</v>
       </c>
     </row>
@@ -29281,22 +29287,25 @@
         <v>91</v>
       </c>
       <c r="H21" t="s">
-        <v>1632</v>
+        <v>1617</v>
       </c>
       <c r="I21" t="s">
-        <v>1664</v>
+        <v>1649</v>
       </c>
       <c r="K21" t="s">
         <v>1518</v>
       </c>
       <c r="L21" t="s">
-        <v>1624</v>
+        <v>1609</v>
       </c>
       <c r="M21">
         <v>3503071.0617284952</v>
       </c>
       <c r="N21" t="s">
-        <v>1591</v>
+        <v>1576</v>
+      </c>
+      <c r="O21" t="s">
+        <v>1205</v>
       </c>
       <c r="Q21" t="s">
         <v>1205</v>
@@ -29305,7 +29314,7 @@
         <v>1205</v>
       </c>
       <c r="S21" t="s">
-        <v>1635</v>
+        <v>1620</v>
       </c>
       <c r="T21" s="22" t="s">
         <v>115</v>
@@ -29317,7 +29326,7 @@
         <v>997</v>
       </c>
       <c r="W21" t="s">
-        <v>1556</v>
+        <v>1659</v>
       </c>
       <c r="X21" s="21">
         <f>prod_table_raw!N91</f>
@@ -29329,11 +29338,11 @@
       </c>
       <c r="Z21"/>
       <c r="AA21">
-        <f>X21-Y21-Z21</f>
+        <f t="shared" si="0"/>
         <v>1266004.5234763699</v>
       </c>
       <c r="AB21" s="54">
-        <f>1-(Y21+Z21)/AA21</f>
+        <f t="shared" si="2"/>
         <v>0.99999646405400056</v>
       </c>
       <c r="AC21" s="34">
@@ -29381,7 +29390,7 @@
         <v>0</v>
       </c>
       <c r="AZ21">
-        <f>Y21</f>
+        <f t="shared" si="1"/>
         <v>4.476523630102041</v>
       </c>
     </row>
@@ -29402,22 +29411,22 @@
         <v>78</v>
       </c>
       <c r="H22" t="s">
-        <v>1629</v>
+        <v>1614</v>
       </c>
       <c r="I22" t="s">
-        <v>1668</v>
+        <v>1653</v>
       </c>
       <c r="K22" t="s">
         <v>1517</v>
       </c>
       <c r="L22" t="s">
-        <v>1617</v>
+        <v>1602</v>
       </c>
       <c r="M22">
         <v>63924259.804899998</v>
       </c>
       <c r="N22" t="s">
-        <v>1596</v>
+        <v>1581</v>
       </c>
       <c r="O22" t="s">
         <v>1205</v>
@@ -29438,10 +29447,10 @@
         <v>1205</v>
       </c>
       <c r="V22" t="s">
-        <v>1659</v>
+        <v>1644</v>
       </c>
       <c r="W22" t="s">
-        <v>1557</v>
+        <v>1661</v>
       </c>
       <c r="X22" s="21">
         <f>prod_table_raw!N93</f>
@@ -29453,11 +29462,11 @@
         <v>343098.03921568632</v>
       </c>
       <c r="AA22">
-        <f>X22-Y22-Z22</f>
+        <f t="shared" si="0"/>
         <v>17064901.960784312</v>
       </c>
       <c r="AB22" s="54">
-        <f>1-(Y22+Z22)/AA22</f>
+        <f t="shared" si="2"/>
         <v>0.97989452034332591</v>
       </c>
       <c r="AC22" s="34"/>
@@ -29508,7 +29517,7 @@
         <v>0</v>
       </c>
       <c r="AZ22">
-        <f>Y22</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -29535,16 +29544,16 @@
         <v>29</v>
       </c>
       <c r="H23" t="s">
-        <v>1632</v>
+        <v>1617</v>
       </c>
       <c r="I23" t="s">
-        <v>1618</v>
+        <v>1603</v>
       </c>
       <c r="K23" t="s">
         <v>1510</v>
       </c>
       <c r="L23" t="s">
-        <v>1617</v>
+        <v>1602</v>
       </c>
       <c r="O23" t="s">
         <v>1205</v>
@@ -29571,7 +29580,7 @@
       <c r="Y23"/>
       <c r="Z23"/>
       <c r="AA23">
-        <f>X23-Y23-Z23</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AB23"/>
@@ -29611,7 +29620,7 @@
       <c r="AX23" s="34"/>
       <c r="AY23" s="34"/>
       <c r="AZ23">
-        <f>Y23</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -29632,19 +29641,19 @@
         <v>64</v>
       </c>
       <c r="H24" t="s">
-        <v>1632</v>
+        <v>1617</v>
       </c>
       <c r="I24" t="s">
-        <v>1664</v>
+        <v>1649</v>
       </c>
       <c r="K24" t="s">
         <v>1510</v>
       </c>
       <c r="L24" t="s">
-        <v>1616</v>
+        <v>1601</v>
       </c>
       <c r="N24" t="s">
-        <v>1597</v>
+        <v>1582</v>
       </c>
       <c r="P24" t="s">
         <v>1205</v>
@@ -29665,7 +29674,7 @@
         <v>997</v>
       </c>
       <c r="W24" t="s">
-        <v>1556</v>
+        <v>1659</v>
       </c>
       <c r="X24" s="21">
         <f>prod_table_raw!N105</f>
@@ -29677,11 +29686,11 @@
       </c>
       <c r="Z24"/>
       <c r="AA24">
-        <f>X24-Y24-Z24</f>
+        <f t="shared" si="0"/>
         <v>439003.82959193876</v>
       </c>
       <c r="AB24" s="54">
-        <f>1-(Y24+Z24)/AA24</f>
+        <f t="shared" ref="AB24:AB30" si="3">1-(Y24+Z24)/AA24</f>
         <v>0.99999050029229786</v>
       </c>
       <c r="AC24" s="34">
@@ -29729,7 +29738,7 @@
         <v>0</v>
       </c>
       <c r="AZ24">
-        <f>Y24</f>
+        <f t="shared" si="1"/>
         <v>4.1704080612244905</v>
       </c>
     </row>
@@ -29753,19 +29762,19 @@
         <v>64</v>
       </c>
       <c r="H25" t="s">
-        <v>1628</v>
+        <v>1613</v>
       </c>
       <c r="I25" t="s">
-        <v>1506</v>
+        <v>1657</v>
       </c>
       <c r="L25" t="s">
-        <v>1615</v>
+        <v>1600</v>
       </c>
       <c r="M25">
         <v>5293594.021862885</v>
       </c>
       <c r="N25" t="s">
-        <v>1598</v>
+        <v>1583</v>
       </c>
       <c r="S25" t="s">
         <v>1205</v>
@@ -29774,13 +29783,13 @@
         <v>203</v>
       </c>
       <c r="U25" t="s">
-        <v>1611</v>
+        <v>1596</v>
       </c>
       <c r="V25" t="s">
-        <v>1560</v>
+        <v>1553</v>
       </c>
       <c r="W25" t="s">
-        <v>1561</v>
+        <v>1669</v>
       </c>
       <c r="X25" s="21">
         <f>prod_table_raw!N110</f>
@@ -29792,11 +29801,11 @@
         <v>4719.666666666667</v>
       </c>
       <c r="AA25">
-        <f>X25-Y25-Z25</f>
+        <f t="shared" si="0"/>
         <v>122587.33333333333</v>
       </c>
       <c r="AB25" s="54">
-        <f>1-(Y25+Z25)/AA25</f>
+        <f t="shared" si="3"/>
         <v>0.96149955677856869</v>
       </c>
       <c r="AC25" s="34"/>
@@ -29850,7 +29859,7 @@
         <v>0</v>
       </c>
       <c r="AZ25">
-        <f>Y25</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -29871,19 +29880,19 @@
         <v>64</v>
       </c>
       <c r="H26" t="s">
-        <v>1632</v>
+        <v>1617</v>
       </c>
       <c r="I26" t="s">
-        <v>1668</v>
+        <v>1653</v>
       </c>
       <c r="K26" t="s">
-        <v>1643</v>
+        <v>1628</v>
       </c>
       <c r="M26">
         <v>4202253.5385999996</v>
       </c>
       <c r="N26" t="s">
-        <v>1599</v>
+        <v>1584</v>
       </c>
       <c r="Q26" t="s">
         <v>1205</v>
@@ -29898,13 +29907,13 @@
         <v>207</v>
       </c>
       <c r="U26" t="s">
-        <v>1612</v>
+        <v>1597</v>
       </c>
       <c r="V26" t="s">
-        <v>1656</v>
+        <v>1641</v>
       </c>
       <c r="W26" t="s">
-        <v>1558</v>
+        <v>1670</v>
       </c>
       <c r="X26" s="21">
         <f>prod_table_raw!N116</f>
@@ -29916,11 +29925,11 @@
         <v>152533.33333333334</v>
       </c>
       <c r="AA26">
-        <f>X26-Y26-Z26</f>
+        <f t="shared" si="0"/>
         <v>1187466.6666666667</v>
       </c>
       <c r="AB26" s="54">
-        <f>1-(Y26+Z26)/AA26</f>
+        <f t="shared" si="3"/>
         <v>0.871547271502358</v>
       </c>
       <c r="AC26" s="34"/>
@@ -29974,7 +29983,7 @@
         <v>0</v>
       </c>
       <c r="AZ26">
-        <f>Y26</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -29995,19 +30004,22 @@
         <v>78</v>
       </c>
       <c r="I27" t="s">
-        <v>1664</v>
+        <v>1649</v>
       </c>
       <c r="K27" t="s">
         <v>1516</v>
       </c>
       <c r="L27" t="s">
-        <v>1625</v>
+        <v>1610</v>
       </c>
       <c r="M27">
         <v>3436361.1128654238</v>
       </c>
       <c r="N27" t="s">
-        <v>1586</v>
+        <v>1571</v>
+      </c>
+      <c r="O27" t="s">
+        <v>1205</v>
       </c>
       <c r="S27" t="s">
         <v>1205</v>
@@ -30016,13 +30028,13 @@
         <v>65</v>
       </c>
       <c r="U27" t="s">
-        <v>1611</v>
+        <v>1596</v>
       </c>
       <c r="V27" t="s">
         <v>1167</v>
       </c>
       <c r="W27" t="s">
-        <v>1556</v>
+        <v>1659</v>
       </c>
       <c r="X27" s="21">
         <f>prod_table_raw!N120</f>
@@ -30034,11 +30046,11 @@
       </c>
       <c r="Z27"/>
       <c r="AA27">
-        <f>X27-Y27-Z27</f>
+        <f t="shared" si="0"/>
         <v>191146.77982239029</v>
       </c>
       <c r="AB27" s="54">
-        <f>1-(Y27+Z27)/AA27</f>
+        <f t="shared" si="3"/>
         <v>0.99999361654111663</v>
       </c>
       <c r="AC27" s="34">
@@ -30089,7 +30101,7 @@
         <v>0</v>
       </c>
       <c r="AZ27">
-        <f>Y27</f>
+        <f t="shared" si="1"/>
         <v>1.2201776096938775</v>
       </c>
     </row>
@@ -30110,13 +30122,13 @@
         <v>91</v>
       </c>
       <c r="H28" t="s">
-        <v>1628</v>
+        <v>1613</v>
       </c>
       <c r="I28" t="s">
-        <v>1669</v>
+        <v>1654</v>
       </c>
       <c r="J28" t="s">
-        <v>1641</v>
+        <v>1626</v>
       </c>
       <c r="K28" t="s">
         <v>1512</v>
@@ -30128,7 +30140,7 @@
         <v>8409093.1265900005</v>
       </c>
       <c r="N28" t="s">
-        <v>1600</v>
+        <v>1585</v>
       </c>
       <c r="Q28" t="s">
         <v>1205</v>
@@ -30143,13 +30155,13 @@
         <v>219</v>
       </c>
       <c r="U28" t="s">
-        <v>1611</v>
+        <v>1596</v>
       </c>
       <c r="V28" t="s">
         <v>1005</v>
       </c>
       <c r="W28" t="s">
-        <v>1562</v>
+        <v>1666</v>
       </c>
       <c r="X28" s="21">
         <f>prod_table_raw!N124</f>
@@ -30158,11 +30170,11 @@
       <c r="Y28"/>
       <c r="Z28"/>
       <c r="AA28">
-        <f>X28-Y28-Z28</f>
+        <f t="shared" si="0"/>
         <v>3798000</v>
       </c>
       <c r="AB28" s="54">
-        <f>1-(Y28+Z28)/AA28</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="AC28" s="34">
@@ -30216,7 +30228,7 @@
         <v>0</v>
       </c>
       <c r="AZ28">
-        <f>Y28</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -30237,10 +30249,10 @@
         <v>64</v>
       </c>
       <c r="H29" t="s">
-        <v>1632</v>
+        <v>1617</v>
       </c>
       <c r="I29" t="s">
-        <v>1664</v>
+        <v>1649</v>
       </c>
       <c r="K29" t="s">
         <v>1516</v>
@@ -30252,7 +30264,7 @@
         <v>11904079.93924279</v>
       </c>
       <c r="N29" t="s">
-        <v>1586</v>
+        <v>1571</v>
       </c>
       <c r="Q29" t="s">
         <v>1205</v>
@@ -30267,13 +30279,13 @@
         <v>65</v>
       </c>
       <c r="U29" t="s">
-        <v>1611</v>
+        <v>1596</v>
       </c>
       <c r="V29" t="s">
         <v>1167</v>
       </c>
       <c r="W29" t="s">
-        <v>1556</v>
+        <v>1659</v>
       </c>
       <c r="X29" s="21">
         <f>prod_table_raw!N134</f>
@@ -30285,11 +30297,11 @@
       </c>
       <c r="Z29"/>
       <c r="AA29">
-        <f>X29-Y29-Z29</f>
+        <f t="shared" si="0"/>
         <v>838411.067179278</v>
       </c>
       <c r="AB29" s="54">
-        <f>1-(Y29+Z29)/AA29</f>
+        <f t="shared" si="3"/>
         <v>0.99999053826812112</v>
       </c>
       <c r="AC29" s="34">
@@ -30340,7 +30352,7 @@
         <v>0</v>
       </c>
       <c r="AZ29">
-        <f>Y29</f>
+        <f t="shared" si="1"/>
         <v>7.932820721938775</v>
       </c>
     </row>
@@ -30361,13 +30373,13 @@
         <v>64</v>
       </c>
       <c r="H30" t="s">
-        <v>1632</v>
+        <v>1617</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>1666</v>
+        <v>1651</v>
       </c>
       <c r="J30" t="s">
-        <v>1639</v>
+        <v>1624</v>
       </c>
       <c r="K30" t="s">
         <v>1518</v>
@@ -30379,7 +30391,7 @@
         <v>5574423.9812850002</v>
       </c>
       <c r="N30" t="s">
-        <v>1601</v>
+        <v>1586</v>
       </c>
       <c r="Q30" t="s">
         <v>1205</v>
@@ -30388,7 +30400,7 @@
         <v>1205</v>
       </c>
       <c r="S30" t="s">
-        <v>1635</v>
+        <v>1620</v>
       </c>
       <c r="T30" s="22" t="s">
         <v>234</v>
@@ -30397,10 +30409,10 @@
         <v>1205</v>
       </c>
       <c r="V30" t="s">
-        <v>1658</v>
+        <v>1643</v>
       </c>
       <c r="W30" t="s">
-        <v>1569</v>
+        <v>1663</v>
       </c>
       <c r="X30" s="21">
         <f>prod_table_raw!N139</f>
@@ -30415,11 +30427,11 @@
         <v>23998.078283999999</v>
       </c>
       <c r="AA30">
-        <f>X30-Y30-Z30</f>
+        <f t="shared" si="0"/>
         <v>1477492.1188132097</v>
       </c>
       <c r="AB30" s="54">
-        <f>1-(Y30+Z30)/AA30</f>
+        <f t="shared" si="3"/>
         <v>0.98375092436630085</v>
       </c>
       <c r="AC30" s="34">
@@ -30476,7 +30488,7 @@
         <v>0</v>
       </c>
       <c r="AZ30">
-        <f>Y30</f>
+        <f t="shared" si="1"/>
         <v>9.8029027903061134</v>
       </c>
     </row>
@@ -30497,7 +30509,7 @@
         <v>71</v>
       </c>
       <c r="H31" t="s">
-        <v>1632</v>
+        <v>1617</v>
       </c>
       <c r="I31" t="s">
         <v>1251</v>
@@ -30506,10 +30518,10 @@
         <v>1518</v>
       </c>
       <c r="L31" t="s">
-        <v>1617</v>
-      </c>
-      <c r="M31" t="s">
-        <v>1205</v>
+        <v>1602</v>
+      </c>
+      <c r="M31">
+        <v>681889.99643018574</v>
       </c>
       <c r="O31" t="s">
         <v>1205</v>
@@ -30527,19 +30539,19 @@
         <v>326</v>
       </c>
       <c r="U31" t="s">
-        <v>1646</v>
+        <v>1631</v>
       </c>
       <c r="V31" t="s">
         <v>995</v>
       </c>
       <c r="W31" t="s">
-        <v>1648</v>
+        <v>1633</v>
       </c>
       <c r="X31" s="21"/>
       <c r="Y31"/>
       <c r="Z31"/>
       <c r="AA31">
-        <f>X31-Y31-Z31</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AB31"/>
@@ -30579,7 +30591,7 @@
       <c r="AX31" s="34"/>
       <c r="AY31" s="34"/>
       <c r="AZ31">
-        <f>Y31</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -30600,25 +30612,28 @@
         <v>64</v>
       </c>
       <c r="H32" t="s">
-        <v>1632</v>
+        <v>1617</v>
       </c>
       <c r="I32" t="s">
-        <v>1664</v>
+        <v>1649</v>
       </c>
       <c r="J32" t="s">
-        <v>1637</v>
+        <v>1622</v>
       </c>
       <c r="K32" t="s">
         <v>1518</v>
       </c>
       <c r="L32" t="s">
-        <v>1508</v>
+        <v>1609</v>
       </c>
       <c r="M32">
         <v>5804864.8944920022</v>
       </c>
       <c r="N32" t="s">
-        <v>1586</v>
+        <v>1571</v>
+      </c>
+      <c r="O32" t="s">
+        <v>1205</v>
       </c>
       <c r="Q32" t="s">
         <v>1205</v>
@@ -30627,7 +30642,7 @@
         <v>1205</v>
       </c>
       <c r="S32" t="s">
-        <v>1635</v>
+        <v>1620</v>
       </c>
       <c r="T32" s="22" t="s">
         <v>65</v>
@@ -30639,7 +30654,7 @@
         <v>997</v>
       </c>
       <c r="W32" t="s">
-        <v>1556</v>
+        <v>1659</v>
       </c>
       <c r="X32" s="21">
         <f>prod_table_raw!N146</f>
@@ -30651,11 +30666,11 @@
       </c>
       <c r="Z32"/>
       <c r="AA32">
-        <f>X32-Y32-Z32</f>
+        <f t="shared" si="0"/>
         <v>441580.74669553828</v>
       </c>
       <c r="AB32" s="54">
-        <f>1-(Y32+Z32)/AA32</f>
+        <f t="shared" ref="AB32:AB42" si="4">1-(Y32+Z32)/AA32</f>
         <v>0.99998357422845985</v>
       </c>
       <c r="AC32" s="34">
@@ -30703,7 +30718,7 @@
         <v>0</v>
       </c>
       <c r="AZ32">
-        <f>Y32</f>
+        <f t="shared" si="1"/>
         <v>7.253304461734694</v>
       </c>
     </row>
@@ -30724,10 +30739,10 @@
         <v>78</v>
       </c>
       <c r="H33" t="s">
-        <v>1632</v>
+        <v>1617</v>
       </c>
       <c r="I33" t="s">
-        <v>1664</v>
+        <v>1649</v>
       </c>
       <c r="K33" t="s">
         <v>1519</v>
@@ -30736,7 +30751,7 @@
         <v>240468.70558949231</v>
       </c>
       <c r="N33" t="s">
-        <v>1597</v>
+        <v>1582</v>
       </c>
       <c r="Q33" t="s">
         <v>1205</v>
@@ -30751,13 +30766,13 @@
         <v>65</v>
       </c>
       <c r="U33" t="s">
-        <v>1612</v>
+        <v>1597</v>
       </c>
       <c r="V33" t="s">
         <v>997</v>
       </c>
       <c r="W33" t="s">
-        <v>1556</v>
+        <v>1659</v>
       </c>
       <c r="X33" s="21">
         <f>prod_table_raw!N150</f>
@@ -30769,11 +30784,11 @@
       </c>
       <c r="Z33"/>
       <c r="AA33">
-        <f>X33-Y33-Z33</f>
+        <f t="shared" si="0"/>
         <v>1165549.9526372449</v>
       </c>
       <c r="AB33" s="54">
-        <f>1-(Y33+Z33)/AA33</f>
+        <f t="shared" si="4"/>
         <v>0.99999910140037096</v>
       </c>
       <c r="AC33" s="34">
@@ -30821,7 +30836,7 @@
         <v>0</v>
       </c>
       <c r="AZ33">
-        <f>Y33</f>
+        <f t="shared" si="1"/>
         <v>1.0473627551020408</v>
       </c>
     </row>
@@ -30842,19 +30857,19 @@
         <v>57</v>
       </c>
       <c r="H34" t="s">
-        <v>1633</v>
+        <v>1618</v>
       </c>
       <c r="I34" t="s">
         <v>1283</v>
       </c>
       <c r="J34" t="s">
-        <v>1642</v>
+        <v>1627</v>
       </c>
       <c r="K34" t="s">
         <v>1512</v>
       </c>
       <c r="L34" t="s">
-        <v>1617</v>
+        <v>1602</v>
       </c>
       <c r="O34" t="s">
         <v>1205</v>
@@ -30875,7 +30890,7 @@
         <v>149</v>
       </c>
       <c r="U34" t="s">
-        <v>1651</v>
+        <v>1636</v>
       </c>
       <c r="V34" t="s">
         <v>1160</v>
@@ -30890,11 +30905,11 @@
       <c r="Y34"/>
       <c r="Z34"/>
       <c r="AA34">
-        <f>X34-Y34-Z34</f>
+        <f t="shared" ref="AA34:AA65" si="5">X34-Y34-Z34</f>
         <v>5600000</v>
       </c>
       <c r="AB34" s="54">
-        <f>1-(Y34+Z34)/AA34</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AC34" s="34"/>
@@ -30939,7 +30954,7 @@
         <v>0</v>
       </c>
       <c r="AZ34">
-        <f>Y34</f>
+        <f t="shared" ref="AZ34:AZ66" si="6">Y34</f>
         <v>0</v>
       </c>
     </row>
@@ -30960,13 +30975,13 @@
         <v>98</v>
       </c>
       <c r="H35" t="s">
-        <v>1632</v>
+        <v>1617</v>
       </c>
       <c r="I35" t="s">
-        <v>1669</v>
+        <v>1654</v>
       </c>
       <c r="J35" t="s">
-        <v>1641</v>
+        <v>1626</v>
       </c>
       <c r="K35" t="s">
         <v>1519</v>
@@ -30975,7 +30990,7 @@
         <v>989146.07241399994</v>
       </c>
       <c r="N35" t="s">
-        <v>1602</v>
+        <v>1587</v>
       </c>
       <c r="Q35" t="s">
         <v>1205</v>
@@ -30990,13 +31005,13 @@
         <v>271</v>
       </c>
       <c r="U35" t="s">
-        <v>1660</v>
+        <v>1645</v>
       </c>
       <c r="V35" t="s">
         <v>1514</v>
       </c>
       <c r="W35" t="s">
-        <v>1563</v>
+        <v>1667</v>
       </c>
       <c r="X35" s="21">
         <f>prod_table_raw!N157</f>
@@ -31005,11 +31020,11 @@
       <c r="Y35"/>
       <c r="Z35"/>
       <c r="AA35">
-        <f>X35-Y35-Z35</f>
+        <f t="shared" si="5"/>
         <v>317660</v>
       </c>
       <c r="AB35" s="54">
-        <f>1-(Y35+Z35)/AA35</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AC35" s="34"/>
@@ -31054,7 +31069,7 @@
         <v>0</v>
       </c>
       <c r="AZ35">
-        <f>Y35</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -31075,10 +31090,10 @@
         <v>91</v>
       </c>
       <c r="H36" t="s">
-        <v>1628</v>
+        <v>1613</v>
       </c>
       <c r="I36" t="s">
-        <v>1664</v>
+        <v>1649</v>
       </c>
       <c r="K36" t="s">
         <v>1518</v>
@@ -31087,7 +31102,7 @@
         <v>1508</v>
       </c>
       <c r="N36" t="s">
-        <v>1590</v>
+        <v>1575</v>
       </c>
       <c r="P36" t="s">
         <v>1205</v>
@@ -31099,7 +31114,7 @@
         <v>1205</v>
       </c>
       <c r="S36" t="s">
-        <v>1635</v>
+        <v>1620</v>
       </c>
       <c r="T36" s="22" t="s">
         <v>115</v>
@@ -31111,7 +31126,7 @@
         <v>1167</v>
       </c>
       <c r="W36" t="s">
-        <v>1556</v>
+        <v>1659</v>
       </c>
       <c r="X36" s="21">
         <f>prod_table_raw!N163</f>
@@ -31123,11 +31138,11 @@
       </c>
       <c r="Z36"/>
       <c r="AA36">
-        <f>X36-Y36-Z36</f>
+        <f t="shared" si="5"/>
         <v>1918130.58586317</v>
       </c>
       <c r="AB36" s="54">
-        <f>1-(Y36+Z36)/AA36</f>
+        <f t="shared" si="4"/>
         <v>0.99999352800225305</v>
       </c>
       <c r="AC36" s="34">
@@ -31178,7 +31193,7 @@
         <v>0</v>
       </c>
       <c r="AZ36">
-        <f>Y36</f>
+        <f t="shared" si="6"/>
         <v>12.41413683010194</v>
       </c>
     </row>
@@ -31199,10 +31214,10 @@
         <v>78</v>
       </c>
       <c r="H37" t="s">
-        <v>1628</v>
+        <v>1613</v>
       </c>
       <c r="I37" t="s">
-        <v>1667</v>
+        <v>1652</v>
       </c>
       <c r="K37" t="s">
         <v>1517</v>
@@ -31214,7 +31229,7 @@
         <v>12606786.4826</v>
       </c>
       <c r="N37" t="s">
-        <v>1603</v>
+        <v>1588</v>
       </c>
       <c r="Q37" t="s">
         <v>1205</v>
@@ -31232,10 +31247,10 @@
         <v>1205</v>
       </c>
       <c r="V37" t="s">
-        <v>1655</v>
+        <v>1640</v>
       </c>
       <c r="W37" t="s">
-        <v>1564</v>
+        <v>1671</v>
       </c>
       <c r="X37" s="21">
         <f>prod_table_raw!N175</f>
@@ -31247,11 +31262,11 @@
         <v>93533.694346666671</v>
       </c>
       <c r="AA37">
-        <f>X37-Y37-Z37</f>
+        <f t="shared" si="5"/>
         <v>21586466.305653334</v>
       </c>
       <c r="AB37" s="54">
-        <f>1-(Y37+Z37)/AA37</f>
+        <f t="shared" si="4"/>
         <v>0.99566702150216357</v>
       </c>
       <c r="AC37" s="34">
@@ -31302,7 +31317,7 @@
         <v>0</v>
       </c>
       <c r="AZ37">
-        <f>Y37</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -31323,22 +31338,22 @@
         <v>78</v>
       </c>
       <c r="H38" t="s">
-        <v>1628</v>
+        <v>1613</v>
       </c>
       <c r="I38" t="s">
-        <v>1667</v>
+        <v>1652</v>
       </c>
       <c r="K38" t="s">
         <v>1518</v>
       </c>
       <c r="L38" t="s">
-        <v>1617</v>
+        <v>1602</v>
       </c>
       <c r="M38">
         <v>7967834.6375599997</v>
       </c>
       <c r="N38" t="s">
-        <v>1604</v>
+        <v>1589</v>
       </c>
       <c r="O38" t="s">
         <v>1205</v>
@@ -31359,10 +31374,10 @@
         <v>1205</v>
       </c>
       <c r="V38" t="s">
-        <v>1655</v>
+        <v>1640</v>
       </c>
       <c r="W38" t="s">
-        <v>1564</v>
+        <v>1671</v>
       </c>
       <c r="X38" s="21">
         <f>prod_table_raw!N179</f>
@@ -31374,11 +31389,11 @@
         <v>45578.436133333336</v>
       </c>
       <c r="AA38">
-        <f>X38-Y38-Z38</f>
+        <f t="shared" si="5"/>
         <v>5902660.5638666665</v>
       </c>
       <c r="AB38" s="54">
-        <f>1-(Y38+Z38)/AA38</f>
+        <f t="shared" si="4"/>
         <v>0.99227832336957622</v>
       </c>
       <c r="AC38" s="34">
@@ -31429,7 +31444,7 @@
         <v>0</v>
       </c>
       <c r="AZ38">
-        <f>Y38</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -31450,10 +31465,10 @@
         <v>64</v>
       </c>
       <c r="H39" t="s">
-        <v>1628</v>
+        <v>1613</v>
       </c>
       <c r="I39" t="s">
-        <v>1664</v>
+        <v>1649</v>
       </c>
       <c r="K39" t="s">
         <v>1518</v>
@@ -31465,13 +31480,13 @@
         <v>1550354.452950391</v>
       </c>
       <c r="N39" t="s">
-        <v>1605</v>
+        <v>1590</v>
       </c>
       <c r="R39" t="s">
         <v>1205</v>
       </c>
       <c r="S39" t="s">
-        <v>1635</v>
+        <v>1620</v>
       </c>
       <c r="T39" s="22" t="s">
         <v>65</v>
@@ -31483,7 +31498,7 @@
         <v>997</v>
       </c>
       <c r="W39" t="s">
-        <v>1556</v>
+        <v>1659</v>
       </c>
       <c r="X39" s="21">
         <f>prod_table_raw!N183</f>
@@ -31495,11 +31510,11 @@
       </c>
       <c r="Z39"/>
       <c r="AA39">
-        <f>X39-Y39-Z39</f>
+        <f t="shared" si="5"/>
         <v>1027994.2871122449</v>
       </c>
       <c r="AB39" s="54">
-        <f>1-(Y39+Z39)/AA39</f>
+        <f t="shared" si="4"/>
         <v>0.9999944426853079</v>
       </c>
       <c r="AC39" s="34">
@@ -31547,7 +31562,7 @@
         <v>0</v>
       </c>
       <c r="AZ39">
-        <f>Y39</f>
+        <f t="shared" si="6"/>
         <v>5.7128877551020407</v>
       </c>
     </row>
@@ -31568,10 +31583,10 @@
         <v>64</v>
       </c>
       <c r="H40" t="s">
-        <v>1631</v>
+        <v>1616</v>
       </c>
       <c r="I40" t="s">
-        <v>1667</v>
+        <v>1652</v>
       </c>
       <c r="K40" t="s">
         <v>1517</v>
@@ -31583,7 +31598,7 @@
         <v>4950459.91493</v>
       </c>
       <c r="N40" t="s">
-        <v>1604</v>
+        <v>1589</v>
       </c>
       <c r="R40" t="s">
         <v>1205</v>
@@ -31598,10 +31613,10 @@
         <v>1205</v>
       </c>
       <c r="V40" t="s">
-        <v>1655</v>
+        <v>1640</v>
       </c>
       <c r="W40" t="s">
-        <v>1564</v>
+        <v>1671</v>
       </c>
       <c r="X40" s="21">
         <f>prod_table_raw!N189</f>
@@ -31613,11 +31628,11 @@
         <v>71667.536000000007</v>
       </c>
       <c r="AA40">
-        <f>X40-Y40-Z40</f>
+        <f t="shared" si="5"/>
         <v>2993332.4640000002</v>
       </c>
       <c r="AB40" s="54">
-        <f>1-(Y40+Z40)/AA40</f>
+        <f t="shared" si="4"/>
         <v>0.97605760908220984</v>
       </c>
       <c r="AC40" s="34">
@@ -31668,7 +31683,7 @@
         <v>0</v>
       </c>
       <c r="AZ40">
-        <f>Y40</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -31695,13 +31710,13 @@
         <v>98</v>
       </c>
       <c r="H41" t="s">
-        <v>1632</v>
+        <v>1617</v>
       </c>
       <c r="I41" t="s">
-        <v>1669</v>
+        <v>1654</v>
       </c>
       <c r="J41" t="s">
-        <v>1642</v>
+        <v>1627</v>
       </c>
       <c r="K41" t="s">
         <v>1519</v>
@@ -31728,7 +31743,7 @@
         <v>1488</v>
       </c>
       <c r="W41" t="s">
-        <v>1553</v>
+        <v>1660</v>
       </c>
       <c r="X41" s="21">
         <f>prod_table_raw!N194</f>
@@ -31740,11 +31755,11 @@
         <v>0</v>
       </c>
       <c r="AA41">
-        <f>X41-Y41-Z41</f>
+        <f t="shared" si="5"/>
         <v>320160</v>
       </c>
       <c r="AB41" s="54">
-        <f>1-(Y41+Z41)/AA41</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="AC41" s="34"/>
@@ -31786,7 +31801,7 @@
         <v>0</v>
       </c>
       <c r="AZ41">
-        <f>Y41</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -31807,16 +31822,16 @@
         <v>64</v>
       </c>
       <c r="H42" t="s">
-        <v>1632</v>
+        <v>1617</v>
       </c>
       <c r="I42" t="s">
-        <v>1619</v>
+        <v>1604</v>
       </c>
       <c r="K42" t="s">
         <v>1518</v>
       </c>
       <c r="L42" t="s">
-        <v>1617</v>
+        <v>1602</v>
       </c>
       <c r="M42">
         <v>2323252.9267690452</v>
@@ -31840,13 +31855,13 @@
         <v>309</v>
       </c>
       <c r="U42" t="s">
-        <v>1205</v>
+        <v>1658</v>
       </c>
       <c r="V42" t="s">
         <v>1487</v>
       </c>
       <c r="W42" t="s">
-        <v>1566</v>
+        <v>1668</v>
       </c>
       <c r="X42" s="21">
         <f>prod_table_raw!N195</f>
@@ -31858,11 +31873,11 @@
         <v>11325.775862068966</v>
       </c>
       <c r="AA42">
-        <f>X42-Y42-Z42</f>
+        <f t="shared" si="5"/>
         <v>2188674.2241379311</v>
       </c>
       <c r="AB42" s="54">
-        <f>1-(Y42+Z42)/AA42</f>
+        <f t="shared" si="4"/>
         <v>0.99482528019146843</v>
       </c>
       <c r="AC42" s="34"/>
@@ -31910,7 +31925,7 @@
         <v>113.25775862068966</v>
       </c>
       <c r="AZ42">
-        <f>Y42</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -31931,10 +31946,10 @@
         <v>1491</v>
       </c>
       <c r="H43" t="s">
-        <v>1632</v>
+        <v>1617</v>
       </c>
       <c r="I43" t="s">
-        <v>1620</v>
+        <v>1605</v>
       </c>
       <c r="P43" t="s">
         <v>1205</v>
@@ -31958,7 +31973,7 @@
       <c r="Y43"/>
       <c r="Z43"/>
       <c r="AA43">
-        <f>X43-Y43-Z43</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB43"/>
@@ -32001,7 +32016,7 @@
       <c r="AX43" s="34"/>
       <c r="AY43" s="34"/>
       <c r="AZ43">
-        <f>Y43</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -32022,16 +32037,16 @@
         <v>91</v>
       </c>
       <c r="H44" t="s">
-        <v>1630</v>
+        <v>1615</v>
       </c>
       <c r="I44" t="s">
-        <v>1669</v>
+        <v>1654</v>
       </c>
       <c r="K44" t="s">
         <v>1510</v>
       </c>
       <c r="L44" t="s">
-        <v>1617</v>
+        <v>1602</v>
       </c>
       <c r="O44" t="s">
         <v>1205</v>
@@ -32058,7 +32073,7 @@
         <v>1488</v>
       </c>
       <c r="W44" t="s">
-        <v>1553</v>
+        <v>1660</v>
       </c>
       <c r="X44" s="21">
         <f>prod_table_raw!N202</f>
@@ -32070,11 +32085,11 @@
         <v>363125</v>
       </c>
       <c r="AA44">
-        <f>X44-Y44-Z44</f>
+        <f t="shared" si="5"/>
         <v>6472169.1176470499</v>
       </c>
       <c r="AB44" s="54">
-        <f>1-(Y44+Z44)/AA44</f>
+        <f t="shared" ref="AB44:AB50" si="7">1-(Y44+Z44)/AA44</f>
         <v>0.94389438943894377</v>
       </c>
       <c r="AC44" s="34"/>
@@ -32122,7 +32137,7 @@
         <v>0</v>
       </c>
       <c r="AZ44">
-        <f>Y44</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -32143,16 +32158,16 @@
         <v>64</v>
       </c>
       <c r="H45" t="s">
-        <v>1630</v>
+        <v>1615</v>
       </c>
       <c r="I45" t="s">
-        <v>1669</v>
+        <v>1654</v>
       </c>
       <c r="K45" t="s">
         <v>1518</v>
       </c>
       <c r="L45" t="s">
-        <v>1617</v>
+        <v>1602</v>
       </c>
       <c r="M45">
         <v>2475749.7725005322</v>
@@ -32179,7 +32194,7 @@
         <v>1490</v>
       </c>
       <c r="W45" t="s">
-        <v>1553</v>
+        <v>1660</v>
       </c>
       <c r="X45" s="21">
         <f>prod_table_raw!N207</f>
@@ -32191,11 +32206,11 @@
         <v>151450</v>
       </c>
       <c r="AA45">
-        <f>X45-Y45-Z45</f>
+        <f t="shared" si="5"/>
         <v>1348550</v>
       </c>
       <c r="AB45" s="54">
-        <f>1-(Y45+Z45)/AA45</f>
+        <f t="shared" si="7"/>
         <v>0.88769419005598604</v>
       </c>
       <c r="AC45" s="34"/>
@@ -32249,7 +32264,7 @@
         <v>0</v>
       </c>
       <c r="AZ45">
-        <f>Y45</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -32270,10 +32285,10 @@
         <v>91</v>
       </c>
       <c r="H46" t="s">
-        <v>1632</v>
+        <v>1617</v>
       </c>
       <c r="I46" t="s">
-        <v>1664</v>
+        <v>1649</v>
       </c>
       <c r="K46" t="s">
         <v>1518</v>
@@ -32285,7 +32300,7 @@
         <v>22789723.436936211</v>
       </c>
       <c r="N46" t="s">
-        <v>1606</v>
+        <v>1591</v>
       </c>
       <c r="R46" t="s">
         <v>1205</v>
@@ -32303,7 +32318,7 @@
         <v>997</v>
       </c>
       <c r="W46" t="s">
-        <v>1556</v>
+        <v>1659</v>
       </c>
       <c r="X46" s="21">
         <f>prod_table_raw!N211</f>
@@ -32315,11 +32330,11 @@
       </c>
       <c r="Z46"/>
       <c r="AA46">
-        <f>X46-Y46-Z46</f>
+        <f t="shared" si="5"/>
         <v>8763991.9465738703</v>
       </c>
       <c r="AB46" s="54">
-        <f>1-(Y46+Z46)/AA46</f>
+        <f t="shared" si="7"/>
         <v>0.99999908107787194</v>
       </c>
       <c r="AC46" s="34">
@@ -32367,7 +32382,7 @@
         <v>0</v>
       </c>
       <c r="AZ46">
-        <f>Y46</f>
+        <f t="shared" si="6"/>
         <v>8.0534261301020305</v>
       </c>
     </row>
@@ -32388,13 +32403,13 @@
         <v>78</v>
       </c>
       <c r="H47" t="s">
-        <v>1628</v>
+        <v>1613</v>
       </c>
       <c r="I47" t="s">
-        <v>1666</v>
+        <v>1651</v>
       </c>
       <c r="J47" t="s">
-        <v>1670</v>
+        <v>1655</v>
       </c>
       <c r="K47" t="s">
         <v>1517</v>
@@ -32406,7 +32421,7 @@
         <v>11531646.543500001</v>
       </c>
       <c r="N47" t="s">
-        <v>1586</v>
+        <v>1571</v>
       </c>
       <c r="Q47" t="s">
         <v>1205</v>
@@ -32424,10 +32439,10 @@
         <v>1205</v>
       </c>
       <c r="V47" t="s">
-        <v>1663</v>
+        <v>1648</v>
       </c>
       <c r="W47" t="s">
-        <v>1564</v>
+        <v>1671</v>
       </c>
       <c r="X47" s="21">
         <f>prod_table_raw!N215</f>
@@ -32442,11 +32457,11 @@
         <v>13333.333333333334</v>
       </c>
       <c r="AA47">
-        <f>X47-Y47-Z47</f>
+        <f t="shared" si="5"/>
         <v>1125666.5079753401</v>
       </c>
       <c r="AB47" s="54">
-        <f>1-(Y47+Z47)/AA47</f>
+        <f t="shared" si="7"/>
         <v>0.98815502466299554</v>
       </c>
       <c r="AC47" s="34">
@@ -32497,7 +32512,7 @@
         <v>0</v>
       </c>
       <c r="AZ47">
-        <f>Y47</f>
+        <f t="shared" si="6"/>
         <v>0.15869132653061224</v>
       </c>
     </row>
@@ -32518,10 +32533,10 @@
         <v>64</v>
       </c>
       <c r="H48" t="s">
-        <v>1632</v>
+        <v>1617</v>
       </c>
       <c r="I48" t="s">
-        <v>1665</v>
+        <v>1650</v>
       </c>
       <c r="J48" t="s">
         <v>1492</v>
@@ -32530,13 +32545,16 @@
         <v>1518</v>
       </c>
       <c r="L48" t="s">
-        <v>1508</v>
+        <v>1609</v>
       </c>
       <c r="M48">
         <v>6139378.4953300003</v>
       </c>
       <c r="N48" t="s">
-        <v>1591</v>
+        <v>1576</v>
+      </c>
+      <c r="O48" t="s">
+        <v>1205</v>
       </c>
       <c r="Q48" t="s">
         <v>1205</v>
@@ -32557,7 +32575,7 @@
         <v>997</v>
       </c>
       <c r="W48" t="s">
-        <v>1556</v>
+        <v>1659</v>
       </c>
       <c r="X48" s="21">
         <f>prod_table_raw!N222</f>
@@ -32569,11 +32587,11 @@
       </c>
       <c r="Z48"/>
       <c r="AA48">
-        <f>X48-Y48-Z48</f>
+        <f t="shared" si="5"/>
         <v>840996.4230975</v>
       </c>
       <c r="AB48" s="54">
-        <f>1-(Y48+Z48)/AA48</f>
+        <f t="shared" si="7"/>
         <v>0.99999574682792725</v>
       </c>
       <c r="AC48" s="34">
@@ -32621,7 +32639,7 @@
         <v>0</v>
       </c>
       <c r="AZ48">
-        <f>Y48</f>
+        <f t="shared" si="6"/>
         <v>3.5769025000000001</v>
       </c>
     </row>
@@ -32642,7 +32660,7 @@
         <v>78</v>
       </c>
       <c r="H49" t="s">
-        <v>1628</v>
+        <v>1613</v>
       </c>
       <c r="I49" t="s">
         <v>1499</v>
@@ -32669,13 +32687,13 @@
         <v>49</v>
       </c>
       <c r="U49" t="s">
-        <v>1651</v>
+        <v>1636</v>
       </c>
       <c r="V49" t="s">
         <v>1160</v>
       </c>
       <c r="W49" t="s">
-        <v>1565</v>
+        <v>1664</v>
       </c>
       <c r="X49" s="21">
         <f>prod_table_raw!N226</f>
@@ -32684,11 +32702,11 @@
       <c r="Y49"/>
       <c r="Z49"/>
       <c r="AA49">
-        <f>X49-Y49-Z49</f>
+        <f t="shared" si="5"/>
         <v>3560000</v>
       </c>
       <c r="AB49" s="54">
-        <f>1-(Y49+Z49)/AA49</f>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="AC49" s="34"/>
@@ -32733,7 +32751,7 @@
         <v>0</v>
       </c>
       <c r="AZ49">
-        <f>Y49</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -32760,19 +32778,19 @@
         <v>264</v>
       </c>
       <c r="H50" t="s">
-        <v>1632</v>
+        <v>1617</v>
       </c>
       <c r="I50" t="s">
-        <v>1669</v>
+        <v>1654</v>
       </c>
       <c r="J50" t="s">
-        <v>1662</v>
+        <v>1647</v>
       </c>
       <c r="K50" t="s">
         <v>1518</v>
       </c>
       <c r="L50" t="s">
-        <v>1617</v>
+        <v>1602</v>
       </c>
       <c r="M50">
         <v>1039802.195699128</v>
@@ -32796,7 +32814,7 @@
         <v>1488</v>
       </c>
       <c r="W50" t="s">
-        <v>1553</v>
+        <v>1660</v>
       </c>
       <c r="X50" s="21">
         <f>prod_table_raw!N239</f>
@@ -32808,11 +32826,11 @@
         <v>47062.5</v>
       </c>
       <c r="AA50">
-        <f>X50-Y50-Z50</f>
+        <f t="shared" si="5"/>
         <v>978934.5</v>
       </c>
       <c r="AB50" s="54">
-        <f>1-(Y50+Z50)/AA50</f>
+        <f t="shared" si="7"/>
         <v>0.95192477126917074</v>
       </c>
       <c r="AC50" s="34"/>
@@ -32860,7 +32878,7 @@
         <v>0</v>
       </c>
       <c r="AZ50">
-        <f>Y50</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -32887,7 +32905,7 @@
         <v>378</v>
       </c>
       <c r="H51" t="s">
-        <v>1632</v>
+        <v>1617</v>
       </c>
       <c r="I51" t="s">
         <v>1252</v>
@@ -32896,7 +32914,7 @@
         <v>1510</v>
       </c>
       <c r="L51" t="s">
-        <v>1617</v>
+        <v>1602</v>
       </c>
       <c r="O51" t="s">
         <v>1205</v>
@@ -32914,19 +32932,19 @@
         <v>379</v>
       </c>
       <c r="U51" t="s">
-        <v>1646</v>
+        <v>1631</v>
       </c>
       <c r="V51" t="s">
         <v>1488</v>
       </c>
       <c r="W51" t="s">
-        <v>1647</v>
+        <v>1632</v>
       </c>
       <c r="X51" s="21"/>
       <c r="Y51"/>
       <c r="Z51"/>
       <c r="AA51">
-        <f>X51-Y51-Z51</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB51"/>
@@ -32966,7 +32984,7 @@
       <c r="AX51" s="34"/>
       <c r="AY51" s="34"/>
       <c r="AZ51">
-        <f>Y51</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -32987,13 +33005,13 @@
         <v>64</v>
       </c>
       <c r="H52" t="s">
-        <v>1632</v>
+        <v>1617</v>
       </c>
       <c r="I52" t="s">
-        <v>1664</v>
+        <v>1649</v>
       </c>
       <c r="N52" t="s">
-        <v>1588</v>
+        <v>1573</v>
       </c>
       <c r="P52" t="s">
         <v>1205</v>
@@ -33011,13 +33029,13 @@
         <v>115</v>
       </c>
       <c r="U52" t="s">
-        <v>1610</v>
+        <v>1595</v>
       </c>
       <c r="V52" t="s">
         <v>997</v>
       </c>
       <c r="W52" t="s">
-        <v>1556</v>
+        <v>1659</v>
       </c>
       <c r="X52" s="21">
         <f>prod_table_raw!N244</f>
@@ -33029,7 +33047,7 @@
       </c>
       <c r="Z52"/>
       <c r="AA52">
-        <f>X52-Y52-Z52</f>
+        <f t="shared" si="5"/>
         <v>234669.77303040153</v>
       </c>
       <c r="AB52" s="54">
@@ -33081,7 +33099,7 @@
         <v>0</v>
       </c>
       <c r="AZ52">
-        <f>Y52</f>
+        <f t="shared" si="6"/>
         <v>1.2269695984693878</v>
       </c>
     </row>
@@ -33102,7 +33120,7 @@
         <v>71</v>
       </c>
       <c r="H53" t="s">
-        <v>1628</v>
+        <v>1613</v>
       </c>
       <c r="I53" t="s">
         <v>1253</v>
@@ -33111,7 +33129,7 @@
         <v>1510</v>
       </c>
       <c r="L53" t="s">
-        <v>1617</v>
+        <v>1602</v>
       </c>
       <c r="O53" t="s">
         <v>1205</v>
@@ -33129,19 +33147,19 @@
         <v>391</v>
       </c>
       <c r="U53" t="s">
-        <v>1646</v>
+        <v>1631</v>
       </c>
       <c r="V53" t="s">
         <v>1489</v>
       </c>
       <c r="W53" t="s">
-        <v>1649</v>
+        <v>1634</v>
       </c>
       <c r="X53" s="21"/>
       <c r="Y53"/>
       <c r="Z53"/>
       <c r="AA53">
-        <f>X53-Y53-Z53</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB53"/>
@@ -33178,7 +33196,7 @@
       <c r="AX53" s="34"/>
       <c r="AY53" s="34"/>
       <c r="AZ53">
-        <f>Y53</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -33199,16 +33217,16 @@
         <v>91</v>
       </c>
       <c r="H54" t="s">
-        <v>1628</v>
+        <v>1613</v>
       </c>
       <c r="I54" t="s">
-        <v>1669</v>
+        <v>1654</v>
       </c>
       <c r="K54" t="s">
         <v>1518</v>
       </c>
       <c r="L54" t="s">
-        <v>1617</v>
+        <v>1602</v>
       </c>
       <c r="O54" t="s">
         <v>1205</v>
@@ -33235,7 +33253,7 @@
         <v>1488</v>
       </c>
       <c r="W54" t="s">
-        <v>1553</v>
+        <v>1660</v>
       </c>
       <c r="X54" s="21">
         <f>prod_table_raw!N250</f>
@@ -33247,7 +33265,7 @@
         <v>49375</v>
       </c>
       <c r="AA54">
-        <f>X54-Y54-Z54</f>
+        <f t="shared" si="5"/>
         <v>415330.88235294097</v>
       </c>
       <c r="AB54" s="54">
@@ -33299,7 +33317,7 @@
         <v>0</v>
       </c>
       <c r="AZ54">
-        <f>Y54</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -33326,13 +33344,13 @@
         <v>98</v>
       </c>
       <c r="H55" t="s">
-        <v>1632</v>
+        <v>1617</v>
       </c>
       <c r="I55" t="s">
-        <v>1669</v>
+        <v>1654</v>
       </c>
       <c r="J55" t="s">
-        <v>1642</v>
+        <v>1627</v>
       </c>
       <c r="K55" t="s">
         <v>1513</v>
@@ -33341,7 +33359,7 @@
         <v>559241.26414497849</v>
       </c>
       <c r="N55" t="s">
-        <v>1608</v>
+        <v>1593</v>
       </c>
       <c r="Q55" t="s">
         <v>1205</v>
@@ -33356,13 +33374,13 @@
         <v>406</v>
       </c>
       <c r="U55" t="s">
-        <v>1661</v>
+        <v>1646</v>
       </c>
       <c r="V55" t="s">
         <v>1488</v>
       </c>
       <c r="W55" t="s">
-        <v>1553</v>
+        <v>1660</v>
       </c>
       <c r="X55" s="21">
         <f>prod_table_raw!N259</f>
@@ -33374,7 +33392,7 @@
         <v>39587.5</v>
       </c>
       <c r="AA55">
-        <f>X55-Y55-Z55</f>
+        <f t="shared" si="5"/>
         <v>374412.5</v>
       </c>
       <c r="AB55" s="54">
@@ -33426,7 +33444,7 @@
         <v>0</v>
       </c>
       <c r="AZ55">
-        <f>Y55</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -33447,7 +33465,7 @@
         <v>71</v>
       </c>
       <c r="H56" t="s">
-        <v>1629</v>
+        <v>1614</v>
       </c>
       <c r="I56" t="s">
         <v>1507</v>
@@ -33456,7 +33474,7 @@
         <v>1511</v>
       </c>
       <c r="L56" t="s">
-        <v>1617</v>
+        <v>1602</v>
       </c>
       <c r="O56" t="s">
         <v>1205</v>
@@ -33483,7 +33501,7 @@
       <c r="Y56"/>
       <c r="Z56"/>
       <c r="AA56">
-        <f>X56-Y56-Z56</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AB56"/>
@@ -33520,7 +33538,7 @@
       <c r="AX56" s="34"/>
       <c r="AY56" s="34"/>
       <c r="AZ56">
-        <f>Y56</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -33541,16 +33559,16 @@
         <v>91</v>
       </c>
       <c r="H57" t="s">
-        <v>1628</v>
+        <v>1613</v>
       </c>
       <c r="I57" t="s">
-        <v>1669</v>
+        <v>1654</v>
       </c>
       <c r="K57" t="s">
         <v>1518</v>
       </c>
       <c r="L57" t="s">
-        <v>1617</v>
+        <v>1602</v>
       </c>
       <c r="O57" t="s">
         <v>1205</v>
@@ -33577,7 +33595,7 @@
         <v>1488</v>
       </c>
       <c r="W57" t="s">
-        <v>1553</v>
+        <v>1660</v>
       </c>
       <c r="X57" s="21">
         <f>prod_table_raw!N268</f>
@@ -33589,11 +33607,11 @@
         <v>84375</v>
       </c>
       <c r="AA57">
-        <f>X57-Y57-Z57</f>
+        <f t="shared" si="5"/>
         <v>709742.64705882303</v>
       </c>
       <c r="AB57" s="54">
-        <f>1-(Y57+Z57)/AA57</f>
+        <f t="shared" ref="AB57:AB66" si="8">1-(Y57+Z57)/AA57</f>
         <v>0.88111888111888104</v>
       </c>
       <c r="AC57" s="34"/>
@@ -33641,7 +33659,7 @@
         <v>0</v>
       </c>
       <c r="AZ57">
-        <f>Y57</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -33662,10 +33680,10 @@
         <v>64</v>
       </c>
       <c r="H58" t="s">
-        <v>1632</v>
+        <v>1617</v>
       </c>
       <c r="I58" t="s">
-        <v>1664</v>
+        <v>1649</v>
       </c>
       <c r="K58" t="s">
         <v>1520</v>
@@ -33677,7 +33695,7 @@
         <v>7249147.17667</v>
       </c>
       <c r="N58" t="s">
-        <v>1609</v>
+        <v>1594</v>
       </c>
       <c r="R58" t="s">
         <v>1205</v>
@@ -33689,13 +33707,13 @@
         <v>65</v>
       </c>
       <c r="U58" t="s">
-        <v>1611</v>
+        <v>1596</v>
       </c>
       <c r="V58" t="s">
         <v>1167</v>
       </c>
       <c r="W58" t="s">
-        <v>1556</v>
+        <v>1659</v>
       </c>
       <c r="X58" s="21">
         <f>prod_table_raw!N271</f>
@@ -33707,11 +33725,11 @@
       </c>
       <c r="Z58"/>
       <c r="AA58">
-        <f>X58-Y58-Z58</f>
+        <f t="shared" si="5"/>
         <v>1033995.8818331235</v>
       </c>
       <c r="AB58" s="54">
-        <f>1-(Y58+Z58)/AA58</f>
+        <f t="shared" si="8"/>
         <v>0.99999601723087206</v>
       </c>
       <c r="AC58" s="34">
@@ -33762,7 +33780,7 @@
         <v>0</v>
       </c>
       <c r="AZ58">
-        <f>Y58</f>
+        <f t="shared" si="6"/>
         <v>4.1181668765306121</v>
       </c>
     </row>
@@ -33783,22 +33801,22 @@
         <v>64</v>
       </c>
       <c r="H59" t="s">
-        <v>1632</v>
+        <v>1617</v>
       </c>
       <c r="I59" t="s">
-        <v>1664</v>
+        <v>1649</v>
       </c>
       <c r="K59" t="s">
         <v>1518</v>
       </c>
       <c r="L59" t="s">
-        <v>1616</v>
+        <v>1601</v>
       </c>
       <c r="M59">
         <v>1874190.45757726</v>
       </c>
       <c r="N59" t="s">
-        <v>1609</v>
+        <v>1594</v>
       </c>
       <c r="R59" t="s">
         <v>1205</v>
@@ -33816,7 +33834,7 @@
         <v>997</v>
       </c>
       <c r="W59" t="s">
-        <v>1556</v>
+        <v>1659</v>
       </c>
       <c r="X59" s="21">
         <f>prod_table_raw!N277</f>
@@ -33828,11 +33846,11 @@
       </c>
       <c r="Z59"/>
       <c r="AA59">
-        <f>X59-Y59-Z59</f>
+        <f t="shared" si="5"/>
         <v>2878041.125247092</v>
       </c>
       <c r="AB59" s="54">
-        <f>1-(Y59+Z59)/AA59</f>
+        <f t="shared" si="8"/>
         <v>0.99999795876686526</v>
       </c>
       <c r="AC59" s="34">
@@ -33880,17 +33898,17 @@
         <v>0</v>
       </c>
       <c r="AZ59">
-        <f>Y59</f>
+        <f t="shared" si="6"/>
         <v>5.8747529081632548</v>
       </c>
     </row>
     <row r="60" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A60" s="21"/>
       <c r="B60" t="s">
-        <v>1654</v>
+        <v>1639</v>
       </c>
       <c r="D60" t="s">
-        <v>1652</v>
+        <v>1637</v>
       </c>
       <c r="E60" t="s">
         <v>453</v>
@@ -33902,16 +33920,16 @@
         <v>64</v>
       </c>
       <c r="H60" t="s">
-        <v>1628</v>
+        <v>1613</v>
       </c>
       <c r="I60" t="s">
-        <v>1653</v>
+        <v>1638</v>
       </c>
       <c r="K60" t="s">
         <v>1518</v>
       </c>
       <c r="L60" t="s">
-        <v>1617</v>
+        <v>1602</v>
       </c>
       <c r="M60">
         <v>1600590.119251437</v>
@@ -33938,7 +33956,7 @@
         <v>1163</v>
       </c>
       <c r="W60" t="s">
-        <v>1671</v>
+        <v>1656</v>
       </c>
       <c r="X60" s="21">
         <f>prod_table_raw!N154</f>
@@ -33947,11 +33965,11 @@
       <c r="Y60"/>
       <c r="Z60"/>
       <c r="AA60">
-        <f>X60-Y60-Z60</f>
+        <f t="shared" si="5"/>
         <v>43726.856187782003</v>
       </c>
       <c r="AB60" s="54">
-        <f>1-(Y60+Z60)/AA60</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AC60" s="34"/>
@@ -34002,7 +34020,7 @@
         <v>0</v>
       </c>
       <c r="AZ60">
-        <f>Y60</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -34024,16 +34042,16 @@
         <v>64</v>
       </c>
       <c r="H61" t="s">
-        <v>1628</v>
+        <v>1613</v>
       </c>
       <c r="I61" t="s">
-        <v>1653</v>
+        <v>1638</v>
       </c>
       <c r="K61" t="s">
         <v>1510</v>
       </c>
       <c r="L61" t="s">
-        <v>1617</v>
+        <v>1602</v>
       </c>
       <c r="M61">
         <v>10235647.18904726</v>
@@ -34060,7 +34078,7 @@
         <v>1163</v>
       </c>
       <c r="W61" t="s">
-        <v>1671</v>
+        <v>1656</v>
       </c>
       <c r="X61" s="21">
         <f>prod_table_raw!N153</f>
@@ -34069,11 +34087,11 @@
       <c r="Y61"/>
       <c r="Z61"/>
       <c r="AA61">
-        <f>X61-Y61-Z61</f>
+        <f t="shared" si="5"/>
         <v>98408.871032543204</v>
       </c>
       <c r="AB61" s="54">
-        <f>1-(Y61+Z61)/AA61</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="AC61" s="34"/>
@@ -34124,7 +34142,7 @@
         <v>0</v>
       </c>
       <c r="AZ61">
-        <f>Y61</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
@@ -34146,7 +34164,7 @@
         <v>324</v>
       </c>
       <c r="I62" t="s">
-        <v>1664</v>
+        <v>1649</v>
       </c>
       <c r="K62" t="s">
         <v>1518</v>
@@ -34164,7 +34182,7 @@
         <v>1205</v>
       </c>
       <c r="S62" t="s">
-        <v>1635</v>
+        <v>1620</v>
       </c>
       <c r="T62" s="22" t="s">
         <v>115</v>
@@ -34176,7 +34194,7 @@
         <v>1167</v>
       </c>
       <c r="W62" t="s">
-        <v>1556</v>
+        <v>1659</v>
       </c>
       <c r="X62" s="21">
         <f>prod_table_raw!N160</f>
@@ -34188,11 +34206,11 @@
       </c>
       <c r="Z62"/>
       <c r="AA62">
-        <f>X62-Y62-Z62</f>
+        <f t="shared" si="5"/>
         <v>3842631.3381266426</v>
       </c>
       <c r="AB62" s="54">
-        <f>1-(Y62+Z62)/AA62</f>
+        <f t="shared" si="8"/>
         <v>0.99999540221275407</v>
       </c>
       <c r="AC62" s="34">
@@ -34243,7 +34261,7 @@
         <v>0</v>
       </c>
       <c r="AZ62">
-        <f>Y62</f>
+        <f t="shared" si="6"/>
         <v>17.66760135719143</v>
       </c>
     </row>
@@ -34265,7 +34283,7 @@
         <v>324</v>
       </c>
       <c r="I63" t="s">
-        <v>1664</v>
+        <v>1649</v>
       </c>
       <c r="K63" t="s">
         <v>1518</v>
@@ -34280,7 +34298,7 @@
         <v>1205</v>
       </c>
       <c r="S63" t="s">
-        <v>1635</v>
+        <v>1620</v>
       </c>
       <c r="T63" s="22" t="s">
         <v>115</v>
@@ -34292,7 +34310,7 @@
         <v>997</v>
       </c>
       <c r="W63" t="s">
-        <v>1556</v>
+        <v>1659</v>
       </c>
       <c r="X63" s="21">
         <f>prod_table_raw!N101</f>
@@ -34304,11 +34322,11 @@
       </c>
       <c r="Z63"/>
       <c r="AA63">
-        <f>X63-Y63-Z63</f>
+        <f t="shared" si="5"/>
         <v>2910991.7480510203</v>
       </c>
       <c r="AB63" s="54">
-        <f>1-(Y63+Z63)/AA63</f>
+        <f t="shared" si="8"/>
         <v>0.99999716524480531</v>
       </c>
       <c r="AC63" s="34">
@@ -34356,7 +34374,7 @@
         <v>0</v>
       </c>
       <c r="AZ63">
-        <f>Y63</f>
+        <f t="shared" si="6"/>
         <v>8.2519489795918357</v>
       </c>
     </row>
@@ -34378,17 +34396,20 @@
         <v>64</v>
       </c>
       <c r="I64" t="s">
-        <v>1664</v>
+        <v>1649</v>
       </c>
       <c r="K64" t="s">
         <v>1518</v>
       </c>
       <c r="L64" t="s">
-        <v>1624</v>
+        <v>1609</v>
       </c>
       <c r="M64">
         <v>1464485.5013698239</v>
       </c>
+      <c r="O64" t="s">
+        <v>1205</v>
+      </c>
       <c r="Q64" t="s">
         <v>1205</v>
       </c>
@@ -34408,7 +34429,7 @@
         <v>997</v>
       </c>
       <c r="W64" t="s">
-        <v>1556</v>
+        <v>1659</v>
       </c>
       <c r="X64" s="21">
         <f>prod_table_raw!N254</f>
@@ -34420,11 +34441,11 @@
       </c>
       <c r="Z64"/>
       <c r="AA64">
-        <f>X64-Y64-Z64</f>
+        <f t="shared" si="5"/>
         <v>1573995.7819845409</v>
       </c>
       <c r="AB64" s="54">
-        <f>1-(Y64+Z64)/AA64</f>
+        <f t="shared" si="8"/>
         <v>0.99999732018630072</v>
       </c>
       <c r="AC64" s="34">
@@ -34472,7 +34493,7 @@
         <v>0</v>
       </c>
       <c r="AZ64">
-        <f>Y64</f>
+        <f t="shared" si="6"/>
         <v>4.2180154591836736</v>
       </c>
     </row>
@@ -34494,19 +34515,22 @@
         <v>64</v>
       </c>
       <c r="I65" t="s">
-        <v>1664</v>
+        <v>1649</v>
       </c>
       <c r="K65" t="s">
         <v>1518</v>
       </c>
       <c r="L65" t="s">
-        <v>1624</v>
+        <v>1609</v>
       </c>
       <c r="M65">
         <v>517003.99124031531</v>
       </c>
       <c r="N65" t="s">
-        <v>1586</v>
+        <v>1571</v>
+      </c>
+      <c r="O65" t="s">
+        <v>1205</v>
       </c>
       <c r="Q65" t="s">
         <v>1205</v>
@@ -34527,7 +34551,7 @@
         <v>997</v>
       </c>
       <c r="W65" t="s">
-        <v>1556</v>
+        <v>1659</v>
       </c>
       <c r="X65" s="21">
         <f>prod_table_raw!N229</f>
@@ -34539,11 +34563,11 @@
       </c>
       <c r="Z65"/>
       <c r="AA65">
-        <f>X65-Y65-Z65</f>
+        <f t="shared" si="5"/>
         <v>121998.76992005153</v>
       </c>
       <c r="AB65" s="54">
-        <f>1-(Y65+Z65)/AA65</f>
+        <f t="shared" si="8"/>
         <v>0.99998991727581121</v>
       </c>
       <c r="AC65" s="34">
@@ -34591,7 +34615,7 @@
         <v>0</v>
       </c>
       <c r="AZ65">
-        <f>Y65</f>
+        <f t="shared" si="6"/>
         <v>1.2300799484693878</v>
       </c>
     </row>
@@ -34614,24 +34638,26 @@
         <v>64</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>1666</v>
+        <v>1651</v>
       </c>
       <c r="J66" t="s">
-        <v>1645</v>
+        <v>1630</v>
       </c>
       <c r="K66" s="24" t="s">
         <v>1519</v>
       </c>
       <c r="L66" t="s">
-        <v>1624</v>
+        <v>1609</v>
       </c>
       <c r="M66">
         <v>3104130.8525155862</v>
       </c>
       <c r="N66" s="24" t="s">
-        <v>1607</v>
-      </c>
-      <c r="O66" s="24"/>
+        <v>1592</v>
+      </c>
+      <c r="O66" t="s">
+        <v>1205</v>
+      </c>
       <c r="P66" s="24"/>
       <c r="Q66" t="s">
         <v>1205</v>
@@ -34646,13 +34672,13 @@
         <v>225</v>
       </c>
       <c r="U66" t="s">
-        <v>1644</v>
+        <v>1629</v>
       </c>
       <c r="V66" t="s">
-        <v>1658</v>
+        <v>1643</v>
       </c>
       <c r="W66" t="s">
-        <v>1559</v>
+        <v>1663</v>
       </c>
       <c r="X66" s="23">
         <f>prod_table_raw!N193+prod_table_raw!N130</f>
@@ -34667,11 +34693,11 @@
         <v>109797.33333333334</v>
       </c>
       <c r="AA66">
-        <f>X66-Y66-Z66</f>
+        <f t="shared" ref="AA66" si="9">X66-Y66-Z66</f>
         <v>2013810.687879523</v>
       </c>
       <c r="AB66" s="54">
-        <f>1-(Y66+Z66)/AA66</f>
+        <f t="shared" si="8"/>
         <v>0.94546145137598558</v>
       </c>
       <c r="AC66" s="55">
@@ -34728,16 +34754,12 @@
         <v>0</v>
       </c>
       <c r="AZ66">
-        <f>Y66</f>
+        <f t="shared" si="6"/>
         <v>32.978787143877547</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AZ66" xr:uid="{19A21E0B-06A8-4909-8999-69A6CC63874F}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AZ66">
-      <sortCondition ref="C1:C66"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:AZ66" xr:uid="{19A21E0B-06A8-4909-8999-69A6CC63874F}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -42011,13 +42033,13 @@
         <v>95</v>
       </c>
       <c r="E154" t="s">
-        <v>1654</v>
+        <v>1639</v>
       </c>
       <c r="F154" t="s">
         <v>97</v>
       </c>
       <c r="G154" t="s">
-        <v>1652</v>
+        <v>1637</v>
       </c>
       <c r="H154" t="s">
         <v>92</v>
@@ -42064,13 +42086,13 @@
         <v>261</v>
       </c>
       <c r="E155" t="s">
-        <v>1654</v>
+        <v>1639</v>
       </c>
       <c r="F155" t="s">
         <v>263</v>
       </c>
       <c r="G155" t="s">
-        <v>1652</v>
+        <v>1637</v>
       </c>
       <c r="H155" t="s">
         <v>92</v>
@@ -42117,13 +42139,13 @@
         <v>261</v>
       </c>
       <c r="E156" t="s">
-        <v>1654</v>
+        <v>1639</v>
       </c>
       <c r="F156" t="s">
         <v>263</v>
       </c>
       <c r="G156" t="s">
-        <v>1652</v>
+        <v>1637</v>
       </c>
       <c r="H156" t="s">
         <v>92</v>

--- a/data/MetalliCan/sites_for_lci.xlsx
+++ b/data/MetalliCan/sites_for_lci.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/regionalized_lci_mineral/data/MetalliCan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2961" documentId="13_ncr:1_{965BE886-D2C4-44D2-937F-E901E74C4ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E197436-D085-44A6-842A-AEDCFBD749A5}"/>
+  <xr:revisionPtr revIDLastSave="2964" documentId="13_ncr:1_{965BE886-D2C4-44D2-937F-E901E74C4ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4356C535-E0C5-4AF5-91ED-8686BD5CEE1B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{9D292A65-B8C8-46CC-8162-88CB3EA3ABC7}"/>
   </bookViews>
@@ -26779,6 +26779,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A21E0B-06A8-4909-8999-69A6CC63874F}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AZ66"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -26987,7 +26988,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="2" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
         <v>53</v>
       </c>
@@ -27107,7 +27108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
         <v>60</v>
       </c>
@@ -27231,7 +27232,7 @@
         <v>0.92040969387755101</v>
       </c>
     </row>
-    <row r="4" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
         <v>68</v>
       </c>
@@ -27325,7 +27326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="21" t="s">
         <v>74</v>
       </c>
@@ -27452,7 +27453,7 @@
         <v>29.039084533163262</v>
       </c>
     </row>
-    <row r="6" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="21" t="s">
         <v>82</v>
       </c>
@@ -27564,7 +27565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="21" t="s">
         <v>88</v>
       </c>
@@ -27682,7 +27683,7 @@
         <v>3.5165997959183577</v>
       </c>
     </row>
-    <row r="8" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="21" t="s">
         <v>524</v>
       </c>
@@ -27806,7 +27807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="21" t="s">
         <v>526</v>
       </c>
@@ -27912,7 +27913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="21" t="s">
         <v>109</v>
       </c>
@@ -28042,7 +28043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="21" t="s">
         <v>527</v>
       </c>
@@ -28169,7 +28170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="21" t="s">
         <v>116</v>
       </c>
@@ -28293,7 +28294,7 @@
         <v>24.008283837755101</v>
       </c>
     </row>
-    <row r="13" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="21" t="s">
         <v>125</v>
       </c>
@@ -28411,7 +28412,7 @@
         <v>2.7760508515306124</v>
       </c>
     </row>
-    <row r="14" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="21" t="s">
         <v>135</v>
       </c>
@@ -28532,7 +28533,7 @@
         <v>7.7388999209183664</v>
       </c>
     </row>
-    <row r="15" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="21" t="s">
         <v>139</v>
       </c>
@@ -28653,7 +28654,7 @@
         <v>0.12428704693877551</v>
       </c>
     </row>
-    <row r="16" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="21" t="s">
         <v>156</v>
       </c>
@@ -28774,7 +28775,7 @@
         <v>1.4536125510204081</v>
       </c>
     </row>
-    <row r="17" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="21" t="s">
         <v>161</v>
       </c>
@@ -28892,7 +28893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="21" t="s">
         <v>529</v>
       </c>
@@ -29019,7 +29020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="21" t="s">
         <v>167</v>
       </c>
@@ -29143,7 +29144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="21" t="s">
         <v>173</v>
       </c>
@@ -29270,7 +29271,7 @@
         <v>4.4745421183166938</v>
       </c>
     </row>
-    <row r="21" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="21" t="s">
         <v>180</v>
       </c>
@@ -29394,7 +29395,7 @@
         <v>4.476523630102041</v>
       </c>
     </row>
-    <row r="22" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="21" t="s">
         <v>186</v>
       </c>
@@ -29521,7 +29522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="21" t="s">
         <v>494</v>
       </c>
@@ -29624,7 +29625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="21" t="s">
         <v>195</v>
       </c>
@@ -29742,7 +29743,7 @@
         <v>4.1704080612244905</v>
       </c>
     </row>
-    <row r="25" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="21" t="s">
         <v>200</v>
       </c>
@@ -29863,7 +29864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="21" t="s">
         <v>205</v>
       </c>
@@ -29987,7 +29988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="21" t="s">
         <v>209</v>
       </c>
@@ -30105,7 +30106,7 @@
         <v>1.2201776096938775</v>
       </c>
     </row>
-    <row r="28" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="21" t="s">
         <v>215</v>
       </c>
@@ -30232,7 +30233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:52" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="21" t="s">
         <v>227</v>
       </c>
@@ -30356,7 +30357,7 @@
         <v>7.932820721938775</v>
       </c>
     </row>
-    <row r="30" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="21" t="s">
         <v>232</v>
       </c>
@@ -30492,7 +30493,7 @@
         <v>9.8029027903061134</v>
       </c>
     </row>
-    <row r="31" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="21" t="s">
         <v>534</v>
       </c>
@@ -30595,7 +30596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="21" t="s">
         <v>239</v>
       </c>
@@ -30722,7 +30723,7 @@
         <v>7.253304461734694</v>
       </c>
     </row>
-    <row r="33" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="21" t="s">
         <v>243</v>
       </c>
@@ -30840,7 +30841,7 @@
         <v>1.0473627551020408</v>
       </c>
     </row>
-    <row r="34" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="21" t="s">
         <v>249</v>
       </c>
@@ -30958,7 +30959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="21" t="s">
         <v>267</v>
       </c>
@@ -31073,7 +31074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="21" t="s">
         <v>277</v>
       </c>
@@ -31197,7 +31198,7 @@
         <v>12.41413683010194</v>
       </c>
     </row>
-    <row r="37" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="21" t="s">
         <v>283</v>
       </c>
@@ -31321,7 +31322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="21" t="s">
         <v>288</v>
       </c>
@@ -31448,7 +31449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
         <v>294</v>
       </c>
@@ -31566,7 +31567,7 @@
         <v>5.7128877551020407</v>
       </c>
     </row>
-    <row r="40" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="21" t="s">
         <v>297</v>
       </c>
@@ -31687,7 +31688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="21" t="s">
         <v>305</v>
       </c>
@@ -31805,7 +31806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="21" t="s">
         <v>311</v>
       </c>
@@ -31929,7 +31930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="21" t="s">
         <v>316</v>
       </c>
@@ -32020,7 +32021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="21" t="s">
         <v>328</v>
       </c>
@@ -32141,7 +32142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="21" t="s">
         <v>333</v>
       </c>
@@ -32268,7 +32269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="21" t="s">
         <v>337</v>
       </c>
@@ -32386,7 +32387,7 @@
         <v>8.0534261301020305</v>
       </c>
     </row>
-    <row r="47" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="21" t="s">
         <v>340</v>
       </c>
@@ -32516,7 +32517,7 @@
         <v>0.15869132653061224</v>
       </c>
     </row>
-    <row r="48" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="21" t="s">
         <v>343</v>
       </c>
@@ -32643,7 +32644,7 @@
         <v>3.5769025000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="21" t="s">
         <v>357</v>
       </c>
@@ -32755,7 +32756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="21" t="s">
         <v>371</v>
       </c>
@@ -32882,7 +32883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="21" t="s">
         <v>376</v>
       </c>
@@ -32988,7 +32989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="21" t="s">
         <v>381</v>
       </c>
@@ -33103,7 +33104,7 @@
         <v>1.2269695984693878</v>
       </c>
     </row>
-    <row r="53" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="21" t="s">
         <v>387</v>
       </c>
@@ -33200,7 +33201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="21" t="s">
         <v>393</v>
       </c>
@@ -33321,7 +33322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="21" t="s">
         <v>533</v>
       </c>
@@ -33448,7 +33449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="21" t="s">
         <v>409</v>
       </c>
@@ -33542,7 +33543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="21" t="s">
         <v>419</v>
       </c>
@@ -33663,7 +33664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="21" t="s">
         <v>423</v>
       </c>
@@ -33784,7 +33785,7 @@
         <v>4.1181668765306121</v>
       </c>
     </row>
-    <row r="59" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="21" t="s">
         <v>428</v>
       </c>
@@ -33963,14 +33964,17 @@
         <v>43726.856187782003</v>
       </c>
       <c r="Y60"/>
-      <c r="Z60"/>
+      <c r="Z60" s="34">
+        <f>AX60</f>
+        <v>10205.82</v>
+      </c>
       <c r="AA60">
         <f t="shared" si="5"/>
-        <v>43726.856187782003</v>
+        <v>33521.036187782003</v>
       </c>
       <c r="AB60" s="54">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0.69553984122603307</v>
       </c>
       <c r="AC60" s="34"/>
       <c r="AD60" s="34"/>
@@ -34085,14 +34089,17 @@
         <v>98408.871032543204</v>
       </c>
       <c r="Y61"/>
-      <c r="Z61"/>
+      <c r="Z61" s="34">
+        <f>AX61</f>
+        <v>7654.3649999999998</v>
+      </c>
       <c r="AA61">
         <f t="shared" si="5"/>
-        <v>98408.871032543204</v>
+        <v>90754.506032543199</v>
       </c>
       <c r="AB61" s="54">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>0.91565856799159639</v>
       </c>
       <c r="AC61" s="34"/>
       <c r="AD61" s="34"/>
@@ -34146,7 +34153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="21"/>
       <c r="B62" t="s">
         <v>273</v>
@@ -34265,7 +34272,7 @@
         <v>17.66760135719143</v>
       </c>
     </row>
-    <row r="63" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="21"/>
       <c r="B63" t="s">
         <v>191</v>
@@ -34378,7 +34385,7 @@
         <v>8.2519489795918357</v>
       </c>
     </row>
-    <row r="64" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="21"/>
       <c r="B64" t="s">
         <v>398</v>
@@ -34497,7 +34504,7 @@
         <v>4.2180154591836736</v>
       </c>
     </row>
-    <row r="65" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="21"/>
       <c r="B65" t="s">
         <v>361</v>
@@ -34619,7 +34626,7 @@
         <v>1.2300799484693878</v>
       </c>
     </row>
-    <row r="66" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:52" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="23"/>
       <c r="B66" s="24" t="s">
         <v>222</v>
@@ -34759,7 +34766,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AZ66" xr:uid="{19A21E0B-06A8-4909-8999-69A6CC63874F}"/>
+  <autoFilter ref="A1:AZ66" xr:uid="{19A21E0B-06A8-4909-8999-69A6CC63874F}">
+    <filterColumn colId="19">
+      <filters>
+        <filter val="Uranium"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>

--- a/data/MetalliCan/sites_for_lci.xlsx
+++ b/data/MetalliCan/sites_for_lci.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/regionalized_lci_mineral/data/MetalliCan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2964" documentId="13_ncr:1_{965BE886-D2C4-44D2-937F-E901E74C4ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4356C535-E0C5-4AF5-91ED-8686BD5CEE1B}"/>
+  <xr:revisionPtr revIDLastSave="2973" documentId="13_ncr:1_{965BE886-D2C4-44D2-937F-E901E74C4ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82654AB1-06BE-4690-A278-AAFCEC49AA1F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{9D292A65-B8C8-46CC-8162-88CB3EA3ABC7}"/>
   </bookViews>
@@ -131,7 +131,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8603" uniqueCount="1672">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8603" uniqueCount="1673">
   <si>
     <t>main_id</t>
   </si>
@@ -5824,6 +5824,9 @@
   <si>
     <t>Cu conc.</t>
   </si>
+  <si>
+    <t>Land+GHG</t>
+  </si>
 </sst>
 </file>
 
@@ -5861,7 +5864,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5919,6 +5922,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -6017,7 +6026,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -6088,6 +6097,14 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="11" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -26779,7 +26796,6 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19A21E0B-06A8-4909-8999-69A6CC63874F}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AZ66"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -26988,7 +27004,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="2" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
         <v>53</v>
       </c>
@@ -27108,131 +27124,129 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
+    <row r="3" spans="1:52" s="57" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="56" t="s">
         <v>60</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="57" t="s">
         <v>63</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="57" t="s">
         <v>439</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="58" t="s">
         <v>435</v>
       </c>
-      <c r="G3" s="21" t="s">
+      <c r="G3" s="56" t="s">
         <v>64</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="57" t="s">
         <v>1615</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="57" t="s">
         <v>1649</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="57" t="s">
         <v>1635</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="57" t="s">
         <v>1511</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="57" t="s">
         <v>1508</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N3" s="57" t="s">
         <v>1571</v>
       </c>
-      <c r="P3" t="s">
+      <c r="P3" s="57" t="s">
         <v>1205</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="Q3" s="57" t="s">
         <v>1205</v>
       </c>
-      <c r="R3" t="s">
+      <c r="R3" s="57" t="s">
         <v>1205</v>
       </c>
-      <c r="S3" t="s">
+      <c r="S3" s="57" t="s">
         <v>1209</v>
       </c>
-      <c r="T3" s="22" t="s">
+      <c r="T3" s="58" t="s">
         <v>65</v>
       </c>
-      <c r="U3" t="s">
+      <c r="U3" s="57" t="s">
         <v>1205</v>
       </c>
-      <c r="V3" t="s">
+      <c r="V3" s="57" t="s">
         <v>997</v>
       </c>
-      <c r="W3" t="s">
+      <c r="W3" s="57" t="s">
         <v>1659</v>
       </c>
-      <c r="X3" s="21">
+      <c r="X3" s="56">
         <f>prod_table_raw!N13</f>
         <v>166000</v>
       </c>
-      <c r="Y3">
+      <c r="Y3" s="57">
         <f>(AC3+AD3)/0.98</f>
         <v>0.92040969387755101</v>
       </c>
-      <c r="Z3"/>
-      <c r="AA3">
+      <c r="AA3" s="57">
         <f t="shared" si="0"/>
         <v>165999.07959030612</v>
       </c>
-      <c r="AB3" s="54">
+      <c r="AB3" s="59">
         <f>1-(Y3+Z3)/AA3</f>
         <v>0.99999445533254672</v>
       </c>
-      <c r="AC3" s="34">
+      <c r="AC3" s="60">
         <f>prod_table_raw!N14</f>
         <v>0.90200150000000001</v>
       </c>
-      <c r="AD3" s="34"/>
-      <c r="AE3" s="34"/>
-      <c r="AF3" s="34"/>
-      <c r="AG3" s="34"/>
-      <c r="AH3" s="34"/>
-      <c r="AI3" s="34"/>
-      <c r="AJ3" s="34"/>
-      <c r="AK3" s="34"/>
-      <c r="AL3" s="34"/>
-      <c r="AM3" s="34"/>
-      <c r="AN3" s="34"/>
-      <c r="AO3" s="34"/>
-      <c r="AP3">
+      <c r="AD3" s="60"/>
+      <c r="AE3" s="60"/>
+      <c r="AF3" s="60"/>
+      <c r="AG3" s="60"/>
+      <c r="AH3" s="60"/>
+      <c r="AI3" s="60"/>
+      <c r="AJ3" s="60"/>
+      <c r="AK3" s="60"/>
+      <c r="AL3" s="60"/>
+      <c r="AM3" s="60"/>
+      <c r="AN3" s="60"/>
+      <c r="AO3" s="60"/>
+      <c r="AP3" s="57">
         <f>AE3/(concentrate_grade!$F$4/100)</f>
         <v>0</v>
       </c>
-      <c r="AQ3">
+      <c r="AQ3" s="57">
         <f>AF3/(concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
-      <c r="AR3">
+      <c r="AR3" s="57">
         <f>AH3/(concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
-      <c r="AS3">
+      <c r="AS3" s="57">
         <f>AI3/(concentrate_grade!$F$9/100)</f>
         <v>0</v>
       </c>
-      <c r="AT3">
+      <c r="AT3" s="57">
         <f>AJ3/(concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
-      <c r="AU3"/>
-      <c r="AV3" s="34"/>
-      <c r="AW3" s="34"/>
-      <c r="AX3" s="34"/>
-      <c r="AY3">
+      <c r="AV3" s="60"/>
+      <c r="AW3" s="60"/>
+      <c r="AX3" s="60"/>
+      <c r="AY3" s="57">
         <f>AO3/concentrate_grade!$F$10</f>
         <v>0</v>
       </c>
-      <c r="AZ3">
+      <c r="AZ3" s="57">
         <f t="shared" si="1"/>
         <v>0.92040969387755101</v>
       </c>
     </row>
-    <row r="4" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
         <v>68</v>
       </c>
@@ -27326,7 +27340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A5" s="21" t="s">
         <v>74</v>
       </c>
@@ -27453,7 +27467,7 @@
         <v>29.039084533163262</v>
       </c>
     </row>
-    <row r="6" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A6" s="21" t="s">
         <v>82</v>
       </c>
@@ -27565,7 +27579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A7" s="21" t="s">
         <v>88</v>
       </c>
@@ -27683,7 +27697,7 @@
         <v>3.5165997959183577</v>
       </c>
     </row>
-    <row r="8" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A8" s="21" t="s">
         <v>524</v>
       </c>
@@ -27807,7 +27821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A9" s="21" t="s">
         <v>526</v>
       </c>
@@ -27913,7 +27927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A10" s="21" t="s">
         <v>109</v>
       </c>
@@ -28043,7 +28057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A11" s="21" t="s">
         <v>527</v>
       </c>
@@ -28170,7 +28184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A12" s="21" t="s">
         <v>116</v>
       </c>
@@ -28294,7 +28308,7 @@
         <v>24.008283837755101</v>
       </c>
     </row>
-    <row r="13" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A13" s="21" t="s">
         <v>125</v>
       </c>
@@ -28412,7 +28426,7 @@
         <v>2.7760508515306124</v>
       </c>
     </row>
-    <row r="14" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A14" s="21" t="s">
         <v>135</v>
       </c>
@@ -28533,7 +28547,7 @@
         <v>7.7388999209183664</v>
       </c>
     </row>
-    <row r="15" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A15" s="21" t="s">
         <v>139</v>
       </c>
@@ -28654,128 +28668,126 @@
         <v>0.12428704693877551</v>
       </c>
     </row>
-    <row r="16" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="21" t="s">
+    <row r="16" spans="1:52" s="39" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="61" t="s">
         <v>156</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="39" t="s">
         <v>159</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="39" t="s">
         <v>437</v>
       </c>
-      <c r="F16" s="22" t="s">
+      <c r="F16" s="62" t="s">
         <v>435</v>
       </c>
-      <c r="G16" s="21" t="s">
+      <c r="G16" s="61" t="s">
         <v>91</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H16" s="39" t="s">
         <v>1617</v>
       </c>
-      <c r="I16" t="s">
+      <c r="I16" s="39" t="s">
         <v>1649</v>
       </c>
-      <c r="K16" t="s">
+      <c r="K16" s="39" t="s">
         <v>1515</v>
       </c>
-      <c r="M16">
+      <c r="M16" s="39">
         <v>7405086.2285420913</v>
       </c>
-      <c r="N16" t="s">
+      <c r="N16" s="39" t="s">
         <v>1577</v>
       </c>
-      <c r="Q16" t="s">
+      <c r="Q16" s="39" t="s">
         <v>1205</v>
       </c>
-      <c r="R16" t="s">
+      <c r="R16" s="39" t="s">
         <v>1205</v>
       </c>
-      <c r="S16" t="s">
+      <c r="S16" s="39" t="s">
         <v>1205</v>
       </c>
-      <c r="T16" s="22" t="s">
+      <c r="T16" s="62" t="s">
         <v>115</v>
       </c>
-      <c r="U16" t="s">
+      <c r="U16" s="39" t="s">
         <v>1597</v>
       </c>
-      <c r="V16" t="s">
+      <c r="V16" s="39" t="s">
         <v>997</v>
       </c>
-      <c r="W16" t="s">
+      <c r="W16" s="39" t="s">
         <v>1659</v>
       </c>
-      <c r="X16" s="21">
+      <c r="X16" s="61">
         <f>prod_table_raw!N70</f>
         <v>457000</v>
       </c>
-      <c r="Y16">
+      <c r="Y16" s="39">
         <f>(AC16+AD16)/0.98</f>
         <v>1.4536125510204081</v>
       </c>
-      <c r="Z16"/>
-      <c r="AA16">
+      <c r="AA16" s="39">
         <f t="shared" si="0"/>
         <v>456998.54638744897</v>
       </c>
-      <c r="AB16" s="54">
+      <c r="AB16" s="63">
         <f t="shared" si="2"/>
         <v>0.99999681921843619</v>
       </c>
-      <c r="AC16" s="34">
+      <c r="AC16" s="37">
         <f>prod_table_raw!N71</f>
         <v>1.3809954</v>
       </c>
-      <c r="AD16" s="34">
+      <c r="AD16" s="37">
         <f>prod_table_raw!N72</f>
         <v>4.3544899999999997E-2</v>
       </c>
-      <c r="AE16" s="34"/>
-      <c r="AF16" s="34"/>
-      <c r="AG16" s="34"/>
-      <c r="AH16" s="34"/>
-      <c r="AI16" s="34"/>
-      <c r="AJ16" s="34"/>
-      <c r="AK16" s="34"/>
-      <c r="AL16" s="34"/>
-      <c r="AM16" s="34"/>
-      <c r="AN16" s="34"/>
-      <c r="AO16" s="34"/>
-      <c r="AP16">
+      <c r="AE16" s="37"/>
+      <c r="AF16" s="37"/>
+      <c r="AG16" s="37"/>
+      <c r="AH16" s="37"/>
+      <c r="AI16" s="37"/>
+      <c r="AJ16" s="37"/>
+      <c r="AK16" s="37"/>
+      <c r="AL16" s="37"/>
+      <c r="AM16" s="37"/>
+      <c r="AN16" s="37"/>
+      <c r="AO16" s="37"/>
+      <c r="AP16" s="39">
         <f>AE16/(concentrate_grade!$F$4/100)</f>
         <v>0</v>
       </c>
-      <c r="AQ16">
+      <c r="AQ16" s="39">
         <f>AF16/(concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
-      <c r="AR16">
+      <c r="AR16" s="39">
         <f>AH16/(concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
-      <c r="AS16">
+      <c r="AS16" s="39">
         <f>AI16/(concentrate_grade!$F$9/100)</f>
         <v>0</v>
       </c>
-      <c r="AT16">
+      <c r="AT16" s="39">
         <f>AJ16/(concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
-      <c r="AU16"/>
-      <c r="AV16" s="34"/>
-      <c r="AW16" s="34"/>
-      <c r="AX16" s="34"/>
-      <c r="AY16">
+      <c r="AV16" s="37"/>
+      <c r="AW16" s="37"/>
+      <c r="AX16" s="37"/>
+      <c r="AY16" s="39">
         <f>AO16/concentrate_grade!$F$10</f>
         <v>0</v>
       </c>
-      <c r="AZ16">
+      <c r="AZ16" s="39">
         <f t="shared" si="1"/>
         <v>1.4536125510204081</v>
       </c>
     </row>
-    <row r="17" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A17" s="21" t="s">
         <v>161</v>
       </c>
@@ -28893,7 +28905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A18" s="21" t="s">
         <v>529</v>
       </c>
@@ -29020,7 +29032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A19" s="21" t="s">
         <v>167</v>
       </c>
@@ -29144,7 +29156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A20" s="21" t="s">
         <v>173</v>
       </c>
@@ -29271,7 +29283,7 @@
         <v>4.4745421183166938</v>
       </c>
     </row>
-    <row r="21" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A21" s="21" t="s">
         <v>180</v>
       </c>
@@ -29395,7 +29407,7 @@
         <v>4.476523630102041</v>
       </c>
     </row>
-    <row r="22" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A22" s="21" t="s">
         <v>186</v>
       </c>
@@ -29522,7 +29534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A23" s="21" t="s">
         <v>494</v>
       </c>
@@ -29625,7 +29637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A24" s="21" t="s">
         <v>195</v>
       </c>
@@ -29743,7 +29755,7 @@
         <v>4.1704080612244905</v>
       </c>
     </row>
-    <row r="25" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A25" s="21" t="s">
         <v>200</v>
       </c>
@@ -29864,7 +29876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A26" s="21" t="s">
         <v>205</v>
       </c>
@@ -29988,7 +30000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A27" s="21" t="s">
         <v>209</v>
       </c>
@@ -30008,7 +30020,7 @@
         <v>1649</v>
       </c>
       <c r="K27" t="s">
-        <v>1516</v>
+        <v>1672</v>
       </c>
       <c r="L27" t="s">
         <v>1610</v>
@@ -30106,7 +30118,7 @@
         <v>1.2201776096938775</v>
       </c>
     </row>
-    <row r="28" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A28" s="21" t="s">
         <v>215</v>
       </c>
@@ -30233,7 +30245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:52" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:52" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="21" t="s">
         <v>227</v>
       </c>
@@ -30256,7 +30268,7 @@
         <v>1649</v>
       </c>
       <c r="K29" t="s">
-        <v>1516</v>
+        <v>1672</v>
       </c>
       <c r="L29" t="s">
         <v>1508</v>
@@ -30357,7 +30369,7 @@
         <v>7.932820721938775</v>
       </c>
     </row>
-    <row r="30" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A30" s="21" t="s">
         <v>232</v>
       </c>
@@ -30493,7 +30505,7 @@
         <v>9.8029027903061134</v>
       </c>
     </row>
-    <row r="31" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A31" s="21" t="s">
         <v>534</v>
       </c>
@@ -30596,7 +30608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A32" s="21" t="s">
         <v>239</v>
       </c>
@@ -30723,7 +30735,7 @@
         <v>7.253304461734694</v>
       </c>
     </row>
-    <row r="33" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A33" s="21" t="s">
         <v>243</v>
       </c>
@@ -30841,7 +30853,7 @@
         <v>1.0473627551020408</v>
       </c>
     </row>
-    <row r="34" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A34" s="21" t="s">
         <v>249</v>
       </c>
@@ -30959,7 +30971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A35" s="21" t="s">
         <v>267</v>
       </c>
@@ -31074,7 +31086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A36" s="21" t="s">
         <v>277</v>
       </c>
@@ -31198,7 +31210,7 @@
         <v>12.41413683010194</v>
       </c>
     </row>
-    <row r="37" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A37" s="21" t="s">
         <v>283</v>
       </c>
@@ -31322,7 +31334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A38" s="21" t="s">
         <v>288</v>
       </c>
@@ -31449,7 +31461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
         <v>294</v>
       </c>
@@ -31567,7 +31579,7 @@
         <v>5.7128877551020407</v>
       </c>
     </row>
-    <row r="40" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A40" s="21" t="s">
         <v>297</v>
       </c>
@@ -31688,7 +31700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A41" s="21" t="s">
         <v>305</v>
       </c>
@@ -31806,7 +31818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A42" s="21" t="s">
         <v>311</v>
       </c>
@@ -31930,7 +31942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A43" s="21" t="s">
         <v>316</v>
       </c>
@@ -32021,7 +32033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A44" s="21" t="s">
         <v>328</v>
       </c>
@@ -32142,7 +32154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A45" s="21" t="s">
         <v>333</v>
       </c>
@@ -32269,7 +32281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A46" s="21" t="s">
         <v>337</v>
       </c>
@@ -32387,7 +32399,7 @@
         <v>8.0534261301020305</v>
       </c>
     </row>
-    <row r="47" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A47" s="21" t="s">
         <v>340</v>
       </c>
@@ -32517,134 +32529,132 @@
         <v>0.15869132653061224</v>
       </c>
     </row>
-    <row r="48" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="21" t="s">
+    <row r="48" spans="1:52" s="57" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="56" t="s">
         <v>343</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" s="57" t="s">
         <v>346</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E48" s="57" t="s">
         <v>437</v>
       </c>
-      <c r="F48" s="22" t="s">
+      <c r="F48" s="58" t="s">
         <v>435</v>
       </c>
-      <c r="G48" s="21" t="s">
+      <c r="G48" s="56" t="s">
         <v>64</v>
       </c>
-      <c r="H48" t="s">
+      <c r="H48" s="57" t="s">
         <v>1617</v>
       </c>
-      <c r="I48" t="s">
+      <c r="I48" s="57" t="s">
         <v>1650</v>
       </c>
-      <c r="J48" t="s">
+      <c r="J48" s="57" t="s">
         <v>1492</v>
       </c>
-      <c r="K48" t="s">
+      <c r="K48" s="57" t="s">
         <v>1518</v>
       </c>
-      <c r="L48" t="s">
+      <c r="L48" s="57" t="s">
         <v>1609</v>
       </c>
-      <c r="M48">
+      <c r="M48" s="57">
         <v>6139378.4953300003</v>
       </c>
-      <c r="N48" t="s">
+      <c r="N48" s="57" t="s">
         <v>1576</v>
       </c>
-      <c r="O48" t="s">
+      <c r="O48" s="57" t="s">
         <v>1205</v>
       </c>
-      <c r="Q48" t="s">
+      <c r="Q48" s="57" t="s">
         <v>1205</v>
       </c>
-      <c r="R48" t="s">
+      <c r="R48" s="57" t="s">
         <v>1205</v>
       </c>
-      <c r="S48" t="s">
+      <c r="S48" s="57" t="s">
         <v>1205</v>
       </c>
-      <c r="T48" s="22" t="s">
+      <c r="T48" s="58" t="s">
         <v>65</v>
       </c>
-      <c r="U48" t="s">
+      <c r="U48" s="57" t="s">
         <v>1205</v>
       </c>
-      <c r="V48" t="s">
+      <c r="V48" s="57" t="s">
         <v>997</v>
       </c>
-      <c r="W48" t="s">
+      <c r="W48" s="57" t="s">
         <v>1659</v>
       </c>
-      <c r="X48" s="21">
+      <c r="X48" s="56">
         <f>prod_table_raw!N222</f>
         <v>841000</v>
       </c>
-      <c r="Y48">
+      <c r="Y48" s="57">
         <f>(AC48+AD48)/0.98</f>
         <v>3.5769025000000001</v>
       </c>
-      <c r="Z48"/>
-      <c r="AA48">
+      <c r="AA48" s="57">
         <f t="shared" si="5"/>
         <v>840996.4230975</v>
       </c>
-      <c r="AB48" s="54">
+      <c r="AB48" s="59">
         <f t="shared" si="7"/>
         <v>0.99999574682792725</v>
       </c>
-      <c r="AC48" s="34">
+      <c r="AC48" s="60">
         <f>prod_table_raw!N223</f>
         <v>3.5053644500000001</v>
       </c>
-      <c r="AD48" s="34"/>
-      <c r="AE48" s="34"/>
-      <c r="AF48" s="34"/>
-      <c r="AG48" s="34"/>
-      <c r="AH48" s="34"/>
-      <c r="AI48" s="34"/>
-      <c r="AJ48" s="34"/>
-      <c r="AK48" s="34"/>
-      <c r="AL48" s="34"/>
-      <c r="AM48" s="34"/>
-      <c r="AN48" s="34"/>
-      <c r="AO48" s="34"/>
-      <c r="AP48">
+      <c r="AD48" s="60"/>
+      <c r="AE48" s="60"/>
+      <c r="AF48" s="60"/>
+      <c r="AG48" s="60"/>
+      <c r="AH48" s="60"/>
+      <c r="AI48" s="60"/>
+      <c r="AJ48" s="60"/>
+      <c r="AK48" s="60"/>
+      <c r="AL48" s="60"/>
+      <c r="AM48" s="60"/>
+      <c r="AN48" s="60"/>
+      <c r="AO48" s="60"/>
+      <c r="AP48" s="57">
         <f>AE48/(concentrate_grade!$F$4/100)</f>
         <v>0</v>
       </c>
-      <c r="AQ48">
+      <c r="AQ48" s="57">
         <f>AF48/(concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
-      <c r="AR48">
+      <c r="AR48" s="57">
         <f>AH48/(concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
-      <c r="AS48">
+      <c r="AS48" s="57">
         <f>AI48/(concentrate_grade!$F$9/100)</f>
         <v>0</v>
       </c>
-      <c r="AT48">
+      <c r="AT48" s="57">
         <f>AJ48/(concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
-      <c r="AU48"/>
-      <c r="AV48" s="34"/>
-      <c r="AW48" s="34"/>
-      <c r="AX48" s="34"/>
-      <c r="AY48">
+      <c r="AV48" s="60"/>
+      <c r="AW48" s="60"/>
+      <c r="AX48" s="60"/>
+      <c r="AY48" s="57">
         <f>AO48/concentrate_grade!$F$10</f>
         <v>0</v>
       </c>
-      <c r="AZ48">
+      <c r="AZ48" s="57">
         <f t="shared" si="6"/>
         <v>3.5769025000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A49" s="21" t="s">
         <v>357</v>
       </c>
@@ -32756,7 +32766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A50" s="21" t="s">
         <v>371</v>
       </c>
@@ -32883,7 +32893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A51" s="21" t="s">
         <v>376</v>
       </c>
@@ -32989,7 +32999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A52" s="21" t="s">
         <v>381</v>
       </c>
@@ -33104,7 +33114,7 @@
         <v>1.2269695984693878</v>
       </c>
     </row>
-    <row r="53" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A53" s="21" t="s">
         <v>387</v>
       </c>
@@ -33201,7 +33211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A54" s="21" t="s">
         <v>393</v>
       </c>
@@ -33322,7 +33332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A55" s="21" t="s">
         <v>533</v>
       </c>
@@ -33449,7 +33459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A56" s="21" t="s">
         <v>409</v>
       </c>
@@ -33543,7 +33553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A57" s="21" t="s">
         <v>419</v>
       </c>
@@ -33664,7 +33674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A58" s="21" t="s">
         <v>423</v>
       </c>
@@ -33785,7 +33795,7 @@
         <v>4.1181668765306121</v>
       </c>
     </row>
-    <row r="59" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A59" s="21" t="s">
         <v>428</v>
       </c>
@@ -34153,7 +34163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A62" s="21"/>
       <c r="B62" t="s">
         <v>273</v>
@@ -34272,7 +34282,7 @@
         <v>17.66760135719143</v>
       </c>
     </row>
-    <row r="63" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A63" s="21"/>
       <c r="B63" t="s">
         <v>191</v>
@@ -34385,7 +34395,7 @@
         <v>8.2519489795918357</v>
       </c>
     </row>
-    <row r="64" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A64" s="21"/>
       <c r="B64" t="s">
         <v>398</v>
@@ -34504,7 +34514,7 @@
         <v>4.2180154591836736</v>
       </c>
     </row>
-    <row r="65" spans="1:52" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A65" s="21"/>
       <c r="B65" t="s">
         <v>361</v>
@@ -34626,7 +34636,7 @@
         <v>1.2300799484693878</v>
       </c>
     </row>
-    <row r="66" spans="1:52" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:52" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="23"/>
       <c r="B66" s="24" t="s">
         <v>222</v>
@@ -34651,7 +34661,7 @@
         <v>1630</v>
       </c>
       <c r="K66" s="24" t="s">
-        <v>1519</v>
+        <v>1628</v>
       </c>
       <c r="L66" t="s">
         <v>1609</v>
@@ -34766,13 +34776,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AZ66" xr:uid="{19A21E0B-06A8-4909-8999-69A6CC63874F}">
-    <filterColumn colId="19">
-      <filters>
-        <filter val="Uranium"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AZ66" xr:uid="{19A21E0B-06A8-4909-8999-69A6CC63874F}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>

--- a/data/MetalliCan/sites_for_lci.xlsx
+++ b/data/MetalliCan/sites_for_lci.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polymtlca-my.sharepoint.com/personal/marin_pellan_polymtl_ca/Documents/POST_DOC/CODE/regionalized_lci_mineral/data/MetalliCan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3192" documentId="13_ncr:1_{965BE886-D2C4-44D2-937F-E901E74C4ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D110C5B-79AF-4105-B58B-9EE87A743CCC}"/>
+  <xr:revisionPtr revIDLastSave="3223" documentId="13_ncr:1_{965BE886-D2C4-44D2-937F-E901E74C4ED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B21A61DB-68BA-4203-8258-EFDC7AECD472}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{9D292A65-B8C8-46CC-8162-88CB3EA3ABC7}"/>
   </bookViews>
@@ -29,7 +29,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">Arch_refineries!$A$1:$J$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">market_shares!$A$1:$J$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">market_shares!$A$1:$J$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">ms_benchmark!$A$1:$C$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">prices!$A$1:$D$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'prod_$_data'!$A$1:$BF$67</definedName>
@@ -132,7 +132,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8495" uniqueCount="1591">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8495" uniqueCount="1589">
   <si>
     <t>main_id</t>
   </si>
@@ -5413,13 +5413,7 @@
     <t>NPRI+Land+GHG</t>
   </si>
   <si>
-    <t>Not sure (no GHG)</t>
-  </si>
-  <si>
     <t>Particular production pattern. Check GHG coverage (only one facility?)</t>
-  </si>
-  <si>
-    <t>Yes (manufacturing)</t>
   </si>
   <si>
     <t>Refined Ni+Cu</t>
@@ -5620,7 +5614,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5678,12 +5672,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5889,27 +5877,27 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="11" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="12" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="11" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="11" fontId="0" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -26543,7 +26531,7 @@
         <v>1514</v>
       </c>
       <c r="R1" s="16" t="s">
-        <v>1590</v>
+        <v>1588</v>
       </c>
       <c r="S1" s="16" t="s">
         <v>1517</v>
@@ -26576,10 +26564,10 @@
         <v>1465</v>
       </c>
       <c r="AC1" s="16" t="s">
-        <v>1588</v>
+        <v>1586</v>
       </c>
       <c r="AD1" s="16" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
       <c r="AE1" s="16" t="s">
         <v>1462</v>
@@ -26657,78 +26645,78 @@
         <v>1504</v>
       </c>
     </row>
-    <row r="2" spans="1:55" s="66" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="64" t="s">
+    <row r="2" spans="1:55" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="59" t="s">
         <v>53</v>
       </c>
-      <c r="B2" s="65"/>
-      <c r="C2" s="66" t="s">
+      <c r="B2" s="60"/>
+      <c r="C2" s="61" t="s">
         <v>56</v>
       </c>
-      <c r="D2" s="65"/>
-      <c r="E2" s="66" t="s">
+      <c r="D2" s="60"/>
+      <c r="E2" s="61" t="s">
         <v>436</v>
       </c>
-      <c r="F2" s="67" t="s">
+      <c r="F2" s="62" t="s">
         <v>435</v>
       </c>
-      <c r="G2" s="64" t="s">
+      <c r="G2" s="59" t="s">
         <v>57</v>
       </c>
-      <c r="I2" s="66" t="s">
+      <c r="I2" s="61" t="s">
         <v>1190</v>
       </c>
-      <c r="J2" s="66" t="s">
+      <c r="J2" s="61" t="s">
         <v>1533</v>
       </c>
-      <c r="K2" s="66" t="s">
+      <c r="K2" s="61" t="s">
         <v>1426</v>
       </c>
-      <c r="L2" s="66" t="s">
+      <c r="L2" s="61" t="s">
         <v>1508</v>
       </c>
-      <c r="M2" s="66">
+      <c r="M2" s="61">
         <v>15702687.604910901</v>
       </c>
-      <c r="N2" s="66" t="s">
+      <c r="N2" s="61" t="s">
         <v>743</v>
       </c>
-      <c r="O2" s="66" t="s">
+      <c r="O2" s="61" t="s">
         <v>1113</v>
       </c>
-      <c r="Q2" s="66" t="s">
+      <c r="Q2" s="61" t="s">
         <v>1113</v>
       </c>
-      <c r="R2" s="66" t="s">
+      <c r="R2" s="61" t="s">
         <v>1113</v>
       </c>
-      <c r="S2" s="66" t="s">
+      <c r="S2" s="61" t="s">
         <v>1113</v>
       </c>
-      <c r="T2" s="66" t="s">
+      <c r="T2" s="61" t="s">
         <v>1113</v>
       </c>
-      <c r="U2" s="67" t="s">
+      <c r="U2" s="62" t="s">
         <v>49</v>
       </c>
-      <c r="V2" s="66" t="s">
-        <v>1542</v>
-      </c>
-      <c r="W2" s="65" t="s">
+      <c r="V2" s="61" t="s">
+        <v>1540</v>
+      </c>
+      <c r="W2" s="60" t="s">
         <v>1068</v>
       </c>
-      <c r="X2" s="66" t="s">
-        <v>1570</v>
-      </c>
-      <c r="Y2" s="64">
+      <c r="X2" s="61" t="s">
+        <v>1568</v>
+      </c>
+      <c r="Y2" s="59">
         <f>prod_table_raw!N11</f>
         <v>11187000</v>
       </c>
-      <c r="AB2" s="66">
+      <c r="AB2" s="61">
         <f t="shared" ref="AB2:AB33" si="0">Y2-Z2-AA2</f>
         <v>11187000</v>
       </c>
-      <c r="AC2" s="72">
+      <c r="AC2" s="67">
         <f>Z2/Y2</f>
         <v>0</v>
       </c>
@@ -26736,126 +26724,127 @@
         <f>AA2/Y2</f>
         <v>0</v>
       </c>
-      <c r="AE2" s="68">
+      <c r="AE2" s="63">
         <f>1-(Z2+AA2)/AB2</f>
         <v>1</v>
       </c>
-      <c r="AF2" s="65"/>
-      <c r="AG2" s="65"/>
-      <c r="AH2" s="65"/>
-      <c r="AI2" s="65"/>
-      <c r="AJ2" s="65"/>
-      <c r="AK2" s="65"/>
-      <c r="AL2" s="65"/>
-      <c r="AM2" s="65"/>
-      <c r="AN2" s="65"/>
-      <c r="AO2" s="65"/>
-      <c r="AP2" s="65"/>
-      <c r="AQ2" s="65"/>
-      <c r="AR2" s="65"/>
-      <c r="AS2" s="66">
+      <c r="AF2" s="60"/>
+      <c r="AG2" s="60"/>
+      <c r="AH2" s="60"/>
+      <c r="AI2" s="60"/>
+      <c r="AJ2" s="60"/>
+      <c r="AK2" s="60"/>
+      <c r="AL2" s="60"/>
+      <c r="AM2" s="60"/>
+      <c r="AN2" s="60"/>
+      <c r="AO2" s="60"/>
+      <c r="AP2" s="60"/>
+      <c r="AQ2" s="60"/>
+      <c r="AR2" s="60"/>
+      <c r="AS2" s="61">
         <f>AH2/(concentrate_grade!$F$4/100)</f>
         <v>0</v>
       </c>
-      <c r="AT2" s="66">
+      <c r="AT2" s="61">
         <f>AI2/(concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
-      <c r="AU2" s="66">
+      <c r="AU2" s="61">
         <f>AK2/(concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
-      <c r="AV2" s="66">
+      <c r="AV2" s="61">
         <f>AL2/(concentrate_grade!$F$9/100)</f>
         <v>0</v>
       </c>
-      <c r="AW2" s="66">
+      <c r="AW2" s="61">
         <f>AM2/(concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
-      <c r="BB2" s="66" t="e">
+      <c r="BB2" s="61" t="e">
         <f>AR2/concentrate_grade!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="BC2" s="66">
+      <c r="BC2" s="61">
         <f t="shared" ref="BC2:BC33" si="1">Z2</f>
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:55" s="54" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="53" t="s">
+    <row r="3" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="C3" s="54" t="s">
+      <c r="C3" t="s">
         <v>63</v>
       </c>
-      <c r="E3" s="54" t="s">
+      <c r="E3" t="s">
         <v>439</v>
       </c>
-      <c r="F3" s="55" t="s">
+      <c r="F3" s="19" t="s">
         <v>435</v>
       </c>
-      <c r="G3" s="53" t="s">
+      <c r="G3" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="H3" s="54" t="s">
+      <c r="H3" t="s">
         <v>1521</v>
       </c>
-      <c r="I3" s="54" t="s">
-        <v>1555</v>
-      </c>
-      <c r="J3" s="54" t="s">
-        <v>1541</v>
-      </c>
-      <c r="K3" s="54" t="s">
+      <c r="I3" t="s">
+        <v>1553</v>
+      </c>
+      <c r="J3" t="s">
+        <v>1539</v>
+      </c>
+      <c r="K3" t="s">
         <v>1419</v>
       </c>
-      <c r="L3" s="54" t="s">
+      <c r="L3" t="s">
         <v>1416</v>
       </c>
-      <c r="N3" s="54" t="s">
+      <c r="N3" t="s">
         <v>1477</v>
       </c>
-      <c r="P3" s="54" t="s">
+      <c r="P3" t="s">
         <v>1113</v>
       </c>
-      <c r="Q3" s="54" t="s">
+      <c r="Q3" t="s">
         <v>1113</v>
       </c>
-      <c r="R3" s="54" t="s">
+      <c r="R3" t="s">
         <v>1113</v>
       </c>
-      <c r="S3" s="54" t="s">
+      <c r="S3" t="s">
         <v>1113</v>
       </c>
-      <c r="T3" s="54" t="s">
+      <c r="T3" t="s">
         <v>1117</v>
       </c>
-      <c r="U3" s="55" t="s">
+      <c r="U3" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="V3" s="54" t="s">
+      <c r="V3" t="s">
         <v>1113</v>
       </c>
-      <c r="W3" s="54" t="s">
+      <c r="W3" t="s">
         <v>920</v>
       </c>
-      <c r="X3" s="54" t="s">
-        <v>1565</v>
-      </c>
-      <c r="Y3" s="53">
+      <c r="X3" t="s">
+        <v>1563</v>
+      </c>
+      <c r="Y3" s="18">
         <f>prod_table_raw!N13</f>
         <v>166000</v>
       </c>
-      <c r="Z3" s="54">
+      <c r="Z3">
         <f>(AF3+AG3)/0.98</f>
         <v>0.92040969387755101</v>
       </c>
-      <c r="AB3" s="54">
+      <c r="AA3"/>
+      <c r="AB3">
         <f t="shared" si="0"/>
         <v>165999.07959030612</v>
       </c>
-      <c r="AC3" s="72">
+      <c r="AC3" s="67">
         <f t="shared" ref="AC3:AC66" si="2">Z3/Y3</f>
         <v>5.544636710105729E-6</v>
       </c>
@@ -26863,150 +26852,151 @@
         <f t="shared" ref="AD3:AD66" si="3">AA3/Y3</f>
         <v>0</v>
       </c>
-      <c r="AE3" s="56">
+      <c r="AE3" s="51">
         <f>1-(Z3+AA3)/AB3</f>
         <v>0.99999445533254672</v>
       </c>
-      <c r="AF3" s="57">
+      <c r="AF3" s="31">
         <f>prod_table_raw!N14</f>
         <v>0.90200150000000001</v>
       </c>
-      <c r="AG3" s="57"/>
-      <c r="AH3" s="57"/>
-      <c r="AI3" s="57"/>
-      <c r="AJ3" s="57"/>
-      <c r="AK3" s="57"/>
-      <c r="AL3" s="57"/>
-      <c r="AM3" s="57"/>
-      <c r="AN3" s="57"/>
-      <c r="AO3" s="57"/>
-      <c r="AP3" s="57"/>
-      <c r="AQ3" s="57"/>
-      <c r="AR3" s="57"/>
-      <c r="AS3" s="54">
+      <c r="AG3" s="31"/>
+      <c r="AH3" s="31"/>
+      <c r="AI3" s="31"/>
+      <c r="AJ3" s="31"/>
+      <c r="AK3" s="31"/>
+      <c r="AL3" s="31"/>
+      <c r="AM3" s="31"/>
+      <c r="AN3" s="31"/>
+      <c r="AO3" s="31"/>
+      <c r="AP3" s="31"/>
+      <c r="AQ3" s="31"/>
+      <c r="AR3" s="31"/>
+      <c r="AS3">
         <f>AH3/(concentrate_grade!$F$4/100)</f>
         <v>0</v>
       </c>
-      <c r="AT3" s="54">
+      <c r="AT3">
         <f>AI3/(concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
-      <c r="AU3" s="54">
+      <c r="AU3">
         <f>AK3/(concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
-      <c r="AV3" s="54">
+      <c r="AV3">
         <f>AL3/(concentrate_grade!$F$9/100)</f>
         <v>0</v>
       </c>
-      <c r="AW3" s="54">
+      <c r="AW3">
         <f>AM3/(concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
-      <c r="AY3" s="57"/>
-      <c r="AZ3" s="57"/>
-      <c r="BA3" s="57"/>
-      <c r="BB3" s="54" t="e">
+      <c r="AX3"/>
+      <c r="AY3" s="31"/>
+      <c r="AZ3" s="31"/>
+      <c r="BA3" s="31"/>
+      <c r="BB3" t="e">
         <f>AR3/concentrate_grade!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="BC3" s="54">
+      <c r="BC3">
         <f t="shared" si="1"/>
         <v>0.92040969387755101</v>
       </c>
     </row>
-    <row r="4" spans="1:55" s="66" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="64" t="s">
+    <row r="4" spans="1:55" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="59" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="66" t="s">
+      <c r="C4" s="61" t="s">
         <v>70</v>
       </c>
-      <c r="E4" s="66" t="s">
+      <c r="E4" s="61" t="s">
         <v>436</v>
       </c>
-      <c r="F4" s="67" t="s">
+      <c r="F4" s="62" t="s">
         <v>540</v>
       </c>
-      <c r="G4" s="64" t="s">
+      <c r="G4" s="59" t="s">
         <v>71</v>
       </c>
-      <c r="I4" s="66" t="s">
+      <c r="I4" s="61" t="s">
         <v>1415</v>
       </c>
-      <c r="K4" s="66" t="s">
+      <c r="K4" s="61" t="s">
         <v>1424</v>
       </c>
-      <c r="M4" s="66">
+      <c r="M4" s="61">
         <v>1248584.6715172599</v>
       </c>
-      <c r="Q4" s="66" t="s">
+      <c r="Q4" s="61" t="s">
         <v>1113</v>
       </c>
-      <c r="R4" s="66" t="s">
+      <c r="R4" s="61" t="s">
         <v>1113</v>
       </c>
-      <c r="T4" s="66" t="s">
+      <c r="T4" s="61" t="s">
         <v>1113</v>
       </c>
-      <c r="U4" s="67" t="s">
+      <c r="U4" s="62" t="s">
         <v>1369</v>
       </c>
-      <c r="V4" s="66" t="s">
+      <c r="V4" s="61" t="s">
         <v>1117</v>
       </c>
-      <c r="W4" s="66" t="s">
+      <c r="W4" s="61" t="s">
         <v>1394</v>
       </c>
-      <c r="Y4" s="64"/>
-      <c r="AB4" s="66">
+      <c r="Y4" s="59"/>
+      <c r="AB4" s="61">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AC4" s="72"/>
+      <c r="AC4" s="67"/>
       <c r="AD4"/>
-      <c r="AF4" s="69"/>
-      <c r="AG4" s="69"/>
-      <c r="AH4" s="69"/>
-      <c r="AI4" s="69"/>
-      <c r="AJ4" s="69"/>
-      <c r="AK4" s="69"/>
-      <c r="AL4" s="69">
+      <c r="AF4" s="64"/>
+      <c r="AG4" s="64"/>
+      <c r="AH4" s="64"/>
+      <c r="AI4" s="64"/>
+      <c r="AJ4" s="64"/>
+      <c r="AK4" s="64"/>
+      <c r="AL4" s="64">
         <f>prod_table_raw!N16</f>
         <v>752600</v>
       </c>
-      <c r="AM4" s="69">
+      <c r="AM4" s="64">
         <f>prod_table_raw!N15</f>
         <v>244600</v>
       </c>
-      <c r="AN4" s="69"/>
-      <c r="AO4" s="69"/>
-      <c r="AP4" s="69"/>
-      <c r="AQ4" s="69"/>
-      <c r="AR4" s="69"/>
-      <c r="AS4" s="65">
+      <c r="AN4" s="64"/>
+      <c r="AO4" s="64"/>
+      <c r="AP4" s="64"/>
+      <c r="AQ4" s="64"/>
+      <c r="AR4" s="64"/>
+      <c r="AS4" s="60">
         <f>AH4/(concentrate_grade!$F$4/100)</f>
         <v>0</v>
       </c>
-      <c r="AT4" s="65">
+      <c r="AT4" s="60">
         <f>AI4/(concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
-      <c r="AU4" s="66">
+      <c r="AU4" s="61">
         <f>AK4/(concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
-      <c r="AV4" s="69"/>
-      <c r="AW4" s="66">
+      <c r="AV4" s="64"/>
+      <c r="AW4" s="61">
         <f>AM4/(concentrate_grade!$F$8/100)</f>
         <v>407666.66666666669</v>
       </c>
-      <c r="AX4" s="69"/>
-      <c r="AY4" s="69"/>
-      <c r="AZ4" s="69"/>
-      <c r="BA4" s="69"/>
-      <c r="BB4" s="69"/>
-      <c r="BC4" s="66">
+      <c r="AX4" s="64"/>
+      <c r="AY4" s="64"/>
+      <c r="AZ4" s="64"/>
+      <c r="BA4" s="64"/>
+      <c r="BB4" s="64"/>
+      <c r="BC4" s="61">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -27031,7 +27021,7 @@
         <v>1523</v>
       </c>
       <c r="I5" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="J5" t="s">
         <v>1531</v>
@@ -27070,7 +27060,7 @@
         <v>1075</v>
       </c>
       <c r="X5" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="Y5" s="18">
         <f>prod_table_raw!N17</f>
@@ -27085,7 +27075,7 @@
         <f t="shared" si="0"/>
         <v>17332870.960915469</v>
       </c>
-      <c r="AC5" s="72">
+      <c r="AC5" s="67">
         <f t="shared" si="2"/>
         <v>1.6753736843322964E-6</v>
       </c>
@@ -27149,70 +27139,70 @@
         <v>29.039084533163262</v>
       </c>
     </row>
-    <row r="6" spans="1:55" s="66" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="64" t="s">
+    <row r="6" spans="1:55" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="59" t="s">
         <v>82</v>
       </c>
-      <c r="C6" s="66" t="s">
+      <c r="C6" s="61" t="s">
         <v>84</v>
       </c>
-      <c r="E6" s="66" t="s">
+      <c r="E6" s="61" t="s">
         <v>442</v>
       </c>
-      <c r="F6" s="67" t="s">
+      <c r="F6" s="62" t="s">
         <v>435</v>
       </c>
-      <c r="G6" s="64" t="s">
+      <c r="G6" s="59" t="s">
         <v>78</v>
       </c>
-      <c r="H6" s="66" t="s">
+      <c r="H6" s="61" t="s">
         <v>1519</v>
       </c>
-      <c r="I6" s="66" t="s">
+      <c r="I6" s="61" t="s">
         <v>1404</v>
       </c>
-      <c r="K6" s="66" t="s">
+      <c r="K6" s="61" t="s">
         <v>1426</v>
       </c>
-      <c r="L6" s="66" t="s">
+      <c r="L6" s="61" t="s">
         <v>1416</v>
       </c>
-      <c r="M6" s="66">
+      <c r="M6" s="61">
         <v>26104648.817951292</v>
       </c>
-      <c r="Q6" s="66" t="s">
+      <c r="Q6" s="61" t="s">
         <v>1113</v>
       </c>
       <c r="R6" t="s">
         <v>1113</v>
       </c>
-      <c r="S6" s="66" t="s">
+      <c r="S6" s="61" t="s">
         <v>1113</v>
       </c>
-      <c r="T6" s="66" t="s">
+      <c r="T6" s="61" t="s">
         <v>1113</v>
       </c>
-      <c r="U6" s="67" t="s">
+      <c r="U6" s="62" t="s">
         <v>49</v>
       </c>
-      <c r="V6" s="66" t="s">
-        <v>1542</v>
-      </c>
-      <c r="W6" s="66" t="s">
+      <c r="V6" s="61" t="s">
+        <v>1540</v>
+      </c>
+      <c r="W6" s="61" t="s">
         <v>1068</v>
       </c>
-      <c r="X6" s="66" t="s">
-        <v>1571</v>
-      </c>
-      <c r="Y6" s="64">
+      <c r="X6" s="61" t="s">
+        <v>1569</v>
+      </c>
+      <c r="Y6" s="59">
         <f>prod_table_raw!N21</f>
         <v>16478000</v>
       </c>
-      <c r="AB6" s="66">
+      <c r="AB6" s="61">
         <f t="shared" si="0"/>
         <v>16478000</v>
       </c>
-      <c r="AC6" s="72">
+      <c r="AC6" s="67">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -27220,51 +27210,51 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AE6" s="68">
+      <c r="AE6" s="63">
         <f>1-(Z6+AA6)/AB6</f>
         <v>1</v>
       </c>
-      <c r="AF6" s="69"/>
-      <c r="AG6" s="69"/>
-      <c r="AH6" s="69"/>
-      <c r="AI6" s="69"/>
-      <c r="AJ6" s="69"/>
-      <c r="AK6" s="69"/>
-      <c r="AL6" s="69"/>
-      <c r="AM6" s="69"/>
-      <c r="AN6" s="69"/>
-      <c r="AO6" s="69"/>
-      <c r="AP6" s="69"/>
-      <c r="AQ6" s="69"/>
-      <c r="AR6" s="69"/>
-      <c r="AS6" s="66">
+      <c r="AF6" s="64"/>
+      <c r="AG6" s="64"/>
+      <c r="AH6" s="64"/>
+      <c r="AI6" s="64"/>
+      <c r="AJ6" s="64"/>
+      <c r="AK6" s="64"/>
+      <c r="AL6" s="64"/>
+      <c r="AM6" s="64"/>
+      <c r="AN6" s="64"/>
+      <c r="AO6" s="64"/>
+      <c r="AP6" s="64"/>
+      <c r="AQ6" s="64"/>
+      <c r="AR6" s="64"/>
+      <c r="AS6" s="61">
         <f>AH6/(concentrate_grade!$F$4/100)</f>
         <v>0</v>
       </c>
-      <c r="AT6" s="66">
+      <c r="AT6" s="61">
         <f>AI6/(concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
-      <c r="AU6" s="66">
+      <c r="AU6" s="61">
         <f>AK6/(concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
-      <c r="AV6" s="66">
+      <c r="AV6" s="61">
         <f>AL6/(concentrate_grade!$F$9/100)</f>
         <v>0</v>
       </c>
-      <c r="AW6" s="66">
+      <c r="AW6" s="61">
         <f>AM6/(concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
-      <c r="AY6" s="69"/>
-      <c r="AZ6" s="69"/>
-      <c r="BA6" s="69"/>
-      <c r="BB6" s="66" t="e">
+      <c r="AY6" s="64"/>
+      <c r="AZ6" s="64"/>
+      <c r="BA6" s="64"/>
+      <c r="BB6" s="61" t="e">
         <f>AR6/concentrate_grade!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="BC6" s="66">
+      <c r="BC6" s="61">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -27289,7 +27279,7 @@
         <v>1523</v>
       </c>
       <c r="I7" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="K7" t="s">
         <v>1426</v>
@@ -27319,7 +27309,7 @@
         <v>920</v>
       </c>
       <c r="X7" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="Y7" s="18">
         <f>prod_table_raw!N24</f>
@@ -27334,7 +27324,7 @@
         <f t="shared" si="0"/>
         <v>1361446.483400204</v>
       </c>
-      <c r="AC7" s="72">
+      <c r="AC7" s="67">
         <f t="shared" si="2"/>
         <v>2.5829812302459567E-6</v>
       </c>
@@ -27424,7 +27414,7 @@
         <v>1523</v>
       </c>
       <c r="I8" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="J8" t="s">
         <v>1533</v>
@@ -27451,13 +27441,13 @@
         <v>373</v>
       </c>
       <c r="V8" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="W8" t="s">
         <v>1396</v>
       </c>
       <c r="X8" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="Y8" s="18">
         <f>prod_table_raw!N30</f>
@@ -27472,7 +27462,7 @@
         <f t="shared" si="0"/>
         <v>693306.25</v>
       </c>
-      <c r="AC8" s="72">
+      <c r="AC8" s="67">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -27533,110 +27523,110 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:55" s="66" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="64" t="s">
+    <row r="9" spans="1:55" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="59" t="s">
         <v>526</v>
       </c>
-      <c r="B9" s="66" t="s">
+      <c r="B9" s="61" t="s">
         <v>403</v>
       </c>
-      <c r="C9" s="66" t="s">
+      <c r="C9" s="61" t="s">
         <v>1371</v>
       </c>
-      <c r="D9" s="66" t="s">
+      <c r="D9" s="61" t="s">
         <v>405</v>
       </c>
-      <c r="E9" s="66" t="s">
+      <c r="E9" s="61" t="s">
         <v>437</v>
       </c>
-      <c r="F9" s="67" t="s">
+      <c r="F9" s="62" t="s">
         <v>540</v>
       </c>
-      <c r="G9" s="64" t="s">
+      <c r="G9" s="59" t="s">
         <v>411</v>
       </c>
-      <c r="H9" s="66" t="s">
+      <c r="H9" s="61" t="s">
         <v>1523</v>
       </c>
-      <c r="I9" s="66" t="s">
+      <c r="I9" s="61" t="s">
         <v>1411</v>
       </c>
-      <c r="K9" s="66" t="s">
+      <c r="K9" s="61" t="s">
         <v>1426</v>
       </c>
-      <c r="L9" s="66" t="s">
+      <c r="L9" s="61" t="s">
         <v>1508</v>
       </c>
-      <c r="M9" s="66">
+      <c r="M9" s="61">
         <v>3963061.6444813549</v>
       </c>
-      <c r="O9" s="66" t="s">
+      <c r="O9" s="61" t="s">
         <v>1113</v>
       </c>
-      <c r="Q9" s="66" t="s">
+      <c r="Q9" s="61" t="s">
         <v>1113</v>
       </c>
       <c r="R9" t="s">
         <v>1113</v>
       </c>
-      <c r="T9" s="66" t="s">
+      <c r="T9" s="61" t="s">
         <v>1113</v>
       </c>
-      <c r="U9" s="67" t="s">
+      <c r="U9" s="62" t="s">
         <v>551</v>
       </c>
-      <c r="V9" s="66" t="s">
-        <v>1552</v>
-      </c>
-      <c r="W9" s="66" t="s">
+      <c r="V9" s="61" t="s">
+        <v>1550</v>
+      </c>
+      <c r="W9" s="61" t="s">
         <v>1396</v>
       </c>
-      <c r="X9" s="66" t="s">
-        <v>1538</v>
-      </c>
-      <c r="Y9" s="64"/>
-      <c r="AB9" s="66">
+      <c r="X9" s="61" t="s">
+        <v>1536</v>
+      </c>
+      <c r="Y9" s="59"/>
+      <c r="AB9" s="61">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AC9" s="72"/>
+      <c r="AC9" s="67"/>
       <c r="AD9"/>
-      <c r="AF9" s="69"/>
-      <c r="AG9" s="69"/>
-      <c r="AH9" s="69">
+      <c r="AF9" s="64"/>
+      <c r="AG9" s="64"/>
+      <c r="AH9" s="64">
         <f>prod_table_raw!N31</f>
         <v>57900</v>
       </c>
-      <c r="AI9" s="69">
+      <c r="AI9" s="64">
         <f>prod_table_raw!N32</f>
         <v>38200</v>
       </c>
-      <c r="AJ9" s="69"/>
-      <c r="AK9" s="69"/>
-      <c r="AL9" s="69"/>
-      <c r="AM9" s="69"/>
-      <c r="AN9" s="69"/>
-      <c r="AO9" s="69"/>
-      <c r="AP9" s="69"/>
-      <c r="AQ9" s="69"/>
-      <c r="AR9" s="69"/>
-      <c r="AS9" s="65"/>
-      <c r="AT9" s="65"/>
-      <c r="AU9" s="66">
+      <c r="AJ9" s="64"/>
+      <c r="AK9" s="64"/>
+      <c r="AL9" s="64"/>
+      <c r="AM9" s="64"/>
+      <c r="AN9" s="64"/>
+      <c r="AO9" s="64"/>
+      <c r="AP9" s="64"/>
+      <c r="AQ9" s="64"/>
+      <c r="AR9" s="64"/>
+      <c r="AS9" s="60"/>
+      <c r="AT9" s="60"/>
+      <c r="AU9" s="61">
         <f>AK9/(concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
-      <c r="AV9" s="69"/>
-      <c r="AW9" s="66">
+      <c r="AV9" s="64"/>
+      <c r="AW9" s="61">
         <f>AM9/(concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
-      <c r="AX9" s="69"/>
-      <c r="AY9" s="69"/>
-      <c r="AZ9" s="69"/>
-      <c r="BA9" s="69"/>
-      <c r="BB9" s="69"/>
-      <c r="BC9" s="66">
+      <c r="AX9" s="64"/>
+      <c r="AY9" s="64"/>
+      <c r="AZ9" s="64"/>
+      <c r="BA9" s="64"/>
+      <c r="BB9" s="64"/>
+      <c r="BC9" s="61">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -27661,7 +27651,7 @@
         <v>1520</v>
       </c>
       <c r="I10" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="K10" t="s">
         <v>1426</v>
@@ -27700,7 +27690,7 @@
         <v>1076</v>
       </c>
       <c r="X10" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="Y10" s="18">
         <f>prod_table_raw!N36</f>
@@ -27715,7 +27705,7 @@
         <f t="shared" si="0"/>
         <v>6798652</v>
       </c>
-      <c r="AC10" s="72">
+      <c r="AC10" s="67">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -27808,7 +27798,7 @@
         <v>1523</v>
       </c>
       <c r="I11" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="J11" t="s">
         <v>1533</v>
@@ -27838,13 +27828,13 @@
         <v>373</v>
       </c>
       <c r="V11" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="W11" t="s">
         <v>1396</v>
       </c>
       <c r="X11" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="Y11" s="18">
         <f>prod_table_raw!N44</f>
@@ -27859,7 +27849,7 @@
         <f t="shared" si="0"/>
         <v>362100</v>
       </c>
-      <c r="AC11" s="72">
+      <c r="AC11" s="67">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -27940,7 +27930,7 @@
         <v>1520</v>
       </c>
       <c r="I12" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="K12" t="s">
         <v>1426</v>
@@ -27973,7 +27963,7 @@
         <v>1075</v>
       </c>
       <c r="X12" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="Y12" s="18">
         <f>prod_table_raw!N48</f>
@@ -27988,7 +27978,7 @@
         <f t="shared" si="0"/>
         <v>25434829.49413256</v>
       </c>
-      <c r="AC12" s="72">
+      <c r="AC12" s="67">
         <f t="shared" si="2"/>
         <v>9.4391280199330541E-7</v>
       </c>
@@ -28072,7 +28062,7 @@
         <v>1523</v>
       </c>
       <c r="I13" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="K13" t="s">
         <v>1418</v>
@@ -28105,7 +28095,7 @@
         <v>920</v>
       </c>
       <c r="X13" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="Y13" s="18">
         <f>prod_table_raw!N55</f>
@@ -28120,7 +28110,7 @@
         <f t="shared" si="0"/>
         <v>222624.22394914847</v>
       </c>
-      <c r="AC13" s="72">
+      <c r="AC13" s="67">
         <f t="shared" si="2"/>
         <v>1.2469515609205588E-5</v>
       </c>
@@ -28201,7 +28191,7 @@
         <v>1519</v>
       </c>
       <c r="I14" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="K14" t="s">
         <v>1418</v>
@@ -28231,7 +28221,7 @@
         <v>1075</v>
       </c>
       <c r="X14" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="Y14" s="18">
         <f>prod_table_raw!N62</f>
@@ -28246,7 +28236,7 @@
         <f t="shared" si="0"/>
         <v>1660992.2611000792</v>
       </c>
-      <c r="AC14" s="72">
+      <c r="AC14" s="67">
         <f t="shared" si="2"/>
         <v>4.6591811685240014E-6</v>
       </c>
@@ -28330,7 +28320,7 @@
         <v>1519</v>
       </c>
       <c r="I15" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="J15" t="s">
         <v>1533</v>
@@ -28366,7 +28356,7 @@
         <v>920</v>
       </c>
       <c r="X15" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="Y15" s="18">
         <f>prod_table_raw!N64</f>
@@ -28381,7 +28371,7 @@
         <f t="shared" si="0"/>
         <v>33244.875712953064</v>
       </c>
-      <c r="AC15" s="72">
+      <c r="AC15" s="67">
         <f t="shared" si="2"/>
         <v>3.7385184821409389E-6</v>
       </c>
@@ -28443,7 +28433,7 @@
       </c>
     </row>
     <row r="16" spans="1:55" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="58" t="s">
+      <c r="A16" s="53" t="s">
         <v>156</v>
       </c>
       <c r="C16" s="36" t="s">
@@ -28452,17 +28442,17 @@
       <c r="E16" s="36" t="s">
         <v>437</v>
       </c>
-      <c r="F16" s="59" t="s">
+      <c r="F16" s="54" t="s">
         <v>435</v>
       </c>
-      <c r="G16" s="58" t="s">
+      <c r="G16" s="53" t="s">
         <v>91</v>
       </c>
       <c r="H16" s="36" t="s">
         <v>1523</v>
       </c>
       <c r="I16" s="36" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="K16" s="36" t="s">
         <v>1423</v>
@@ -28485,7 +28475,7 @@
       <c r="T16" s="36" t="s">
         <v>1113</v>
       </c>
-      <c r="U16" s="59" t="s">
+      <c r="U16" s="54" t="s">
         <v>115</v>
       </c>
       <c r="V16" s="36" t="s">
@@ -28495,9 +28485,9 @@
         <v>920</v>
       </c>
       <c r="X16" s="36" t="s">
-        <v>1565</v>
-      </c>
-      <c r="Y16" s="58">
+        <v>1563</v>
+      </c>
+      <c r="Y16" s="53">
         <f>prod_table_raw!N70</f>
         <v>457000</v>
       </c>
@@ -28509,7 +28499,7 @@
         <f t="shared" si="0"/>
         <v>456998.54638744897</v>
       </c>
-      <c r="AC16" s="72">
+      <c r="AC16" s="67">
         <f t="shared" si="2"/>
         <v>3.1807714464341536E-6</v>
       </c>
@@ -28517,7 +28507,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AE16" s="60">
+      <c r="AE16" s="55">
         <f t="shared" si="4"/>
         <v>0.99999681921843619</v>
       </c>
@@ -28598,7 +28588,7 @@
         <v>1523</v>
       </c>
       <c r="I17" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="J17" t="s">
         <v>1533</v>
@@ -28631,7 +28621,7 @@
         <v>1396</v>
       </c>
       <c r="X17" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="Y17" s="18">
         <f>prod_table_raw!N73</f>
@@ -28646,7 +28636,7 @@
         <f t="shared" si="0"/>
         <v>553033</v>
       </c>
-      <c r="AC17" s="72">
+      <c r="AC17" s="67">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -28727,7 +28717,7 @@
         <v>1523</v>
       </c>
       <c r="I18" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="J18" t="s">
         <v>1533</v>
@@ -28757,13 +28747,13 @@
         <v>373</v>
       </c>
       <c r="V18" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="W18" t="s">
         <v>1396</v>
       </c>
       <c r="X18" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="Y18" s="18">
         <f>prod_table_raw!N76</f>
@@ -28778,7 +28768,7 @@
         <f t="shared" si="0"/>
         <v>566337.5</v>
       </c>
-      <c r="AC18" s="72">
+      <c r="AC18" s="67">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -28859,7 +28849,7 @@
         <v>1519</v>
       </c>
       <c r="I19" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="K19" t="s">
         <v>1425</v>
@@ -28892,10 +28882,10 @@
         <v>1113</v>
       </c>
       <c r="W19" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
       <c r="X19" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="Y19" s="18">
         <f>prod_table_raw!N80</f>
@@ -28910,7 +28900,7 @@
         <f t="shared" si="0"/>
         <v>29813563.015247058</v>
       </c>
-      <c r="AC19" s="72">
+      <c r="AC19" s="67">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -28991,7 +28981,7 @@
         <v>64</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="J20" t="s">
         <v>1529</v>
@@ -29027,10 +29017,10 @@
         <v>1113</v>
       </c>
       <c r="W20" t="s">
-        <v>1548</v>
+        <v>1546</v>
       </c>
       <c r="X20" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="Y20" s="18">
         <f>prod_table_raw!N86</f>
@@ -29048,7 +29038,7 @@
         <f t="shared" si="0"/>
         <v>2886792.7316552154</v>
       </c>
-      <c r="AC20" s="72">
+      <c r="AC20" s="67">
         <f t="shared" si="2"/>
         <v>1.5499323705853058E-6</v>
       </c>
@@ -29132,7 +29122,7 @@
         <v>1523</v>
       </c>
       <c r="I21" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="K21" t="s">
         <v>1426</v>
@@ -29171,7 +29161,7 @@
         <v>920</v>
       </c>
       <c r="X21" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="Y21" s="18">
         <f>prod_table_raw!N91</f>
@@ -29186,7 +29176,7 @@
         <f t="shared" si="0"/>
         <v>1266004.5234763699</v>
       </c>
-      <c r="AC21" s="72">
+      <c r="AC21" s="67">
         <f t="shared" si="2"/>
         <v>3.5359334966039271E-6</v>
       </c>
@@ -29267,7 +29257,7 @@
         <v>1520</v>
       </c>
       <c r="I22" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="K22" t="s">
         <v>1425</v>
@@ -29303,10 +29293,10 @@
         <v>1113</v>
       </c>
       <c r="W22" t="s">
-        <v>1550</v>
+        <v>1548</v>
       </c>
       <c r="X22" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="Y22" s="18">
         <f>prod_table_raw!N93</f>
@@ -29321,7 +29311,7 @@
         <f t="shared" si="0"/>
         <v>17064901.960784312</v>
       </c>
-      <c r="AC22" s="72">
+      <c r="AC22" s="67">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -29385,107 +29375,107 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:55" s="66" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="64" t="s">
+    <row r="23" spans="1:55" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="59" t="s">
         <v>494</v>
       </c>
-      <c r="B23" s="66" t="s">
+      <c r="B23" s="61" t="s">
         <v>493</v>
       </c>
-      <c r="C23" s="66" t="s">
+      <c r="C23" s="61" t="s">
         <v>495</v>
       </c>
-      <c r="D23" s="66" t="s">
+      <c r="D23" s="61" t="s">
         <v>492</v>
       </c>
-      <c r="E23" s="66" t="s">
+      <c r="E23" s="61" t="s">
         <v>436</v>
       </c>
-      <c r="F23" s="67" t="s">
+      <c r="F23" s="62" t="s">
         <v>540</v>
       </c>
-      <c r="G23" s="64" t="s">
+      <c r="G23" s="59" t="s">
         <v>29</v>
       </c>
-      <c r="H23" s="66" t="s">
+      <c r="H23" s="61" t="s">
         <v>1523</v>
       </c>
-      <c r="I23" s="66" t="s">
+      <c r="I23" s="61" t="s">
         <v>1509</v>
       </c>
-      <c r="K23" s="66" t="s">
+      <c r="K23" s="61" t="s">
         <v>1418</v>
       </c>
-      <c r="L23" s="66" t="s">
+      <c r="L23" s="61" t="s">
         <v>1508</v>
       </c>
-      <c r="O23" s="66" t="s">
+      <c r="O23" s="61" t="s">
         <v>1113</v>
       </c>
-      <c r="P23" s="66" t="s">
+      <c r="P23" s="61" t="s">
         <v>1113</v>
       </c>
-      <c r="Q23" s="66" t="s">
+      <c r="Q23" s="61" t="s">
         <v>1113</v>
       </c>
       <c r="R23" t="s">
         <v>1113</v>
       </c>
-      <c r="T23" s="66" t="s">
+      <c r="T23" s="61" t="s">
         <v>1113</v>
       </c>
-      <c r="U23" s="67" t="s">
+      <c r="U23" s="62" t="s">
         <v>548</v>
       </c>
-      <c r="V23" s="66" t="s">
+      <c r="V23" s="61" t="s">
         <v>1089</v>
       </c>
-      <c r="W23" s="66" t="s">
+      <c r="W23" s="61" t="s">
         <v>918</v>
       </c>
-      <c r="Y23" s="64"/>
-      <c r="AB23" s="66">
+      <c r="Y23" s="59"/>
+      <c r="AB23" s="61">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AC23" s="72"/>
+      <c r="AC23" s="67"/>
       <c r="AD23"/>
-      <c r="AF23" s="69"/>
-      <c r="AG23" s="69"/>
-      <c r="AH23" s="69"/>
-      <c r="AI23" s="69"/>
-      <c r="AJ23" s="69"/>
-      <c r="AK23" s="69"/>
-      <c r="AL23" s="69"/>
-      <c r="AM23" s="69"/>
-      <c r="AN23" s="69"/>
-      <c r="AO23" s="69"/>
-      <c r="AP23" s="69"/>
-      <c r="AQ23" s="69"/>
-      <c r="AR23" s="69"/>
-      <c r="AS23" s="65">
+      <c r="AF23" s="64"/>
+      <c r="AG23" s="64"/>
+      <c r="AH23" s="64"/>
+      <c r="AI23" s="64"/>
+      <c r="AJ23" s="64"/>
+      <c r="AK23" s="64"/>
+      <c r="AL23" s="64"/>
+      <c r="AM23" s="64"/>
+      <c r="AN23" s="64"/>
+      <c r="AO23" s="64"/>
+      <c r="AP23" s="64"/>
+      <c r="AQ23" s="64"/>
+      <c r="AR23" s="64"/>
+      <c r="AS23" s="60">
         <f>AH23/(concentrate_grade!$F$4/100)</f>
         <v>0</v>
       </c>
-      <c r="AT23" s="65">
+      <c r="AT23" s="60">
         <f>AI23/(concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
-      <c r="AU23" s="66">
+      <c r="AU23" s="61">
         <f>AK23/(concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
-      <c r="AV23" s="69"/>
-      <c r="AW23" s="66">
+      <c r="AV23" s="64"/>
+      <c r="AW23" s="61">
         <f>AM23/(concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
-      <c r="AX23" s="69"/>
-      <c r="AY23" s="69"/>
-      <c r="AZ23" s="69"/>
-      <c r="BA23" s="69"/>
-      <c r="BB23" s="69"/>
-      <c r="BC23" s="66">
+      <c r="AX23" s="64"/>
+      <c r="AY23" s="64"/>
+      <c r="AZ23" s="64"/>
+      <c r="BA23" s="64"/>
+      <c r="BB23" s="64"/>
+      <c r="BC23" s="61">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -29510,7 +29500,7 @@
         <v>1523</v>
       </c>
       <c r="I24" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="K24" t="s">
         <v>1418</v>
@@ -29540,7 +29530,7 @@
         <v>920</v>
       </c>
       <c r="X24" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="Y24" s="18">
         <f>prod_table_raw!N105</f>
@@ -29555,7 +29545,7 @@
         <f t="shared" si="0"/>
         <v>439003.82959193876</v>
       </c>
-      <c r="AC24" s="72">
+      <c r="AC24" s="67">
         <f t="shared" si="2"/>
         <v>9.4996174585075685E-6</v>
       </c>
@@ -29639,7 +29629,7 @@
         <v>1519</v>
       </c>
       <c r="I25" t="s">
-        <v>1563</v>
+        <v>1561</v>
       </c>
       <c r="L25" t="s">
         <v>1506</v>
@@ -29666,7 +29656,7 @@
         <v>1459</v>
       </c>
       <c r="X25" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="Y25" s="18">
         <f>prod_table_raw!N110</f>
@@ -29681,7 +29671,7 @@
         <f t="shared" si="0"/>
         <v>122587.33333333333</v>
       </c>
-      <c r="AC25" s="72">
+      <c r="AC25" s="67">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -29768,7 +29758,7 @@
         <v>1523</v>
       </c>
       <c r="I26" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
       <c r="K26" t="s">
         <v>1534</v>
@@ -29795,13 +29785,13 @@
         <v>207</v>
       </c>
       <c r="V26" t="s">
-        <v>1503</v>
+        <v>1113</v>
       </c>
       <c r="W26" t="s">
-        <v>1547</v>
+        <v>1545</v>
       </c>
       <c r="X26" t="s">
-        <v>1576</v>
+        <v>1574</v>
       </c>
       <c r="Y26" s="18">
         <f>prod_table_raw!N116</f>
@@ -29816,7 +29806,7 @@
         <f t="shared" si="0"/>
         <v>1187466.6666666667</v>
       </c>
-      <c r="AC26" s="72">
+      <c r="AC26" s="67">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -29900,10 +29890,10 @@
         <v>78</v>
       </c>
       <c r="I27" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="K27" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="L27" t="s">
         <v>1516</v>
@@ -29927,13 +29917,13 @@
         <v>65</v>
       </c>
       <c r="V27" t="s">
-        <v>1502</v>
+        <v>1113</v>
       </c>
       <c r="W27" t="s">
         <v>1075</v>
       </c>
       <c r="X27" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="Y27" s="18">
         <f>prod_table_raw!N120</f>
@@ -29948,7 +29938,7 @@
         <f t="shared" si="0"/>
         <v>191146.77982239029</v>
       </c>
-      <c r="AC27" s="72">
+      <c r="AC27" s="67">
         <f t="shared" si="2"/>
         <v>6.3834181351302525E-6</v>
       </c>
@@ -30032,7 +30022,7 @@
         <v>1519</v>
       </c>
       <c r="I28" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="J28" t="s">
         <v>1532</v>
@@ -30071,7 +30061,7 @@
         <v>922</v>
       </c>
       <c r="X28" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
       <c r="Y28" s="18">
         <f>prod_table_raw!N124</f>
@@ -30083,7 +30073,7 @@
         <f t="shared" si="0"/>
         <v>3798000</v>
       </c>
-      <c r="AC28" s="72">
+      <c r="AC28" s="67">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -30170,10 +30160,10 @@
         <v>1523</v>
       </c>
       <c r="I29" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="K29" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="L29" t="s">
         <v>1416</v>
@@ -30206,7 +30196,7 @@
         <v>1075</v>
       </c>
       <c r="X29" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="Y29" s="18">
         <f>prod_table_raw!N134</f>
@@ -30221,7 +30211,7 @@
         <f t="shared" si="0"/>
         <v>838411.067179278</v>
       </c>
-      <c r="AC29" s="72">
+      <c r="AC29" s="67">
         <f t="shared" si="2"/>
         <v>9.4616423553602378E-6</v>
       </c>
@@ -30305,7 +30295,7 @@
         <v>1523</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="J30" t="s">
         <v>1530</v>
@@ -30341,10 +30331,10 @@
         <v>1113</v>
       </c>
       <c r="W30" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="X30" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="Y30" s="18">
         <f>prod_table_raw!N139</f>
@@ -30362,7 +30352,7 @@
         <f t="shared" si="0"/>
         <v>1477492.1188132097</v>
       </c>
-      <c r="AC30" s="72">
+      <c r="AC30" s="67">
         <f t="shared" si="2"/>
         <v>6.5287397870836583E-6</v>
       </c>
@@ -30432,107 +30422,107 @@
         <v>9.8029027903061134</v>
       </c>
     </row>
-    <row r="31" spans="1:55" s="66" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="64" t="s">
+    <row r="31" spans="1:55" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="59" t="s">
         <v>534</v>
       </c>
-      <c r="C31" s="66" t="s">
+      <c r="C31" s="61" t="s">
         <v>535</v>
       </c>
-      <c r="E31" s="66" t="s">
+      <c r="E31" s="61" t="s">
         <v>442</v>
       </c>
-      <c r="F31" s="67" t="s">
+      <c r="F31" s="62" t="s">
         <v>540</v>
       </c>
-      <c r="G31" s="64" t="s">
+      <c r="G31" s="59" t="s">
         <v>71</v>
       </c>
-      <c r="H31" s="66" t="s">
+      <c r="H31" s="61" t="s">
         <v>1523</v>
       </c>
-      <c r="I31" s="66" t="s">
+      <c r="I31" s="61" t="s">
         <v>1159</v>
       </c>
-      <c r="K31" s="66" t="s">
+      <c r="K31" s="61" t="s">
         <v>1426</v>
       </c>
-      <c r="L31" s="66" t="s">
+      <c r="L31" s="61" t="s">
         <v>1508</v>
       </c>
-      <c r="M31" s="66">
+      <c r="M31" s="61">
         <v>681889.99643018574</v>
       </c>
-      <c r="O31" s="66" t="s">
+      <c r="O31" s="61" t="s">
         <v>1113</v>
       </c>
-      <c r="P31" s="66" t="s">
+      <c r="P31" s="61" t="s">
         <v>1113</v>
       </c>
-      <c r="Q31" s="66" t="s">
+      <c r="Q31" s="61" t="s">
         <v>1113</v>
       </c>
       <c r="R31" t="s">
         <v>1113</v>
       </c>
-      <c r="T31" s="66" t="s">
+      <c r="T31" s="61" t="s">
         <v>1113</v>
       </c>
-      <c r="U31" s="67" t="s">
+      <c r="U31" s="62" t="s">
         <v>326</v>
       </c>
-      <c r="V31" s="66" t="s">
+      <c r="V31" s="61" t="s">
+        <v>1117</v>
+      </c>
+      <c r="W31" s="61" t="s">
+        <v>919</v>
+      </c>
+      <c r="X31" s="61" t="s">
         <v>1537</v>
       </c>
-      <c r="W31" s="66" t="s">
-        <v>919</v>
-      </c>
-      <c r="X31" s="66" t="s">
-        <v>1539</v>
-      </c>
-      <c r="Y31" s="64"/>
-      <c r="AB31" s="66">
+      <c r="Y31" s="59"/>
+      <c r="AB31" s="61">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AC31" s="72"/>
+      <c r="AC31" s="67"/>
       <c r="AD31"/>
-      <c r="AF31" s="69"/>
-      <c r="AG31" s="69"/>
-      <c r="AH31" s="69"/>
-      <c r="AI31" s="69">
+      <c r="AF31" s="64"/>
+      <c r="AG31" s="64"/>
+      <c r="AH31" s="64"/>
+      <c r="AI31" s="64">
         <f>prod_table_raw!N145</f>
         <v>27700</v>
       </c>
-      <c r="AJ31" s="69"/>
-      <c r="AK31" s="69"/>
-      <c r="AL31" s="69"/>
-      <c r="AM31" s="69"/>
-      <c r="AN31" s="69"/>
-      <c r="AO31" s="69"/>
-      <c r="AP31" s="69"/>
-      <c r="AQ31" s="69"/>
-      <c r="AR31" s="69"/>
-      <c r="AS31" s="65">
+      <c r="AJ31" s="64"/>
+      <c r="AK31" s="64"/>
+      <c r="AL31" s="64"/>
+      <c r="AM31" s="64"/>
+      <c r="AN31" s="64"/>
+      <c r="AO31" s="64"/>
+      <c r="AP31" s="64"/>
+      <c r="AQ31" s="64"/>
+      <c r="AR31" s="64"/>
+      <c r="AS31" s="60">
         <f>AH31/(concentrate_grade!$F$4/100)</f>
         <v>0</v>
       </c>
-      <c r="AT31" s="65"/>
-      <c r="AU31" s="66">
+      <c r="AT31" s="60"/>
+      <c r="AU31" s="61">
         <f>AK31/(concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
-      <c r="AV31" s="69"/>
-      <c r="AW31" s="66">
+      <c r="AV31" s="64"/>
+      <c r="AW31" s="61">
         <f>AM31/(concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
-      <c r="AX31" s="69"/>
-      <c r="AY31" s="69"/>
-      <c r="AZ31" s="69"/>
-      <c r="BA31" s="69"/>
-      <c r="BB31" s="69"/>
-      <c r="BC31" s="66">
+      <c r="AX31" s="64"/>
+      <c r="AY31" s="64"/>
+      <c r="AZ31" s="64"/>
+      <c r="BA31" s="64"/>
+      <c r="BB31" s="64"/>
+      <c r="BC31" s="61">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -30557,7 +30547,7 @@
         <v>1523</v>
       </c>
       <c r="I32" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="J32" t="s">
         <v>1528</v>
@@ -30599,7 +30589,7 @@
         <v>920</v>
       </c>
       <c r="X32" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="Y32" s="18">
         <f>prod_table_raw!N146</f>
@@ -30614,7 +30604,7 @@
         <f t="shared" si="0"/>
         <v>441580.74669553828</v>
       </c>
-      <c r="AC32" s="72">
+      <c r="AC32" s="67">
         <f t="shared" si="2"/>
         <v>1.6425501738576894E-5</v>
       </c>
@@ -30695,7 +30685,7 @@
         <v>1523</v>
       </c>
       <c r="I33" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="K33" t="s">
         <v>1427</v>
@@ -30722,13 +30712,13 @@
         <v>65</v>
       </c>
       <c r="V33" t="s">
-        <v>1503</v>
+        <v>1113</v>
       </c>
       <c r="W33" t="s">
         <v>920</v>
       </c>
       <c r="X33" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="Y33" s="18">
         <f>prod_table_raw!N150</f>
@@ -30743,7 +30733,7 @@
         <f t="shared" si="0"/>
         <v>1165549.9526372449</v>
       </c>
-      <c r="AC33" s="72">
+      <c r="AC33" s="67">
         <f t="shared" si="2"/>
         <v>8.9859882158913749E-7</v>
       </c>
@@ -30804,76 +30794,76 @@
         <v>1.0473627551020408</v>
       </c>
     </row>
-    <row r="34" spans="1:55" s="66" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="64" t="s">
+    <row r="34" spans="1:55" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="59" t="s">
         <v>249</v>
       </c>
-      <c r="C34" s="66" t="s">
+      <c r="C34" s="61" t="s">
         <v>251</v>
       </c>
-      <c r="E34" s="66" t="s">
+      <c r="E34" s="61" t="s">
         <v>434</v>
       </c>
-      <c r="F34" s="67" t="s">
+      <c r="F34" s="62" t="s">
         <v>435</v>
       </c>
-      <c r="G34" s="64" t="s">
+      <c r="G34" s="59" t="s">
         <v>57</v>
       </c>
-      <c r="H34" s="66" t="s">
+      <c r="H34" s="61" t="s">
         <v>1524</v>
       </c>
-      <c r="I34" s="66" t="s">
+      <c r="I34" s="61" t="s">
         <v>1191</v>
       </c>
-      <c r="J34" s="66" t="s">
+      <c r="J34" s="61" t="s">
         <v>1533</v>
       </c>
-      <c r="K34" s="66" t="s">
+      <c r="K34" s="61" t="s">
         <v>1420</v>
       </c>
-      <c r="L34" s="66" t="s">
+      <c r="L34" s="61" t="s">
         <v>1508</v>
       </c>
-      <c r="O34" s="66" t="s">
+      <c r="O34" s="61" t="s">
         <v>1113</v>
       </c>
-      <c r="P34" s="66" t="s">
+      <c r="P34" s="61" t="s">
         <v>1113</v>
       </c>
-      <c r="Q34" s="66" t="s">
+      <c r="Q34" s="61" t="s">
         <v>1113</v>
       </c>
       <c r="R34" t="s">
         <v>1113</v>
       </c>
-      <c r="S34" s="66" t="s">
+      <c r="S34" s="61" t="s">
         <v>1113</v>
       </c>
-      <c r="T34" s="66" t="s">
+      <c r="T34" s="61" t="s">
         <v>1113</v>
       </c>
-      <c r="U34" s="67" t="s">
+      <c r="U34" s="62" t="s">
         <v>149</v>
       </c>
-      <c r="V34" s="66" t="s">
-        <v>1542</v>
-      </c>
-      <c r="W34" s="66" t="s">
+      <c r="V34" s="61" t="s">
+        <v>1540</v>
+      </c>
+      <c r="W34" s="61" t="s">
         <v>1068</v>
       </c>
-      <c r="X34" s="66" t="s">
+      <c r="X34" s="61" t="s">
         <v>513</v>
       </c>
-      <c r="Y34" s="64">
+      <c r="Y34" s="59">
         <f>prod_table_raw!N151</f>
         <v>5600000</v>
       </c>
-      <c r="AB34" s="66">
+      <c r="AB34" s="61">
         <f t="shared" ref="AB34:AB65" si="7">Y34-Z34-AA34</f>
         <v>5600000</v>
       </c>
-      <c r="AC34" s="72">
+      <c r="AC34" s="67">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -30881,51 +30871,51 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AE34" s="68">
+      <c r="AE34" s="63">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="AF34" s="69"/>
-      <c r="AG34" s="69"/>
-      <c r="AH34" s="69"/>
-      <c r="AI34" s="69"/>
-      <c r="AJ34" s="69"/>
-      <c r="AK34" s="69"/>
-      <c r="AL34" s="69"/>
-      <c r="AM34" s="69"/>
-      <c r="AN34" s="69"/>
-      <c r="AO34" s="69"/>
-      <c r="AP34" s="69"/>
-      <c r="AQ34" s="69"/>
-      <c r="AR34" s="69"/>
-      <c r="AS34" s="66">
+      <c r="AF34" s="64"/>
+      <c r="AG34" s="64"/>
+      <c r="AH34" s="64"/>
+      <c r="AI34" s="64"/>
+      <c r="AJ34" s="64"/>
+      <c r="AK34" s="64"/>
+      <c r="AL34" s="64"/>
+      <c r="AM34" s="64"/>
+      <c r="AN34" s="64"/>
+      <c r="AO34" s="64"/>
+      <c r="AP34" s="64"/>
+      <c r="AQ34" s="64"/>
+      <c r="AR34" s="64"/>
+      <c r="AS34" s="61">
         <f>AH34/(concentrate_grade!$F$4/100)</f>
         <v>0</v>
       </c>
-      <c r="AT34" s="66">
+      <c r="AT34" s="61">
         <f>AI34/(concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
-      <c r="AU34" s="66">
+      <c r="AU34" s="61">
         <f>AK34/(concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
-      <c r="AV34" s="66">
+      <c r="AV34" s="61">
         <f>AL34/(concentrate_grade!$F$9/100)</f>
         <v>0</v>
       </c>
-      <c r="AW34" s="66">
+      <c r="AW34" s="61">
         <f>AM34/(concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
-      <c r="AY34" s="69"/>
-      <c r="AZ34" s="69"/>
-      <c r="BA34" s="69"/>
-      <c r="BB34" s="66" t="e">
+      <c r="AY34" s="64"/>
+      <c r="AZ34" s="64"/>
+      <c r="BA34" s="64"/>
+      <c r="BB34" s="61" t="e">
         <f>AR34/concentrate_grade!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="BC34" s="66">
+      <c r="BC34" s="61">
         <f t="shared" ref="BC34:BC66" si="8">Z34</f>
         <v>0</v>
       </c>
@@ -30950,7 +30940,7 @@
         <v>1523</v>
       </c>
       <c r="I35" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="J35" t="s">
         <v>1532</v>
@@ -30980,13 +30970,13 @@
         <v>271</v>
       </c>
       <c r="V35" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="W35" t="s">
         <v>1422</v>
       </c>
       <c r="X35" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="Y35" s="18">
         <f>prod_table_raw!N157</f>
@@ -30998,7 +30988,7 @@
         <f t="shared" si="7"/>
         <v>317660</v>
       </c>
-      <c r="AC35" s="72">
+      <c r="AC35" s="67">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -31076,7 +31066,7 @@
         <v>1519</v>
       </c>
       <c r="I36" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="K36" t="s">
         <v>1426</v>
@@ -31109,7 +31099,7 @@
         <v>1075</v>
       </c>
       <c r="X36" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="Y36" s="18">
         <f>prod_table_raw!N163</f>
@@ -31124,7 +31114,7 @@
         <f t="shared" si="7"/>
         <v>1918130.58586317</v>
       </c>
-      <c r="AC36" s="72">
+      <c r="AC36" s="67">
         <f t="shared" si="2"/>
         <v>6.4719558604869089E-6</v>
       </c>
@@ -31208,7 +31198,7 @@
         <v>1519</v>
       </c>
       <c r="I37" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="K37" t="s">
         <v>1425</v>
@@ -31241,10 +31231,10 @@
         <v>1113</v>
       </c>
       <c r="W37" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="X37" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="Y37" s="18">
         <f>prod_table_raw!N175</f>
@@ -31259,7 +31249,7 @@
         <f t="shared" si="7"/>
         <v>21586466.305653334</v>
       </c>
-      <c r="AC37" s="72">
+      <c r="AC37" s="67">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -31343,7 +31333,7 @@
         <v>1519</v>
       </c>
       <c r="I38" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="K38" t="s">
         <v>1426</v>
@@ -31379,10 +31369,10 @@
         <v>1113</v>
       </c>
       <c r="W38" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="X38" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="Y38" s="18">
         <f>prod_table_raw!N179</f>
@@ -31397,7 +31387,7 @@
         <f t="shared" si="7"/>
         <v>5902660.5638666665</v>
       </c>
-      <c r="AC38" s="72">
+      <c r="AC38" s="67">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -31481,7 +31471,7 @@
         <v>1519</v>
       </c>
       <c r="I39" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="K39" t="s">
         <v>1426</v>
@@ -31511,7 +31501,7 @@
         <v>920</v>
       </c>
       <c r="X39" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="Y39" s="18">
         <f>prod_table_raw!N183</f>
@@ -31526,7 +31516,7 @@
         <f t="shared" si="7"/>
         <v>1027994.2871122449</v>
       </c>
-      <c r="AC39" s="72">
+      <c r="AC39" s="67">
         <f t="shared" si="2"/>
         <v>5.5572838084650201E-6</v>
       </c>
@@ -31607,7 +31597,7 @@
         <v>1522</v>
       </c>
       <c r="I40" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
       <c r="K40" t="s">
         <v>1425</v>
@@ -31637,10 +31627,10 @@
         <v>1113</v>
       </c>
       <c r="W40" t="s">
-        <v>1546</v>
+        <v>1544</v>
       </c>
       <c r="X40" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="Y40" s="18">
         <f>prod_table_raw!N189</f>
@@ -31655,7 +31645,7 @@
         <f t="shared" si="7"/>
         <v>2993332.4640000002</v>
       </c>
-      <c r="AC40" s="72">
+      <c r="AC40" s="67">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -31745,7 +31735,7 @@
         <v>1523</v>
       </c>
       <c r="I41" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="J41" t="s">
         <v>1533</v>
@@ -31778,7 +31768,7 @@
         <v>1396</v>
       </c>
       <c r="X41" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="Y41" s="18">
         <f>prod_table_raw!N194</f>
@@ -31793,7 +31783,7 @@
         <f t="shared" si="7"/>
         <v>320160</v>
       </c>
-      <c r="AC41" s="72">
+      <c r="AC41" s="67">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -31848,225 +31838,225 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:55" s="66" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="64" t="s">
+    <row r="42" spans="1:55" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="59" t="s">
         <v>311</v>
       </c>
-      <c r="C42" s="66" t="s">
+      <c r="C42" s="61" t="s">
         <v>313</v>
       </c>
-      <c r="E42" s="66" t="s">
+      <c r="E42" s="61" t="s">
         <v>436</v>
       </c>
-      <c r="F42" s="67" t="s">
+      <c r="F42" s="62" t="s">
         <v>435</v>
       </c>
-      <c r="G42" s="64" t="s">
+      <c r="G42" s="59" t="s">
         <v>64</v>
       </c>
-      <c r="H42" s="66" t="s">
+      <c r="H42" s="61" t="s">
         <v>1523</v>
       </c>
-      <c r="I42" s="66" t="s">
+      <c r="I42" s="61" t="s">
         <v>1510</v>
       </c>
-      <c r="K42" s="66" t="s">
+      <c r="K42" s="61" t="s">
         <v>1426</v>
       </c>
-      <c r="L42" s="66" t="s">
+      <c r="L42" s="61" t="s">
         <v>1508</v>
       </c>
-      <c r="M42" s="66">
+      <c r="M42" s="61">
         <v>2323252.9267690452</v>
       </c>
-      <c r="O42" s="66" t="s">
+      <c r="O42" s="61" t="s">
         <v>1113</v>
       </c>
-      <c r="P42" s="66" t="s">
+      <c r="P42" s="61" t="s">
         <v>1113</v>
       </c>
-      <c r="Q42" s="66" t="s">
+      <c r="Q42" s="61" t="s">
         <v>1113</v>
       </c>
       <c r="R42" t="s">
         <v>1113</v>
       </c>
-      <c r="S42" s="66" t="s">
+      <c r="S42" s="61" t="s">
         <v>1113</v>
       </c>
-      <c r="T42" s="66" t="s">
+      <c r="T42" s="61" t="s">
         <v>1113</v>
       </c>
-      <c r="U42" s="67" t="s">
+      <c r="U42" s="62" t="s">
         <v>309</v>
       </c>
-      <c r="V42" s="66" t="s">
-        <v>1564</v>
-      </c>
-      <c r="W42" s="66" t="s">
+      <c r="V42" s="61" t="s">
+        <v>1562</v>
+      </c>
+      <c r="W42" s="61" t="s">
         <v>1395</v>
       </c>
-      <c r="X42" s="66" t="s">
-        <v>1574</v>
-      </c>
-      <c r="Y42" s="64">
+      <c r="X42" s="61" t="s">
+        <v>1572</v>
+      </c>
+      <c r="Y42" s="59">
         <f>prod_table_raw!N195</f>
         <v>2200000</v>
       </c>
-      <c r="AA42" s="66" t="e">
+      <c r="AA42" s="61" t="e">
         <f>AR42/(concentrate_grade!#REF!/100)</f>
         <v>#REF!</v>
       </c>
-      <c r="AB42" s="66" t="e">
+      <c r="AB42" s="61" t="e">
         <f t="shared" si="7"/>
         <v>#REF!</v>
       </c>
-      <c r="AC42" s="72">
+      <c r="AC42" s="67">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AD42"/>
-      <c r="AE42" s="68" t="e">
+      <c r="AE42" s="63" t="e">
         <f t="shared" si="6"/>
         <v>#REF!</v>
       </c>
-      <c r="AF42" s="69"/>
-      <c r="AG42" s="69"/>
-      <c r="AH42" s="69"/>
-      <c r="AI42" s="69"/>
-      <c r="AJ42" s="69"/>
-      <c r="AK42" s="69"/>
-      <c r="AL42" s="69"/>
-      <c r="AM42" s="69"/>
-      <c r="AN42" s="69"/>
-      <c r="AO42" s="69"/>
-      <c r="AP42" s="69"/>
-      <c r="AQ42" s="69"/>
-      <c r="AR42" s="69">
+      <c r="AF42" s="64"/>
+      <c r="AG42" s="64"/>
+      <c r="AH42" s="64"/>
+      <c r="AI42" s="64"/>
+      <c r="AJ42" s="64"/>
+      <c r="AK42" s="64"/>
+      <c r="AL42" s="64"/>
+      <c r="AM42" s="64"/>
+      <c r="AN42" s="64"/>
+      <c r="AO42" s="64"/>
+      <c r="AP42" s="64"/>
+      <c r="AQ42" s="64"/>
+      <c r="AR42" s="64">
         <f>prod_table_raw!N196</f>
         <v>6568.95</v>
       </c>
-      <c r="AS42" s="66">
+      <c r="AS42" s="61">
         <f>AH42/(concentrate_grade!$F$4/100)</f>
         <v>0</v>
       </c>
-      <c r="AT42" s="66">
+      <c r="AT42" s="61">
         <f>AI42/(concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
-      <c r="AU42" s="66">
+      <c r="AU42" s="61">
         <f>AK42/(concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
-      <c r="AV42" s="66">
+      <c r="AV42" s="61">
         <f>AL42/(concentrate_grade!$F$9/100)</f>
         <v>0</v>
       </c>
-      <c r="AW42" s="66">
+      <c r="AW42" s="61">
         <f>AM42/(concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
-      <c r="AY42" s="69"/>
-      <c r="AZ42" s="69"/>
-      <c r="BA42" s="69"/>
-      <c r="BB42" s="66" t="e">
+      <c r="AY42" s="64"/>
+      <c r="AZ42" s="64"/>
+      <c r="BA42" s="64"/>
+      <c r="BB42" s="61" t="e">
         <f>AR42/concentrate_grade!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="BC42" s="66">
+      <c r="BC42" s="61">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:55" s="66" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="64" t="s">
+    <row r="43" spans="1:55" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="59" t="s">
         <v>316</v>
       </c>
-      <c r="C43" s="66" t="s">
+      <c r="C43" s="61" t="s">
         <v>318</v>
       </c>
-      <c r="E43" s="66" t="s">
+      <c r="E43" s="61" t="s">
         <v>436</v>
       </c>
-      <c r="F43" s="67" t="s">
+      <c r="F43" s="62" t="s">
         <v>540</v>
       </c>
-      <c r="G43" s="64" t="s">
+      <c r="G43" s="59" t="s">
         <v>1399</v>
       </c>
-      <c r="H43" s="66" t="s">
+      <c r="H43" s="61" t="s">
         <v>1523</v>
       </c>
-      <c r="I43" s="66" t="s">
+      <c r="I43" s="61" t="s">
         <v>1511</v>
       </c>
-      <c r="P43" s="66" t="s">
+      <c r="P43" s="61" t="s">
         <v>1113</v>
       </c>
-      <c r="Q43" s="66" t="s">
+      <c r="Q43" s="61" t="s">
         <v>1113</v>
       </c>
       <c r="R43" t="s">
         <v>1113</v>
       </c>
-      <c r="T43" s="66" t="s">
+      <c r="T43" s="61" t="s">
         <v>1113</v>
       </c>
-      <c r="U43" s="67" t="s">
+      <c r="U43" s="62" t="s">
         <v>315</v>
       </c>
-      <c r="V43" s="66" t="s">
+      <c r="V43" s="61" t="s">
         <v>1089</v>
       </c>
-      <c r="W43" s="66" t="s">
+      <c r="W43" s="61" t="s">
         <v>1395</v>
       </c>
-      <c r="Y43" s="64"/>
-      <c r="AB43" s="66">
+      <c r="Y43" s="59"/>
+      <c r="AB43" s="61">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AC43" s="72"/>
+      <c r="AC43" s="67"/>
       <c r="AD43"/>
-      <c r="AF43" s="69"/>
-      <c r="AG43" s="69"/>
-      <c r="AH43" s="69"/>
-      <c r="AI43" s="69"/>
-      <c r="AJ43" s="69"/>
-      <c r="AK43" s="69"/>
-      <c r="AL43" s="69"/>
-      <c r="AM43" s="69"/>
-      <c r="AN43" s="69"/>
-      <c r="AO43" s="69"/>
-      <c r="AP43" s="69"/>
-      <c r="AQ43" s="69"/>
-      <c r="AR43" s="69">
+      <c r="AF43" s="64"/>
+      <c r="AG43" s="64"/>
+      <c r="AH43" s="64"/>
+      <c r="AI43" s="64"/>
+      <c r="AJ43" s="64"/>
+      <c r="AK43" s="64"/>
+      <c r="AL43" s="64"/>
+      <c r="AM43" s="64"/>
+      <c r="AN43" s="64"/>
+      <c r="AO43" s="64"/>
+      <c r="AP43" s="64"/>
+      <c r="AQ43" s="64"/>
+      <c r="AR43" s="64">
         <f>prod_table_raw!N197</f>
         <v>11700</v>
       </c>
-      <c r="AS43" s="65">
+      <c r="AS43" s="60">
         <f>AH43/(concentrate_grade!$F$4/100)</f>
         <v>0</v>
       </c>
-      <c r="AT43" s="65">
+      <c r="AT43" s="60">
         <f>AI43/(concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
-      <c r="AU43" s="66">
+      <c r="AU43" s="61">
         <f>AK43/(concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
-      <c r="AV43" s="69"/>
-      <c r="AW43" s="66">
+      <c r="AV43" s="64"/>
+      <c r="AW43" s="61">
         <f>AM43/(concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
-      <c r="AX43" s="69"/>
-      <c r="AY43" s="69"/>
-      <c r="AZ43" s="69"/>
-      <c r="BA43" s="69"/>
-      <c r="BB43" s="69"/>
-      <c r="BC43" s="66">
+      <c r="AX43" s="64"/>
+      <c r="AY43" s="64"/>
+      <c r="AZ43" s="64"/>
+      <c r="BA43" s="64"/>
+      <c r="BB43" s="64"/>
+      <c r="BC43" s="61">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -32091,7 +32081,7 @@
         <v>1521</v>
       </c>
       <c r="I44" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="K44" t="s">
         <v>1418</v>
@@ -32127,7 +32117,7 @@
         <v>1396</v>
       </c>
       <c r="X44" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="Y44" s="18">
         <f>prod_table_raw!N202</f>
@@ -32142,7 +32132,7 @@
         <f t="shared" si="7"/>
         <v>6472169.1176470499</v>
       </c>
-      <c r="AC44" s="72">
+      <c r="AC44" s="67">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -32223,7 +32213,7 @@
         <v>1521</v>
       </c>
       <c r="I45" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="K45" t="s">
         <v>1426</v>
@@ -32259,7 +32249,7 @@
         <v>1398</v>
       </c>
       <c r="X45" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="Y45" s="18">
         <f>prod_table_raw!N207</f>
@@ -32274,7 +32264,7 @@
         <f t="shared" si="7"/>
         <v>1348550</v>
       </c>
-      <c r="AC45" s="72">
+      <c r="AC45" s="67">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -32361,7 +32351,7 @@
         <v>1523</v>
       </c>
       <c r="I46" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="K46" t="s">
         <v>1426</v>
@@ -32391,7 +32381,7 @@
         <v>920</v>
       </c>
       <c r="X46" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="Y46" s="18">
         <f>prod_table_raw!N211</f>
@@ -32406,7 +32396,7 @@
         <f t="shared" si="7"/>
         <v>8763991.9465738703</v>
       </c>
-      <c r="AC46" s="72">
+      <c r="AC46" s="67">
         <f t="shared" si="2"/>
         <v>9.1892128367207101E-7</v>
       </c>
@@ -32467,224 +32457,224 @@
         <v>8.0534261301020305</v>
       </c>
     </row>
-    <row r="47" spans="1:55" x14ac:dyDescent="0.25">
-      <c r="A47" s="18" t="s">
+    <row r="47" spans="1:55" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="69" t="s">
         <v>340</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" s="12" t="s">
         <v>341</v>
       </c>
-      <c r="E47" t="s">
+      <c r="E47" s="12" t="s">
         <v>439</v>
       </c>
-      <c r="F47" s="19" t="s">
+      <c r="F47" s="70" t="s">
         <v>435</v>
       </c>
-      <c r="G47" s="18" t="s">
+      <c r="G47" s="69" t="s">
         <v>78</v>
       </c>
-      <c r="H47" t="s">
+      <c r="H47" s="12" t="s">
         <v>1519</v>
       </c>
-      <c r="I47" t="s">
-        <v>1557</v>
-      </c>
-      <c r="J47" t="s">
-        <v>1561</v>
-      </c>
-      <c r="K47" t="s">
+      <c r="I47" s="12" t="s">
+        <v>1555</v>
+      </c>
+      <c r="J47" s="12" t="s">
+        <v>1559</v>
+      </c>
+      <c r="K47" s="12" t="s">
         <v>1425</v>
       </c>
-      <c r="L47" t="s">
+      <c r="L47" s="12" t="s">
         <v>1416</v>
       </c>
-      <c r="M47">
+      <c r="M47" s="12">
         <v>11531646.543500001</v>
       </c>
-      <c r="N47" t="s">
+      <c r="N47" s="12" t="s">
         <v>1477</v>
       </c>
-      <c r="Q47" t="s">
+      <c r="Q47" s="12" t="s">
         <v>1113</v>
       </c>
-      <c r="R47" t="s">
+      <c r="R47" s="12" t="s">
         <v>1113</v>
       </c>
-      <c r="S47" t="s">
+      <c r="S47" s="12" t="s">
         <v>1113</v>
       </c>
-      <c r="T47" t="s">
+      <c r="T47" s="12" t="s">
         <v>1117</v>
       </c>
-      <c r="U47" s="19" t="s">
+      <c r="U47" s="70" t="s">
         <v>292</v>
       </c>
-      <c r="V47" t="s">
-        <v>1113</v>
-      </c>
-      <c r="W47" t="s">
-        <v>1554</v>
-      </c>
-      <c r="X47" t="s">
-        <v>1577</v>
-      </c>
-      <c r="Y47" s="18">
+      <c r="V47" s="12" t="s">
+        <v>1117</v>
+      </c>
+      <c r="W47" s="12" t="s">
+        <v>1552</v>
+      </c>
+      <c r="X47" s="12" t="s">
+        <v>1575</v>
+      </c>
+      <c r="Y47" s="69">
         <f>prod_table_raw!N215</f>
         <v>1139000</v>
       </c>
-      <c r="Z47">
+      <c r="Z47" s="12">
         <f>(AF47+AG47)/0.98</f>
         <v>0.15869132653061224</v>
       </c>
-      <c r="AA47">
+      <c r="AA47" s="12">
         <f>AH47/(concentrate_grade!$F$4/100)</f>
         <v>13333.333333333334</v>
       </c>
-      <c r="AB47">
+      <c r="AB47" s="12">
         <f t="shared" si="7"/>
         <v>1125666.5079753401</v>
       </c>
-      <c r="AC47" s="72">
+      <c r="AC47" s="71">
         <f t="shared" si="2"/>
         <v>1.3932513303828993E-7</v>
       </c>
-      <c r="AD47">
+      <c r="AD47" s="12">
         <f t="shared" si="3"/>
         <v>1.170617500731636E-2</v>
       </c>
-      <c r="AE47" s="51">
+      <c r="AE47" s="72">
         <f t="shared" si="9"/>
         <v>0.98815502466299554</v>
       </c>
-      <c r="AF47" s="31">
+      <c r="AF47" s="73">
         <f>prod_table_raw!N214</f>
         <v>0.1555175</v>
       </c>
-      <c r="AG47" s="31"/>
-      <c r="AH47" s="31">
+      <c r="AG47" s="73"/>
+      <c r="AH47" s="73">
         <f>prod_table_raw!N217</f>
         <v>4000</v>
       </c>
-      <c r="AI47" s="31"/>
-      <c r="AJ47" s="31"/>
-      <c r="AK47" s="31"/>
-      <c r="AL47" s="31"/>
-      <c r="AM47" s="31"/>
-      <c r="AN47" s="31"/>
-      <c r="AO47" s="31"/>
-      <c r="AP47" s="31"/>
-      <c r="AQ47" s="31"/>
-      <c r="AR47" s="31"/>
-      <c r="AS47">
+      <c r="AI47" s="73"/>
+      <c r="AJ47" s="73"/>
+      <c r="AK47" s="73"/>
+      <c r="AL47" s="73"/>
+      <c r="AM47" s="73"/>
+      <c r="AN47" s="73"/>
+      <c r="AO47" s="73"/>
+      <c r="AP47" s="73"/>
+      <c r="AQ47" s="73"/>
+      <c r="AR47" s="73"/>
+      <c r="AS47" s="12">
         <f>AH47/(concentrate_grade!$F$4/100)</f>
         <v>13333.333333333334</v>
       </c>
-      <c r="AT47">
+      <c r="AT47" s="12">
         <f>AI47/(concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
-      <c r="AU47">
+      <c r="AU47" s="12">
         <f>AK47/(concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
-      <c r="AV47">
+      <c r="AV47" s="12">
         <f>AL47/(concentrate_grade!$F$9/100)</f>
         <v>0</v>
       </c>
-      <c r="AW47">
+      <c r="AW47" s="12">
         <f>AM47/(concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
-      <c r="AX47"/>
-      <c r="AY47" s="31"/>
-      <c r="AZ47" s="31"/>
-      <c r="BA47" s="31"/>
-      <c r="BB47" t="e">
+      <c r="AY47" s="73"/>
+      <c r="AZ47" s="73"/>
+      <c r="BA47" s="73"/>
+      <c r="BB47" s="12" t="e">
         <f>AR47/concentrate_grade!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="BC47">
+      <c r="BC47" s="12">
         <f t="shared" si="8"/>
         <v>0.15869132653061224</v>
       </c>
     </row>
-    <row r="48" spans="1:55" s="54" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="53" t="s">
+    <row r="48" spans="1:55" x14ac:dyDescent="0.25">
+      <c r="A48" s="18" t="s">
         <v>343</v>
       </c>
-      <c r="C48" s="54" t="s">
+      <c r="C48" t="s">
         <v>346</v>
       </c>
-      <c r="E48" s="54" t="s">
+      <c r="E48" t="s">
         <v>437</v>
       </c>
-      <c r="F48" s="55" t="s">
+      <c r="F48" s="19" t="s">
         <v>435</v>
       </c>
-      <c r="G48" s="53" t="s">
+      <c r="G48" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="H48" s="54" t="s">
+      <c r="H48" t="s">
         <v>1523</v>
       </c>
-      <c r="I48" s="54" t="s">
-        <v>1556</v>
-      </c>
-      <c r="J48" s="54" t="s">
+      <c r="I48" t="s">
+        <v>1554</v>
+      </c>
+      <c r="J48" t="s">
         <v>1400</v>
       </c>
-      <c r="K48" s="54" t="s">
+      <c r="K48" t="s">
         <v>1426</v>
       </c>
-      <c r="L48" s="54" t="s">
+      <c r="L48" t="s">
         <v>1515</v>
       </c>
-      <c r="M48" s="54">
+      <c r="M48">
         <v>6139378.4953300003</v>
       </c>
-      <c r="N48" s="54" t="s">
+      <c r="N48" t="s">
         <v>1482</v>
       </c>
-      <c r="O48" s="54" t="s">
+      <c r="O48" t="s">
         <v>1113</v>
       </c>
-      <c r="Q48" s="54" t="s">
+      <c r="Q48" t="s">
         <v>1113</v>
       </c>
       <c r="R48" t="s">
         <v>1113</v>
       </c>
-      <c r="S48" s="54" t="s">
+      <c r="S48" t="s">
         <v>1113</v>
       </c>
-      <c r="T48" s="54" t="s">
+      <c r="T48" t="s">
         <v>1113</v>
       </c>
-      <c r="U48" s="55" t="s">
+      <c r="U48" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="V48" s="54" t="s">
+      <c r="V48" t="s">
         <v>1113</v>
       </c>
-      <c r="W48" s="54" t="s">
+      <c r="W48" t="s">
         <v>920</v>
       </c>
-      <c r="X48" s="54" t="s">
-        <v>1565</v>
-      </c>
-      <c r="Y48" s="53">
+      <c r="X48" t="s">
+        <v>1563</v>
+      </c>
+      <c r="Y48" s="18">
         <f>prod_table_raw!N222</f>
         <v>841000</v>
       </c>
-      <c r="Z48" s="54">
+      <c r="Z48">
         <f>(AF48+AG48)/0.98</f>
         <v>3.5769025000000001</v>
       </c>
-      <c r="AB48" s="54">
+      <c r="AA48"/>
+      <c r="AB48">
         <f t="shared" si="7"/>
         <v>840996.4230975</v>
       </c>
-      <c r="AC48" s="72">
+      <c r="AC48" s="67">
         <f t="shared" si="2"/>
         <v>4.2531539833531507E-6</v>
       </c>
@@ -32692,122 +32682,123 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AE48" s="56">
+      <c r="AE48" s="51">
         <f t="shared" si="9"/>
         <v>0.99999574682792725</v>
       </c>
-      <c r="AF48" s="57">
+      <c r="AF48" s="31">
         <f>prod_table_raw!N223</f>
         <v>3.5053644500000001</v>
       </c>
-      <c r="AG48" s="57"/>
-      <c r="AH48" s="57"/>
-      <c r="AI48" s="57"/>
-      <c r="AJ48" s="57"/>
-      <c r="AK48" s="57"/>
-      <c r="AL48" s="57"/>
-      <c r="AM48" s="57"/>
-      <c r="AN48" s="57"/>
-      <c r="AO48" s="57"/>
-      <c r="AP48" s="57"/>
-      <c r="AQ48" s="57"/>
-      <c r="AR48" s="57"/>
-      <c r="AS48" s="54">
+      <c r="AG48" s="31"/>
+      <c r="AH48" s="31"/>
+      <c r="AI48" s="31"/>
+      <c r="AJ48" s="31"/>
+      <c r="AK48" s="31"/>
+      <c r="AL48" s="31"/>
+      <c r="AM48" s="31"/>
+      <c r="AN48" s="31"/>
+      <c r="AO48" s="31"/>
+      <c r="AP48" s="31"/>
+      <c r="AQ48" s="31"/>
+      <c r="AR48" s="31"/>
+      <c r="AS48">
         <f>AH48/(concentrate_grade!$F$4/100)</f>
         <v>0</v>
       </c>
-      <c r="AT48" s="54">
+      <c r="AT48">
         <f>AI48/(concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
-      <c r="AU48" s="54">
+      <c r="AU48">
         <f>AK48/(concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
-      <c r="AV48" s="54">
+      <c r="AV48">
         <f>AL48/(concentrate_grade!$F$9/100)</f>
         <v>0</v>
       </c>
-      <c r="AW48" s="54">
+      <c r="AW48">
         <f>AM48/(concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
-      <c r="AY48" s="57"/>
-      <c r="AZ48" s="57"/>
-      <c r="BA48" s="57"/>
-      <c r="BB48" s="54" t="e">
+      <c r="AX48"/>
+      <c r="AY48" s="31"/>
+      <c r="AZ48" s="31"/>
+      <c r="BA48" s="31"/>
+      <c r="BB48" t="e">
         <f>AR48/concentrate_grade!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="BC48" s="54">
+      <c r="BC48">
         <f t="shared" si="8"/>
         <v>3.5769025000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:55" s="66" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="64" t="s">
+    <row r="49" spans="1:55" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="59" t="s">
         <v>357</v>
       </c>
-      <c r="C49" s="66" t="s">
+      <c r="C49" s="61" t="s">
         <v>359</v>
       </c>
-      <c r="E49" s="66" t="s">
+      <c r="E49" s="61" t="s">
         <v>442</v>
       </c>
-      <c r="F49" s="67" t="s">
+      <c r="F49" s="62" t="s">
         <v>435</v>
       </c>
-      <c r="G49" s="64" t="s">
+      <c r="G49" s="59" t="s">
         <v>78</v>
       </c>
-      <c r="H49" s="66" t="s">
+      <c r="H49" s="61" t="s">
         <v>1519</v>
       </c>
-      <c r="I49" s="66" t="s">
+      <c r="I49" s="61" t="s">
         <v>1407</v>
       </c>
-      <c r="K49" s="66" t="s">
+      <c r="K49" s="61" t="s">
         <v>1426</v>
       </c>
-      <c r="L49" s="66" t="s">
+      <c r="L49" s="61" t="s">
         <v>1416</v>
       </c>
-      <c r="M49" s="66">
+      <c r="M49" s="61">
         <v>10572188.566137601</v>
       </c>
-      <c r="Q49" s="66" t="s">
+      <c r="Q49" s="61" t="s">
         <v>1113</v>
       </c>
       <c r="R49" t="s">
         <v>1113</v>
       </c>
-      <c r="S49" s="66" t="s">
+      <c r="S49" s="61" t="s">
         <v>1113</v>
       </c>
-      <c r="T49" s="66" t="s">
+      <c r="T49" s="61" t="s">
         <v>1113</v>
       </c>
-      <c r="U49" s="67" t="s">
+      <c r="U49" s="62" t="s">
         <v>49</v>
       </c>
-      <c r="V49" s="66" t="s">
-        <v>1542</v>
-      </c>
-      <c r="W49" s="66" t="s">
+      <c r="V49" s="61" t="s">
+        <v>1540</v>
+      </c>
+      <c r="W49" s="61" t="s">
         <v>1068</v>
       </c>
-      <c r="X49" s="66" t="s">
-        <v>1570</v>
-      </c>
-      <c r="Y49" s="64">
+      <c r="X49" s="61" t="s">
+        <v>1568</v>
+      </c>
+      <c r="Y49" s="59">
         <f>prod_table_raw!N226</f>
         <v>3560000</v>
       </c>
-      <c r="AB49" s="66">
+      <c r="AB49" s="61">
         <f t="shared" si="7"/>
         <v>3560000</v>
       </c>
-      <c r="AC49" s="72">
+      <c r="AC49" s="67">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -32815,297 +32806,294 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AE49" s="68">
+      <c r="AE49" s="63">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="AF49" s="69"/>
-      <c r="AG49" s="69"/>
-      <c r="AH49" s="69"/>
-      <c r="AI49" s="69"/>
-      <c r="AJ49" s="69"/>
-      <c r="AK49" s="69"/>
-      <c r="AL49" s="69"/>
-      <c r="AM49" s="69"/>
-      <c r="AN49" s="69"/>
-      <c r="AO49" s="69"/>
-      <c r="AP49" s="69"/>
-      <c r="AQ49" s="69"/>
-      <c r="AR49" s="69"/>
-      <c r="AS49" s="66">
+      <c r="AF49" s="64"/>
+      <c r="AG49" s="64"/>
+      <c r="AH49" s="64"/>
+      <c r="AI49" s="64"/>
+      <c r="AJ49" s="64"/>
+      <c r="AK49" s="64"/>
+      <c r="AL49" s="64"/>
+      <c r="AM49" s="64"/>
+      <c r="AN49" s="64"/>
+      <c r="AO49" s="64"/>
+      <c r="AP49" s="64"/>
+      <c r="AQ49" s="64"/>
+      <c r="AR49" s="64"/>
+      <c r="AS49" s="61">
         <f>AH49/(concentrate_grade!$F$4/100)</f>
         <v>0</v>
       </c>
-      <c r="AT49" s="66">
+      <c r="AT49" s="61">
         <f>AI49/(concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
-      <c r="AU49" s="66">
+      <c r="AU49" s="61">
         <f>AK49/(concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
-      <c r="AV49" s="66">
+      <c r="AV49" s="61">
         <f>AL49/(concentrate_grade!$F$9/100)</f>
         <v>0</v>
       </c>
-      <c r="AW49" s="66">
+      <c r="AW49" s="61">
         <f>AM49/(concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
-      <c r="AY49" s="69"/>
-      <c r="AZ49" s="69"/>
-      <c r="BA49" s="69"/>
-      <c r="BB49" s="66" t="e">
+      <c r="AY49" s="64"/>
+      <c r="AZ49" s="64"/>
+      <c r="BA49" s="64"/>
+      <c r="BB49" s="61" t="e">
         <f>AR49/concentrate_grade!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="BC49" s="66">
+      <c r="BC49" s="61">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:55" x14ac:dyDescent="0.25">
-      <c r="A50" s="18" t="s">
+    <row r="50" spans="1:55" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="69" t="s">
         <v>371</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B50" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="12" t="s">
         <v>372</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D50" s="12" t="s">
         <v>164</v>
       </c>
-      <c r="E50" t="s">
+      <c r="E50" s="12" t="s">
         <v>437</v>
       </c>
-      <c r="F50" s="19" t="s">
+      <c r="F50" s="70" t="s">
         <v>435</v>
       </c>
-      <c r="G50" s="18" t="s">
+      <c r="G50" s="69" t="s">
         <v>264</v>
       </c>
-      <c r="H50" t="s">
+      <c r="H50" s="12" t="s">
         <v>1523</v>
       </c>
-      <c r="I50" t="s">
-        <v>1560</v>
-      </c>
-      <c r="J50" t="s">
-        <v>1553</v>
-      </c>
-      <c r="K50" t="s">
+      <c r="I50" s="12" t="s">
+        <v>1558</v>
+      </c>
+      <c r="J50" s="12" t="s">
+        <v>1551</v>
+      </c>
+      <c r="K50" s="12" t="s">
         <v>1426</v>
       </c>
-      <c r="L50" t="s">
+      <c r="L50" s="12" t="s">
         <v>1508</v>
       </c>
-      <c r="M50">
+      <c r="M50" s="12">
         <v>1039802.195699128</v>
       </c>
-      <c r="O50" t="s">
+      <c r="O50" s="12" t="s">
         <v>1113</v>
       </c>
-      <c r="Q50" t="s">
+      <c r="Q50" s="12" t="s">
         <v>1113</v>
       </c>
-      <c r="R50" t="s">
+      <c r="R50" s="12" t="s">
         <v>1113</v>
       </c>
-      <c r="T50" t="s">
+      <c r="T50" s="12" t="s">
         <v>1113</v>
       </c>
-      <c r="U50" s="19" t="s">
+      <c r="U50" s="70" t="s">
         <v>373</v>
       </c>
-      <c r="V50" t="s">
-        <v>1113</v>
-      </c>
-      <c r="W50" t="s">
+      <c r="V50" s="12" t="s">
+        <v>1117</v>
+      </c>
+      <c r="W50" s="12" t="s">
         <v>1396</v>
       </c>
-      <c r="X50" t="s">
-        <v>1566</v>
-      </c>
-      <c r="Y50" s="18">
+      <c r="X50" s="12" t="s">
+        <v>1564</v>
+      </c>
+      <c r="Y50" s="69">
         <f>prod_table_raw!N239</f>
         <v>1025997</v>
       </c>
-      <c r="Z50"/>
-      <c r="AA50">
+      <c r="AA50" s="12">
         <f>AI50/(concentrate_grade!$F$6/100)</f>
         <v>47062.5</v>
       </c>
-      <c r="AB50">
+      <c r="AB50" s="12">
         <f t="shared" si="7"/>
         <v>978934.5</v>
       </c>
-      <c r="AC50" s="72">
+      <c r="AC50" s="71">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AD50">
+      <c r="AD50" s="12">
         <f t="shared" si="3"/>
         <v>4.5870017163792874E-2</v>
       </c>
-      <c r="AE50" s="51">
+      <c r="AE50" s="72">
         <f t="shared" si="9"/>
         <v>0.95192477126917074</v>
       </c>
-      <c r="AF50" s="31"/>
-      <c r="AG50" s="31"/>
-      <c r="AH50" s="31">
+      <c r="AF50" s="73"/>
+      <c r="AG50" s="73"/>
+      <c r="AH50" s="73">
         <f>prod_table_raw!N237</f>
         <v>7154</v>
       </c>
-      <c r="AI50" s="31">
+      <c r="AI50" s="73">
         <f>prod_table_raw!N238</f>
         <v>7530</v>
       </c>
-      <c r="AJ50" s="31"/>
-      <c r="AK50" s="31"/>
-      <c r="AL50" s="31"/>
-      <c r="AM50" s="31"/>
-      <c r="AN50" s="31"/>
-      <c r="AO50" s="31"/>
-      <c r="AP50" s="31"/>
-      <c r="AQ50" s="31"/>
-      <c r="AR50" s="31"/>
-      <c r="AS50"/>
-      <c r="AT50">
+      <c r="AJ50" s="73"/>
+      <c r="AK50" s="73"/>
+      <c r="AL50" s="73"/>
+      <c r="AM50" s="73"/>
+      <c r="AN50" s="73"/>
+      <c r="AO50" s="73"/>
+      <c r="AP50" s="73"/>
+      <c r="AQ50" s="73"/>
+      <c r="AR50" s="73"/>
+      <c r="AT50" s="12">
         <f>AI50/(concentrate_grade!$F$6/100)</f>
         <v>47062.5</v>
       </c>
-      <c r="AU50">
+      <c r="AU50" s="12">
         <f>AK50/(concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
-      <c r="AV50">
+      <c r="AV50" s="12">
         <f>AL50/(concentrate_grade!$F$9/100)</f>
         <v>0</v>
       </c>
-      <c r="AW50">
+      <c r="AW50" s="12">
         <f>AM50/(concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
-      <c r="AX50"/>
-      <c r="AY50" s="31"/>
-      <c r="AZ50" s="31"/>
-      <c r="BA50" s="31"/>
-      <c r="BB50" t="e">
+      <c r="AY50" s="73"/>
+      <c r="AZ50" s="73"/>
+      <c r="BA50" s="73"/>
+      <c r="BB50" s="12" t="e">
         <f>AR50/concentrate_grade!#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="BC50">
+      <c r="BC50" s="12">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:55" s="66" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="64" t="s">
+    <row r="51" spans="1:55" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="59" t="s">
         <v>376</v>
       </c>
-      <c r="B51" s="66" t="s">
+      <c r="B51" s="61" t="s">
         <v>162</v>
       </c>
-      <c r="C51" s="66" t="s">
+      <c r="C51" s="61" t="s">
         <v>377</v>
       </c>
-      <c r="D51" s="66" t="s">
+      <c r="D51" s="61" t="s">
         <v>164</v>
       </c>
-      <c r="E51" s="66" t="s">
+      <c r="E51" s="61" t="s">
         <v>437</v>
       </c>
-      <c r="F51" s="67" t="s">
+      <c r="F51" s="62" t="s">
         <v>540</v>
       </c>
-      <c r="G51" s="64" t="s">
+      <c r="G51" s="59" t="s">
         <v>378</v>
       </c>
-      <c r="H51" s="66" t="s">
+      <c r="H51" s="61" t="s">
         <v>1523</v>
       </c>
-      <c r="I51" s="66" t="s">
+      <c r="I51" s="61" t="s">
         <v>1160</v>
       </c>
-      <c r="K51" s="66" t="s">
+      <c r="K51" s="61" t="s">
         <v>1418</v>
       </c>
-      <c r="L51" s="66" t="s">
+      <c r="L51" s="61" t="s">
         <v>1508</v>
       </c>
-      <c r="O51" s="66" t="s">
+      <c r="O51" s="61" t="s">
         <v>1113</v>
       </c>
-      <c r="P51" s="66" t="s">
+      <c r="P51" s="61" t="s">
         <v>1113</v>
       </c>
-      <c r="Q51" s="66" t="s">
+      <c r="Q51" s="61" t="s">
         <v>1113</v>
       </c>
       <c r="R51" t="s">
         <v>1113</v>
       </c>
-      <c r="T51" s="66" t="s">
+      <c r="T51" s="61" t="s">
         <v>1113</v>
       </c>
-      <c r="U51" s="67" t="s">
+      <c r="U51" s="62" t="s">
         <v>379</v>
       </c>
-      <c r="V51" s="66" t="s">
-        <v>1537</v>
-      </c>
-      <c r="W51" s="66" t="s">
+      <c r="V51" s="61" t="s">
+        <v>1117</v>
+      </c>
+      <c r="W51" s="61" t="s">
         <v>1396</v>
       </c>
-      <c r="X51" s="66" t="s">
-        <v>1538</v>
-      </c>
-      <c r="Y51" s="64"/>
-      <c r="AB51" s="66">
+      <c r="X51" s="61" t="s">
+        <v>1536</v>
+      </c>
+      <c r="Y51" s="59"/>
+      <c r="AB51" s="61">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AC51" s="72"/>
+      <c r="AC51" s="67"/>
       <c r="AD51"/>
-      <c r="AF51" s="69"/>
-      <c r="AG51" s="69"/>
-      <c r="AH51" s="69">
+      <c r="AF51" s="64"/>
+      <c r="AG51" s="64"/>
+      <c r="AH51" s="64">
         <f>prod_table_raw!N241</f>
         <v>13720</v>
       </c>
-      <c r="AI51" s="69">
+      <c r="AI51" s="64">
         <f>prod_table_raw!N240</f>
         <v>62251</v>
       </c>
-      <c r="AJ51" s="69"/>
-      <c r="AK51" s="69"/>
-      <c r="AL51" s="69"/>
-      <c r="AM51" s="69"/>
-      <c r="AN51" s="69"/>
-      <c r="AO51" s="69"/>
-      <c r="AP51" s="69"/>
-      <c r="AQ51" s="69"/>
-      <c r="AR51" s="69"/>
-      <c r="AS51" s="65"/>
-      <c r="AT51" s="65"/>
-      <c r="AU51" s="66">
+      <c r="AJ51" s="64"/>
+      <c r="AK51" s="64"/>
+      <c r="AL51" s="64"/>
+      <c r="AM51" s="64"/>
+      <c r="AN51" s="64"/>
+      <c r="AO51" s="64"/>
+      <c r="AP51" s="64"/>
+      <c r="AQ51" s="64"/>
+      <c r="AR51" s="64"/>
+      <c r="AS51" s="60"/>
+      <c r="AT51" s="60"/>
+      <c r="AU51" s="61">
         <f>AK51/(concentrate_grade!$F$5/100)</f>
         <v>0</v>
       </c>
-      <c r="AV51" s="69"/>
-      <c r="AW51" s="66">
+      <c r="AV51" s="64"/>
+      <c r="AW51" s="61">
         <f>AM51/(concentrate_grade!$F$8/100)</f>
         <v>0</v>
       </c>
-      <c r="AX51" s="69"/>
-      <c r="AY51" s="69"/>
-      <c r="AZ51" s="69"/>
-      <c r="BA51" s="69"/>
-      <c r="BB51" s="69"/>
-      <c r="BC51" s="66">
+      <c r="AX51" s="64"/>
+      <c r="AY51" s="64"/>
+      <c r="AZ51" s="64"/>
+      <c r="BA51" s="64"/>
+      <c r="BB51" s="64"/>
+      <c r="BC51" s="61">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -33130,7 +33118,7 @@
         <v>1523</v>
       </c>
       <c r="I52" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="N52" t="s">
         <v>1479</v>
@@ -33160,7 +33148,7 @@
         <v>920</v>
       </c>
       <c r="X52" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="Y52" s="18">
         <f>prod_table_raw!N244</f>
@@ -33175,7 +33163,7 @@
         <f t="shared" si="7"/>
         <v>234669.77303040153</v>
       </c>
-      <c r="AC52" s="72">
+      <c r="AC52" s="67">
         <f t="shared" si="2"/>
         <v>5.2284670814433306E-6</v>
       </c>
@@ -33236,101 +33224,101 @@
         <v>1.2269695984693878</v>
       </c>
     </row>
-    <row r="53" spans="1:55" s="66" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="64" t="s">
+    <row r="53" spans="1:55" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="59" t="s">
         <v>387</v>
       </c>
-      <c r="C53" s="66" t="s">
+      <c r="C53" s="61" t="s">
         <v>390</v>
       </c>
-      <c r="E53" s="66" t="s">
+      <c r="E53" s="61" t="s">
         <v>538</v>
       </c>
-      <c r="F53" s="67" t="s">
+      <c r="F53" s="62" t="s">
         <v>540</v>
       </c>
-      <c r="G53" s="64" t="s">
+      <c r="G53" s="59" t="s">
         <v>71</v>
       </c>
-      <c r="H53" s="66" t="s">
+      <c r="H53" s="61" t="s">
         <v>1519</v>
       </c>
-      <c r="I53" s="66" t="s">
+      <c r="I53" s="61" t="s">
         <v>1161</v>
       </c>
-      <c r="K53" s="66" t="s">
+      <c r="K53" s="61" t="s">
         <v>1418</v>
       </c>
-      <c r="L53" s="66" t="s">
+      <c r="L53" s="61" t="s">
         <v>1508</v>
       </c>
-      <c r="O53" s="66" t="s">
+      <c r="O53" s="61" t="s">
         <v>1113</v>
       </c>
-      <c r="P53" s="66" t="s">
+      <c r="P53" s="61" t="s">
         <v>1113</v>
       </c>
-      <c r="Q53" s="66" t="s">
+      <c r="Q53" s="61" t="s">
         <v>1113</v>
       </c>
       <c r="R53" t="s">
         <v>1113</v>
       </c>
-      <c r="T53" s="66" t="s">
+      <c r="T53" s="61" t="s">
         <v>1113</v>
       </c>
-      <c r="U53" s="67" t="s">
+      <c r="U53" s="62" t="s">
         <v>391</v>
       </c>
-      <c r="V53" s="66" t="s">
-        <v>1537</v>
-      </c>
-      <c r="W53" s="66" t="s">
+      <c r="V53" s="61" t="s">
+        <v>1117</v>
+      </c>
+      <c r="W53" s="61" t="s">
         <v>1397</v>
       </c>
-      <c r="X53" s="66" t="s">
-        <v>1540</v>
-      </c>
-      <c r="Y53" s="64"/>
-      <c r="AB53" s="66">
+      <c r="X53" s="61" t="s">
+        <v>1538</v>
+      </c>
+      <c r="Y53" s="59"/>
+      <c r="AB53" s="61">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AC53" s="72"/>
+      <c r="AC53" s="67"/>
       <c r="AD53"/>
-      <c r="AF53" s="69"/>
-      <c r="AG53" s="69"/>
-      <c r="AH53" s="69"/>
-      <c r="AI53" s="69">
+      <c r="AF53" s="64"/>
+      <c r="AG53" s="64"/>
+      <c r="AH53" s="64"/>
+      <c r="AI53" s="64">
         <f>prod_table_raw!N247</f>
         <v>32268</v>
       </c>
-      <c r="AJ53" s="69">
+      <c r="AJ53" s="64">
         <f>prod_table_raw!N246</f>
         <v>3368</v>
       </c>
-      <c r="AK53" s="69"/>
-      <c r="AL53" s="69"/>
-      <c r="AM53" s="69"/>
-      <c r="AN53" s="69"/>
-      <c r="AO53" s="69"/>
-      <c r="AP53" s="69"/>
-      <c r="AQ53" s="69"/>
-      <c r="AR53" s="69"/>
-      <c r="AS53" s="65">
+      <c r="AK53" s="64"/>
+      <c r="AL53" s="64"/>
+      <c r="AM53" s="64"/>
+      <c r="AN53" s="64"/>
+      <c r="AO53" s="64"/>
+      <c r="AP53" s="64"/>
+      <c r="AQ53" s="64"/>
+      <c r="AR53" s="64"/>
+      <c r="AS53" s="60">
         <f>AH53/(concentrate_grade!$F$4/100)</f>
         <v>0</v>
       </c>
-      <c r="AT53" s="65"/>
-      <c r="AU53" s="69"/>
-      <c r="AV53" s="69"/>
-      <c r="AW53" s="69"/>
-      <c r="AX53" s="69"/>
-      <c r="AY53" s="69"/>
-      <c r="AZ53" s="69"/>
-      <c r="BA53" s="69"/>
-      <c r="BB53" s="69"/>
-      <c r="BC53" s="66">
+      <c r="AT53" s="60"/>
+      <c r="AU53" s="64"/>
+      <c r="AV53" s="64"/>
+      <c r="AW53" s="64"/>
+      <c r="AX53" s="64"/>
+      <c r="AY53" s="64"/>
+      <c r="AZ53" s="64"/>
+      <c r="BA53" s="64"/>
+      <c r="BB53" s="64"/>
+      <c r="BC53" s="61">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -33355,7 +33343,7 @@
         <v>1519</v>
       </c>
       <c r="I54" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="K54" t="s">
         <v>1426</v>
@@ -33391,7 +33379,7 @@
         <v>1396</v>
       </c>
       <c r="X54" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="Y54" s="18">
         <f>prod_table_raw!N250</f>
@@ -33406,7 +33394,7 @@
         <f t="shared" si="7"/>
         <v>415330.88235294097</v>
       </c>
-      <c r="AC54" s="72">
+      <c r="AC54" s="67">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -33493,7 +33481,7 @@
         <v>1523</v>
       </c>
       <c r="I55" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="J55" t="s">
         <v>1533</v>
@@ -33523,13 +33511,13 @@
         <v>406</v>
       </c>
       <c r="V55" t="s">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="W55" t="s">
         <v>1396</v>
       </c>
       <c r="X55" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="Y55" s="18">
         <f>prod_table_raw!N259</f>
@@ -33544,7 +33532,7 @@
         <f t="shared" si="7"/>
         <v>374412.5</v>
       </c>
-      <c r="AC55" s="72">
+      <c r="AC55" s="67">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -33605,98 +33593,98 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:55" s="66" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="64" t="s">
+    <row r="56" spans="1:55" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="59" t="s">
         <v>409</v>
       </c>
-      <c r="C56" s="66" t="s">
+      <c r="C56" s="61" t="s">
         <v>410</v>
       </c>
-      <c r="E56" s="66" t="s">
+      <c r="E56" s="61" t="s">
         <v>439</v>
       </c>
-      <c r="F56" s="67" t="s">
+      <c r="F56" s="62" t="s">
         <v>540</v>
       </c>
-      <c r="G56" s="64" t="s">
+      <c r="G56" s="59" t="s">
         <v>71</v>
       </c>
-      <c r="H56" s="66" t="s">
+      <c r="H56" s="61" t="s">
         <v>1520</v>
       </c>
-      <c r="I56" s="66" t="s">
+      <c r="I56" s="61" t="s">
         <v>1415</v>
       </c>
-      <c r="K56" s="66" t="s">
+      <c r="K56" s="61" t="s">
         <v>1419</v>
       </c>
-      <c r="L56" s="66" t="s">
+      <c r="L56" s="61" t="s">
         <v>1508</v>
       </c>
-      <c r="O56" s="66" t="s">
+      <c r="O56" s="61" t="s">
         <v>1113</v>
       </c>
-      <c r="P56" s="66" t="s">
+      <c r="P56" s="61" t="s">
         <v>1113</v>
       </c>
-      <c r="Q56" s="66" t="s">
+      <c r="Q56" s="61" t="s">
         <v>1113</v>
       </c>
       <c r="R56" t="s">
         <v>1113</v>
       </c>
-      <c r="T56" s="66" t="s">
+      <c r="T56" s="61" t="s">
         <v>1117</v>
       </c>
-      <c r="U56" s="67" t="s">
+      <c r="U56" s="62" t="s">
         <v>412</v>
       </c>
-      <c r="V56" s="66" t="s">
+      <c r="V56" s="61" t="s">
         <v>1117</v>
       </c>
-      <c r="W56" s="66" t="s">
+      <c r="W56" s="61" t="s">
         <v>1394</v>
       </c>
-      <c r="Y56" s="64"/>
-      <c r="AB56" s="66">
+      <c r="Y56" s="59"/>
+      <c r="AB56" s="61">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AC56" s="72"/>
+      <c r="AC56" s="67"/>
       <c r="AD56"/>
-      <c r="AF56" s="69"/>
-      <c r="AG56" s="69"/>
-      <c r="AH56" s="69"/>
-      <c r="AI56" s="69"/>
-      <c r="AJ56" s="69"/>
-      <c r="AK56" s="69"/>
-      <c r="AL56" s="69">
+      <c r="AF56" s="64"/>
+      <c r="AG56" s="64"/>
+      <c r="AH56" s="64"/>
+      <c r="AI56" s="64"/>
+      <c r="AJ56" s="64"/>
+      <c r="AK56" s="64"/>
+      <c r="AL56" s="64">
         <f>prod_table_raw!N262</f>
         <v>256000</v>
       </c>
-      <c r="AM56" s="69"/>
-      <c r="AN56" s="69"/>
-      <c r="AO56" s="69"/>
-      <c r="AP56" s="69"/>
-      <c r="AQ56" s="69"/>
-      <c r="AR56" s="69"/>
-      <c r="AS56" s="65">
+      <c r="AM56" s="64"/>
+      <c r="AN56" s="64"/>
+      <c r="AO56" s="64"/>
+      <c r="AP56" s="64"/>
+      <c r="AQ56" s="64"/>
+      <c r="AR56" s="64"/>
+      <c r="AS56" s="60">
         <f>AH56/(concentrate_grade!$F$4/100)</f>
         <v>0</v>
       </c>
-      <c r="AT56" s="65">
+      <c r="AT56" s="60">
         <f>AI56/(concentrate_grade!$F$6/100)</f>
         <v>0</v>
       </c>
-      <c r="AU56" s="69"/>
-      <c r="AV56" s="69"/>
-      <c r="AW56" s="69"/>
-      <c r="AX56" s="69"/>
-      <c r="AY56" s="69"/>
-      <c r="AZ56" s="69"/>
-      <c r="BA56" s="69"/>
-      <c r="BB56" s="69"/>
-      <c r="BC56" s="66">
+      <c r="AU56" s="64"/>
+      <c r="AV56" s="64"/>
+      <c r="AW56" s="64"/>
+      <c r="AX56" s="64"/>
+      <c r="AY56" s="64"/>
+      <c r="AZ56" s="64"/>
+      <c r="BA56" s="64"/>
+      <c r="BB56" s="64"/>
+      <c r="BC56" s="61">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
@@ -33721,7 +33709,7 @@
         <v>1519</v>
       </c>
       <c r="I57" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
       <c r="K57" t="s">
         <v>1426</v>
@@ -33757,7 +33745,7 @@
         <v>1396</v>
       </c>
       <c r="X57" t="s">
-        <v>1566</v>
+        <v>1564</v>
       </c>
       <c r="Y57" s="18">
         <f>prod_table_raw!N268</f>
@@ -33772,7 +33760,7 @@
         <f t="shared" si="7"/>
         <v>709742.64705882303</v>
       </c>
-      <c r="AC57" s="72">
+      <c r="AC57" s="67">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -33853,7 +33841,7 @@
         <v>1523</v>
       </c>
       <c r="I58" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="K58" t="s">
         <v>1428</v>
@@ -33877,13 +33865,13 @@
         <v>65</v>
       </c>
       <c r="V58" t="s">
-        <v>1502</v>
+        <v>1113</v>
       </c>
       <c r="W58" t="s">
         <v>1075</v>
       </c>
       <c r="X58" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="Y58" s="18">
         <f>prod_table_raw!N271</f>
@@ -33898,7 +33886,7 @@
         <f t="shared" si="7"/>
         <v>1033995.8818331235</v>
       </c>
-      <c r="AC58" s="72">
+      <c r="AC58" s="67">
         <f t="shared" si="2"/>
         <v>3.9827532655034929E-6</v>
       </c>
@@ -33982,7 +33970,7 @@
         <v>1523</v>
       </c>
       <c r="I59" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="K59" t="s">
         <v>1426</v>
@@ -34012,7 +34000,7 @@
         <v>920</v>
       </c>
       <c r="X59" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="Y59" s="18">
         <f>prod_table_raw!N277</f>
@@ -34027,7 +34015,7 @@
         <f t="shared" si="7"/>
         <v>2878041.125247092</v>
       </c>
-      <c r="AC59" s="72">
+      <c r="AC59" s="67">
         <f t="shared" si="2"/>
         <v>2.0412289681729502E-6</v>
       </c>
@@ -34091,10 +34079,10 @@
     <row r="60" spans="1:55" x14ac:dyDescent="0.25">
       <c r="A60" s="18"/>
       <c r="B60" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="D60" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="E60" t="s">
         <v>453</v>
@@ -34109,7 +34097,7 @@
         <v>1519</v>
       </c>
       <c r="I60" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="K60" t="s">
         <v>1426</v>
@@ -34145,7 +34133,7 @@
         <v>1071</v>
       </c>
       <c r="X60" t="s">
-        <v>1562</v>
+        <v>1560</v>
       </c>
       <c r="Y60" s="18">
         <f>prod_table_raw!N154</f>
@@ -34160,7 +34148,7 @@
         <f t="shared" si="7"/>
         <v>34121.378540723177</v>
       </c>
-      <c r="AC60" s="72">
+      <c r="AC60" s="67">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -34245,7 +34233,7 @@
         <v>1519</v>
       </c>
       <c r="I61" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="K61" t="s">
         <v>1418</v>
@@ -34281,7 +34269,7 @@
         <v>1071</v>
       </c>
       <c r="X61" t="s">
-        <v>1562</v>
+        <v>1560</v>
       </c>
       <c r="Y61" s="18">
         <f>prod_table_raw!N153</f>
@@ -34296,7 +34284,7 @@
         <f t="shared" si="7"/>
         <v>91204.762797249088</v>
       </c>
-      <c r="AC61" s="72">
+      <c r="AC61" s="67">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -34378,7 +34366,7 @@
         <v>324</v>
       </c>
       <c r="I62" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="K62" t="s">
         <v>1426</v>
@@ -34408,7 +34396,7 @@
         <v>1075</v>
       </c>
       <c r="X62" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="Y62" s="18">
         <f>prod_table_raw!N160</f>
@@ -34423,7 +34411,7 @@
         <f t="shared" si="7"/>
         <v>3842631.3381266426</v>
       </c>
-      <c r="AC62" s="72">
+      <c r="AC62" s="67">
         <f t="shared" si="2"/>
         <v>4.5977661063644968E-6</v>
       </c>
@@ -34505,7 +34493,7 @@
         <v>324</v>
       </c>
       <c r="I63" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="K63" t="s">
         <v>1426</v>
@@ -34532,7 +34520,7 @@
         <v>920</v>
       </c>
       <c r="X63" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="Y63" s="18">
         <f>prod_table_raw!N101</f>
@@ -34547,7 +34535,7 @@
         <f t="shared" si="7"/>
         <v>2910991.7480510203</v>
       </c>
-      <c r="AC63" s="72">
+      <c r="AC63" s="67">
         <f t="shared" si="2"/>
         <v>2.8347471589116577E-6</v>
       </c>
@@ -34626,7 +34614,7 @@
         <v>64</v>
       </c>
       <c r="I64" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="K64" t="s">
         <v>1426</v>
@@ -34659,7 +34647,7 @@
         <v>920</v>
       </c>
       <c r="X64" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="Y64" s="18">
         <f>prod_table_raw!N254</f>
@@ -34674,7 +34662,7 @@
         <f t="shared" si="7"/>
         <v>1573995.7819845409</v>
       </c>
-      <c r="AC64" s="72">
+      <c r="AC64" s="67">
         <f t="shared" si="2"/>
         <v>2.6798065179057645E-6</v>
       </c>
@@ -34753,7 +34741,7 @@
         <v>64</v>
       </c>
       <c r="I65" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="K65" t="s">
         <v>1426</v>
@@ -34792,7 +34780,7 @@
         <v>920</v>
       </c>
       <c r="X65" t="s">
-        <v>1565</v>
+        <v>1563</v>
       </c>
       <c r="Y65" s="18">
         <f>prod_table_raw!N229</f>
@@ -34807,7 +34795,7 @@
         <f t="shared" si="7"/>
         <v>121998.76992005153</v>
       </c>
-      <c r="AC65" s="72">
+      <c r="AC65" s="67">
         <f t="shared" si="2"/>
         <v>1.0082622528437605E-5</v>
       </c>
@@ -34887,10 +34875,10 @@
         <v>64</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="J66" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="K66" s="21" t="s">
         <v>1534</v>
@@ -34924,13 +34912,13 @@
         <v>225</v>
       </c>
       <c r="V66" t="s">
-        <v>1535</v>
+        <v>1113</v>
       </c>
       <c r="W66" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="X66" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="Y66" s="20">
         <f>prod_table_raw!N193+prod_table_raw!N130</f>
@@ -34948,7 +34936,7 @@
         <f t="shared" ref="AB66" si="11">Y66-Z66-AA66</f>
         <v>2013810.687879523</v>
       </c>
-      <c r="AC66" s="72">
+      <c r="AC66" s="67">
         <f t="shared" si="2"/>
         <v>1.552936072710856E-5</v>
       </c>
@@ -35020,124 +35008,124 @@
     </row>
     <row r="67" spans="1:139" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="68" spans="1:139" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="Y68" s="61">
+      <c r="Y68" s="56">
         <f>SUM(Y2:Y66)</f>
         <v>227227178.21114755</v>
       </c>
-      <c r="Z68" s="62">
+      <c r="Z68" s="57">
         <f t="shared" ref="Z68:BC68" si="12">SUM(Z2:Z66)</f>
         <v>215.43763719285494</v>
       </c>
-      <c r="AA68" s="62" t="e">
+      <c r="AA68" s="57" t="e">
         <f t="shared" si="12"/>
         <v>#REF!</v>
       </c>
-      <c r="AB68" s="62" t="e">
+      <c r="AB68" s="57" t="e">
         <f t="shared" si="12"/>
         <v>#REF!</v>
       </c>
-      <c r="AC68" s="73">
+      <c r="AC68" s="68">
         <f>AVERAGE(AC2:AC66)</f>
         <v>2.6911520652505657E-6</v>
       </c>
-      <c r="AD68" s="62"/>
-      <c r="AE68" s="62" t="e">
+      <c r="AD68" s="57"/>
+      <c r="AE68" s="57" t="e">
         <f t="shared" si="12"/>
         <v>#REF!</v>
       </c>
-      <c r="AF68" s="62">
+      <c r="AF68" s="57">
         <f t="shared" si="12"/>
         <v>169.91780446799788</v>
       </c>
-      <c r="AG68" s="62">
+      <c r="AG68" s="57">
         <f t="shared" si="12"/>
         <v>146.66640810850001</v>
       </c>
-      <c r="AH68" s="62">
+      <c r="AH68" s="57">
         <f t="shared" si="12"/>
         <v>455883.27627700003</v>
       </c>
-      <c r="AI68" s="62">
+      <c r="AI68" s="57">
         <f t="shared" si="12"/>
         <v>306056</v>
       </c>
-      <c r="AJ68" s="62">
+      <c r="AJ68" s="57">
         <f t="shared" si="12"/>
         <v>3866</v>
       </c>
-      <c r="AK68" s="62">
+      <c r="AK68" s="57">
         <f t="shared" si="12"/>
         <v>1445.217584</v>
       </c>
-      <c r="AL68" s="62">
+      <c r="AL68" s="57">
         <f t="shared" si="12"/>
         <v>1090883.4385170001</v>
       </c>
-      <c r="AM68" s="62">
+      <c r="AM68" s="57">
         <f t="shared" si="12"/>
         <v>245825</v>
       </c>
-      <c r="AN68" s="62">
+      <c r="AN68" s="57">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AO68" s="62">
+      <c r="AO68" s="57">
         <f t="shared" si="12"/>
         <v>5.0941312299999995</v>
       </c>
-      <c r="AP68" s="62">
+      <c r="AP68" s="57">
         <f t="shared" si="12"/>
         <v>0.77758749999999999</v>
       </c>
-      <c r="AQ68" s="62">
+      <c r="AQ68" s="57">
         <f t="shared" si="12"/>
         <v>14288.148000000001</v>
       </c>
-      <c r="AR68" s="62">
+      <c r="AR68" s="57">
         <f t="shared" si="12"/>
         <v>18268.95</v>
       </c>
-      <c r="AS68" s="62">
+      <c r="AS68" s="57">
         <f t="shared" si="12"/>
         <v>938884.25425666687</v>
       </c>
-      <c r="AT68" s="62">
+      <c r="AT68" s="57">
         <f t="shared" si="12"/>
         <v>910231.25</v>
       </c>
-      <c r="AU68" s="62">
+      <c r="AU68" s="57">
         <f t="shared" si="12"/>
         <v>2833.7599686274507</v>
       </c>
-      <c r="AV68" s="62">
+      <c r="AV68" s="57">
         <f t="shared" si="12"/>
         <v>164566.877034</v>
       </c>
-      <c r="AW68" s="62">
+      <c r="AW68" s="57">
         <f t="shared" si="12"/>
         <v>409708.33333333337</v>
       </c>
-      <c r="AX68" s="62">
+      <c r="AX68" s="57">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AY68" s="62">
+      <c r="AY68" s="57">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AZ68" s="62">
+      <c r="AZ68" s="57">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="BA68" s="62">
+      <c r="BA68" s="57">
         <f t="shared" si="12"/>
         <v>16809.585882352942</v>
       </c>
-      <c r="BB68" s="62" t="e">
+      <c r="BB68" s="57" t="e">
         <f t="shared" si="12"/>
         <v>#REF!</v>
       </c>
-      <c r="BC68" s="63">
+      <c r="BC68" s="58">
         <f t="shared" si="12"/>
         <v>215.43763719285494</v>
       </c>
@@ -35236,7 +35224,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29AC4CBE-FB64-41C9-95AB-B4C2DC9E9DC5}">
-  <dimension ref="A1:S66"/>
+  <dimension ref="A1:S58"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.85546875" bestFit="1" customWidth="1"/>
@@ -35257,10 +35245,10 @@
         <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>918</v>
@@ -35283,2738 +35271,2402 @@
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="str">
-        <f>prod_data!C2</f>
-        <v>Bloom Lake</v>
+        <f>prod_data!C3</f>
+        <v>Brucejack</v>
       </c>
       <c r="B2">
-        <f>prod_data!D2</f>
+        <f>prod_data!D3</f>
         <v>0</v>
       </c>
       <c r="C2" t="str">
-        <f>prod_data!U2</f>
-        <v>Iron</v>
+        <f>prod_data!U3</f>
+        <v>Gold, silver</v>
       </c>
       <c r="D2" t="str">
-        <f>prod_data!X2</f>
-        <v>Fe conc.</v>
-      </c>
-      <c r="E2" s="71">
-        <f>prod_data!Z2/prod_data!$Z$68</f>
-        <v>0</v>
-      </c>
-      <c r="F2" s="70">
-        <f>prod_data!AS2/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G2" s="71">
-        <f>prod_data!AT2/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H2" s="71">
-        <f>prod_data!BA2/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I2" s="71">
-        <f>prod_data!AV2/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J2" s="71">
-        <f>prod_data!AU2/prod_data!$AU$68</f>
+        <f>prod_data!X3</f>
+        <v>Au-Ag doré</v>
+      </c>
+      <c r="E2" s="66">
+        <f>prod_data!Z3/prod_data!$Z$68</f>
+        <v>4.2722790031976673E-3</v>
+      </c>
+      <c r="F2" s="65">
+        <f>prod_data!AS3/prod_data!$AS$68</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="66">
+        <f>prod_data!AT3/prod_data!$AT$68</f>
+        <v>0</v>
+      </c>
+      <c r="H2" s="66">
+        <f>prod_data!BA3/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="66">
+        <f>prod_data!AV3/prod_data!$AV$68</f>
+        <v>0</v>
+      </c>
+      <c r="J2" s="66">
+        <f>prod_data!AU3/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
-        <f>prod_data!C3</f>
-        <v>Brucejack</v>
+        <f>prod_data!C5</f>
+        <v>Canadian Malartic</v>
       </c>
       <c r="B3">
-        <f>prod_data!D3</f>
+        <f>prod_data!D5</f>
         <v>0</v>
       </c>
       <c r="C3" t="str">
-        <f>prod_data!U3</f>
+        <f>prod_data!U5</f>
         <v>Gold, silver</v>
       </c>
       <c r="D3" t="str">
-        <f>prod_data!X3</f>
+        <f>prod_data!X5</f>
         <v>Au-Ag doré</v>
       </c>
-      <c r="E3" s="71">
-        <f>prod_data!Z3/prod_data!$Z$68</f>
-        <v>4.2722790031976673E-3</v>
-      </c>
-      <c r="F3" s="70">
-        <f>prod_data!AS3/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G3" s="71">
-        <f>prod_data!AT3/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H3" s="71">
-        <f>prod_data!BA3/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I3" s="71">
-        <f>prod_data!AV3/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J3" s="71">
-        <f>prod_data!AU3/prod_data!$AU$68</f>
+      <c r="E3" s="66">
+        <f>prod_data!Z5/prod_data!$Z$68</f>
+        <v>0.13479113915071453</v>
+      </c>
+      <c r="F3" s="65">
+        <f>prod_data!AS5/prod_data!$AS$68</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="66">
+        <f>prod_data!AT5/prod_data!$AT$68</f>
+        <v>0</v>
+      </c>
+      <c r="H3" s="66">
+        <f>prod_data!BA5/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="66">
+        <f>prod_data!AV5/prod_data!$AV$68</f>
+        <v>0</v>
+      </c>
+      <c r="J3" s="66">
+        <f>prod_data!AU5/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
-        <f>prod_data!C4</f>
-        <v>Canadian Electrolytic Zinc Limited (CEZinc)</v>
+        <f>prod_data!C7</f>
+        <v>Casa Berardi</v>
       </c>
       <c r="B4">
-        <f>prod_data!D4</f>
+        <f>prod_data!D7</f>
         <v>0</v>
       </c>
       <c r="C4" t="str">
-        <f>prod_data!U4</f>
-        <v>Lead, zinc</v>
-      </c>
-      <c r="D4">
-        <f>prod_data!X4</f>
-        <v>0</v>
-      </c>
-      <c r="E4" s="71">
-        <f>prod_data!Z4/prod_data!$Z$68</f>
-        <v>0</v>
-      </c>
-      <c r="F4" s="70">
-        <f>prod_data!AS4/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G4" s="71">
-        <f>prod_data!AT4/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H4" s="71">
-        <f>prod_data!BA4/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I4" s="71">
-        <f>prod_data!AV4/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J4" s="71">
-        <f>prod_data!AU4/prod_data!$AU$68</f>
+        <f>prod_data!U7</f>
+        <v>Gold, silver</v>
+      </c>
+      <c r="D4" t="str">
+        <f>prod_data!X7</f>
+        <v>Au-Ag doré</v>
+      </c>
+      <c r="E4" s="66">
+        <f>prod_data!Z7/prod_data!$Z$68</f>
+        <v>1.6323052191527593E-2</v>
+      </c>
+      <c r="F4" s="65">
+        <f>prod_data!AS7/prod_data!$AS$68</f>
+        <v>0</v>
+      </c>
+      <c r="G4" s="66">
+        <f>prod_data!AT7/prod_data!$AT$68</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="66">
+        <f>prod_data!BA7/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="66">
+        <f>prod_data!AV7/prod_data!$AV$68</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="66">
+        <f>prod_data!AU7/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
-        <f>prod_data!C5</f>
-        <v>Canadian Malartic</v>
-      </c>
-      <c r="B5">
-        <f>prod_data!D5</f>
-        <v>0</v>
+        <f>prod_data!C8</f>
+        <v>Copper Cliff Complex (mine)</v>
+      </c>
+      <c r="B5" t="str">
+        <f>prod_data!D8</f>
+        <v>Sudbury Operation</v>
       </c>
       <c r="C5" t="str">
-        <f>prod_data!U5</f>
-        <v>Gold, silver</v>
+        <f>prod_data!U8</f>
+        <v>Nickel, copper, platinum group metals, gold, silver, cobalt, selenium, tellurium</v>
       </c>
       <c r="D5" t="str">
-        <f>prod_data!X5</f>
-        <v>Au-Ag doré</v>
-      </c>
-      <c r="E5" s="71">
-        <f>prod_data!Z5/prod_data!$Z$68</f>
-        <v>0.13479113915071453</v>
-      </c>
-      <c r="F5" s="70">
-        <f>prod_data!AS5/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G5" s="71">
-        <f>prod_data!AT5/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H5" s="71">
-        <f>prod_data!BA5/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I5" s="71">
-        <f>prod_data!AV5/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J5" s="71">
-        <f>prod_data!AU5/prod_data!$AU$68</f>
+        <f>prod_data!X8</f>
+        <v>Ni-Cu bulk conc.</v>
+      </c>
+      <c r="E5" s="66">
+        <f>prod_data!Z8/prod_data!$Z$68</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="65">
+        <f>prod_data!AS8/prod_data!$AS$68</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="66">
+        <f>prod_data!AT8/prod_data!$AT$68</f>
+        <v>6.00877524255512E-2</v>
+      </c>
+      <c r="H5" s="66">
+        <f>prod_data!BA8/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="66">
+        <f>prod_data!AV8/prod_data!$AV$68</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="66">
+        <f>prod_data!AU8/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
-        <f>prod_data!C6</f>
-        <v>Carol Lake</v>
-      </c>
-      <c r="B6">
-        <f>prod_data!D6</f>
-        <v>0</v>
+        <f>prod_data!C9</f>
+        <v>Copper Cliff Complex (refinery)</v>
+      </c>
+      <c r="B6" t="str">
+        <f>prod_data!D9</f>
+        <v>Sudbury Operation</v>
       </c>
       <c r="C6" t="str">
-        <f>prod_data!U6</f>
-        <v>Iron</v>
+        <f>prod_data!U9</f>
+        <v>Nickel (oxide sinter, pellets, powder, sulfide), copper cathodes, gold, silver, selenium cake, tellurium dioxide cake, platinum group metals (in residues), liquid sulfur dioxide, sulfuric acid</v>
       </c>
       <c r="D6" t="str">
-        <f>prod_data!X6</f>
-        <v>Fe conc., Fe pellets</v>
-      </c>
-      <c r="E6" s="71">
-        <f>prod_data!Z6/prod_data!$Z$68</f>
-        <v>0</v>
-      </c>
-      <c r="F6" s="70">
-        <f>prod_data!AS6/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G6" s="71">
-        <f>prod_data!AT6/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H6" s="71">
-        <f>prod_data!BA6/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="71">
-        <f>prod_data!AV6/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J6" s="71">
-        <f>prod_data!AU6/prod_data!$AU$68</f>
+        <f>prod_data!X9</f>
+        <v>Refined Ni+Cu</v>
+      </c>
+      <c r="E6" s="66">
+        <f>prod_data!Z9/prod_data!$Z$68</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="65">
+        <f>prod_data!AS9/prod_data!$AS$68</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="66">
+        <f>prod_data!AT9/prod_data!$AT$68</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="66">
+        <f>prod_data!BA9/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="66">
+        <f>prod_data!AV9/prod_data!$AV$68</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="66">
+        <f>prod_data!AU9/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
-        <f>prod_data!C7</f>
-        <v>Casa Berardi</v>
+        <f>prod_data!C10</f>
+        <v>Copper Mountain</v>
       </c>
       <c r="B7">
-        <f>prod_data!D7</f>
+        <f>prod_data!D10</f>
         <v>0</v>
       </c>
       <c r="C7" t="str">
-        <f>prod_data!U7</f>
-        <v>Gold, silver</v>
+        <f>prod_data!U10</f>
+        <v>Copper, gold, silver</v>
       </c>
       <c r="D7" t="str">
-        <f>prod_data!X7</f>
-        <v>Au-Ag doré</v>
-      </c>
-      <c r="E7" s="71">
-        <f>prod_data!Z7/prod_data!$Z$68</f>
-        <v>1.6323052191527593E-2</v>
-      </c>
-      <c r="F7" s="70">
-        <f>prod_data!AS7/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G7" s="71">
-        <f>prod_data!AT7/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H7" s="71">
-        <f>prod_data!BA7/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I7" s="71">
-        <f>prod_data!AV7/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J7" s="71">
-        <f>prod_data!AU7/prod_data!$AU$68</f>
+        <f>prod_data!X10</f>
+        <v>Cu conc.</v>
+      </c>
+      <c r="E7" s="66">
+        <f>prod_data!Z10/prod_data!$Z$68</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="65">
+        <f>prod_data!AS10/prod_data!$AS$68</f>
+        <v>6.7633469953412101E-2</v>
+      </c>
+      <c r="G7" s="66">
+        <f>prod_data!AT10/prod_data!$AT$68</f>
+        <v>0</v>
+      </c>
+      <c r="H7" s="66">
+        <f>prod_data!BA10/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="66">
+        <f>prod_data!AV10/prod_data!$AV$68</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="66">
+        <f>prod_data!AU10/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
-        <f>prod_data!C8</f>
-        <v>Copper Cliff Complex (mine)</v>
+        <f>prod_data!C11</f>
+        <v>Creighton</v>
       </c>
       <c r="B8" t="str">
-        <f>prod_data!D8</f>
+        <f>prod_data!D11</f>
         <v>Sudbury Operation</v>
       </c>
       <c r="C8" t="str">
-        <f>prod_data!U8</f>
+        <f>prod_data!U11</f>
         <v>Nickel, copper, platinum group metals, gold, silver, cobalt, selenium, tellurium</v>
       </c>
       <c r="D8" t="str">
-        <f>prod_data!X8</f>
+        <f>prod_data!X11</f>
         <v>Ni-Cu bulk conc.</v>
       </c>
-      <c r="E8" s="71">
-        <f>prod_data!Z8/prod_data!$Z$68</f>
-        <v>0</v>
-      </c>
-      <c r="F8" s="70">
-        <f>prod_data!AS8/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G8" s="71">
-        <f>prod_data!AT8/prod_data!$AT$68</f>
-        <v>6.00877524255512E-2</v>
-      </c>
-      <c r="H8" s="71">
-        <f>prod_data!BA8/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I8" s="71">
-        <f>prod_data!AV8/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J8" s="71">
-        <f>prod_data!AU8/prod_data!$AU$68</f>
+      <c r="E8" s="66">
+        <f>prod_data!Z11/prod_data!$Z$68</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="65">
+        <f>prod_data!AS11/prod_data!$AS$68</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="66">
+        <f>prod_data!AT11/prod_data!$AT$68</f>
+        <v>7.7892293853897024E-2</v>
+      </c>
+      <c r="H8" s="66">
+        <f>prod_data!BA11/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="66">
+        <f>prod_data!AV11/prod_data!$AV$68</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="66">
+        <f>prod_data!AU11/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
-        <f>prod_data!C9</f>
-        <v>Copper Cliff Complex (refinery)</v>
-      </c>
-      <c r="B9" t="str">
-        <f>prod_data!D9</f>
-        <v>Sudbury Operation</v>
+        <f>prod_data!C12</f>
+        <v>Detour Lake</v>
+      </c>
+      <c r="B9">
+        <f>prod_data!D12</f>
+        <v>0</v>
       </c>
       <c r="C9" t="str">
-        <f>prod_data!U9</f>
-        <v>Nickel (oxide sinter, pellets, powder, sulfide), copper cathodes, gold, silver, selenium cake, tellurium dioxide cake, platinum group metals (in residues), liquid sulfur dioxide, sulfuric acid</v>
+        <f>prod_data!U12</f>
+        <v>Gold</v>
       </c>
       <c r="D9" t="str">
-        <f>prod_data!X9</f>
-        <v>Refined Ni+Cu</v>
-      </c>
-      <c r="E9" s="71">
-        <f>prod_data!Z9/prod_data!$Z$68</f>
-        <v>0</v>
-      </c>
-      <c r="F9" s="70">
-        <f>prod_data!AS9/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G9" s="71">
-        <f>prod_data!AT9/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H9" s="71">
-        <f>prod_data!BA9/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I9" s="71">
-        <f>prod_data!AV9/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J9" s="71">
-        <f>prod_data!AU9/prod_data!$AU$68</f>
+        <f>prod_data!X12</f>
+        <v>Au-Ag doré</v>
+      </c>
+      <c r="E9" s="66">
+        <f>prod_data!Z12/prod_data!$Z$68</f>
+        <v>0.11143959871906423</v>
+      </c>
+      <c r="F9" s="65">
+        <f>prod_data!AS12/prod_data!$AS$68</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="66">
+        <f>prod_data!AT12/prod_data!$AT$68</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="66">
+        <f>prod_data!BA12/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="66">
+        <f>prod_data!AV12/prod_data!$AV$68</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="66">
+        <f>prod_data!AU12/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
-        <f>prod_data!C10</f>
-        <v>Copper Mountain</v>
+        <f>prod_data!C13</f>
+        <v>Eagle River</v>
       </c>
       <c r="B10">
-        <f>prod_data!D10</f>
+        <f>prod_data!D13</f>
         <v>0</v>
       </c>
       <c r="C10" t="str">
-        <f>prod_data!U10</f>
-        <v>Copper, gold, silver</v>
+        <f>prod_data!U13</f>
+        <v>Gold</v>
       </c>
       <c r="D10" t="str">
-        <f>prod_data!X10</f>
-        <v>Cu conc.</v>
-      </c>
-      <c r="E10" s="71">
-        <f>prod_data!Z10/prod_data!$Z$68</f>
-        <v>0</v>
-      </c>
-      <c r="F10" s="70">
-        <f>prod_data!AS10/prod_data!$AS$68</f>
-        <v>6.7633469953412101E-2</v>
-      </c>
-      <c r="G10" s="71">
-        <f>prod_data!AT10/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H10" s="71">
-        <f>prod_data!BA10/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I10" s="71">
-        <f>prod_data!AV10/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J10" s="71">
-        <f>prod_data!AU10/prod_data!$AU$68</f>
+        <f>prod_data!X13</f>
+        <v>Au-Ag doré</v>
+      </c>
+      <c r="E10" s="66">
+        <f>prod_data!Z13/prod_data!$Z$68</f>
+        <v>1.2885635433541048E-2</v>
+      </c>
+      <c r="F10" s="65">
+        <f>prod_data!AS13/prod_data!$AS$68</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="66">
+        <f>prod_data!AT13/prod_data!$AT$68</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="66">
+        <f>prod_data!BA13/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="66">
+        <f>prod_data!AV13/prod_data!$AV$68</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="66">
+        <f>prod_data!AU13/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
-        <f>prod_data!C11</f>
-        <v>Creighton</v>
-      </c>
-      <c r="B11" t="str">
-        <f>prod_data!D11</f>
-        <v>Sudbury Operation</v>
+        <f>prod_data!C14</f>
+        <v>Éléonore</v>
+      </c>
+      <c r="B11">
+        <f>prod_data!D14</f>
+        <v>0</v>
       </c>
       <c r="C11" t="str">
-        <f>prod_data!U11</f>
-        <v>Nickel, copper, platinum group metals, gold, silver, cobalt, selenium, tellurium</v>
+        <f>prod_data!U14</f>
+        <v>Gold, silver</v>
       </c>
       <c r="D11" t="str">
-        <f>prod_data!X11</f>
-        <v>Ni-Cu bulk conc.</v>
-      </c>
-      <c r="E11" s="71">
-        <f>prod_data!Z11/prod_data!$Z$68</f>
-        <v>0</v>
-      </c>
-      <c r="F11" s="70">
-        <f>prod_data!AS11/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G11" s="71">
-        <f>prod_data!AT11/prod_data!$AT$68</f>
-        <v>7.7892293853897024E-2</v>
-      </c>
-      <c r="H11" s="71">
-        <f>prod_data!BA11/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I11" s="71">
-        <f>prod_data!AV11/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J11" s="71">
-        <f>prod_data!AU11/prod_data!$AU$68</f>
+        <f>prod_data!X14</f>
+        <v>Au-Ag doré</v>
+      </c>
+      <c r="E11" s="66">
+        <f>prod_data!Z14/prod_data!$Z$68</f>
+        <v>3.5921763818782863E-2</v>
+      </c>
+      <c r="F11" s="65">
+        <f>prod_data!AS14/prod_data!$AS$68</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="66">
+        <f>prod_data!AT14/prod_data!$AT$68</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="66">
+        <f>prod_data!BA14/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="66">
+        <f>prod_data!AV14/prod_data!$AV$68</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="66">
+        <f>prod_data!AU14/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
-        <f>prod_data!C12</f>
-        <v>Detour Lake</v>
+        <f>prod_data!C15</f>
+        <v>Elk</v>
       </c>
       <c r="B12">
-        <f>prod_data!D12</f>
+        <f>prod_data!D15</f>
         <v>0</v>
       </c>
       <c r="C12" t="str">
-        <f>prod_data!U12</f>
+        <f>prod_data!U15</f>
         <v>Gold</v>
       </c>
       <c r="D12" t="str">
-        <f>prod_data!X12</f>
+        <f>prod_data!X15</f>
         <v>Au-Ag doré</v>
       </c>
-      <c r="E12" s="71">
-        <f>prod_data!Z12/prod_data!$Z$68</f>
-        <v>0.11143959871906423</v>
-      </c>
-      <c r="F12" s="70">
-        <f>prod_data!AS12/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G12" s="71">
-        <f>prod_data!AT12/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H12" s="71">
-        <f>prod_data!BA12/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I12" s="71">
-        <f>prod_data!AV12/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J12" s="71">
-        <f>prod_data!AU12/prod_data!$AU$68</f>
+      <c r="E12" s="66">
+        <f>prod_data!Z15/prod_data!$Z$68</f>
+        <v>5.7690498539731262E-4</v>
+      </c>
+      <c r="F12" s="65">
+        <f>prod_data!AS15/prod_data!$AS$68</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="66">
+        <f>prod_data!AT15/prod_data!$AT$68</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="66">
+        <f>prod_data!BA15/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="66">
+        <f>prod_data!AV15/prod_data!$AV$68</f>
+        <v>0</v>
+      </c>
+      <c r="J12" s="66">
+        <f>prod_data!AU15/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
-        <f>prod_data!C13</f>
-        <v>Eagle River</v>
+        <f>prod_data!C16</f>
+        <v>Fox Complex</v>
       </c>
       <c r="B13">
-        <f>prod_data!D13</f>
+        <f>prod_data!D16</f>
         <v>0</v>
       </c>
       <c r="C13" t="str">
-        <f>prod_data!U13</f>
+        <f>prod_data!U16</f>
         <v>Gold</v>
       </c>
       <c r="D13" t="str">
-        <f>prod_data!X13</f>
+        <f>prod_data!X16</f>
         <v>Au-Ag doré</v>
       </c>
-      <c r="E13" s="71">
-        <f>prod_data!Z13/prod_data!$Z$68</f>
-        <v>1.2885635433541048E-2</v>
-      </c>
-      <c r="F13" s="70">
-        <f>prod_data!AS13/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G13" s="71">
-        <f>prod_data!AT13/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H13" s="71">
-        <f>prod_data!BA13/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I13" s="71">
-        <f>prod_data!AV13/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J13" s="71">
-        <f>prod_data!AU13/prod_data!$AU$68</f>
+      <c r="E13" s="66">
+        <f>prod_data!Z16/prod_data!$Z$68</f>
+        <v>6.747254425739764E-3</v>
+      </c>
+      <c r="F13" s="65">
+        <f>prod_data!AS16/prod_data!$AS$68</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="66">
+        <f>prod_data!AT16/prod_data!$AT$68</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="66">
+        <f>prod_data!BA16/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="66">
+        <f>prod_data!AV16/prod_data!$AV$68</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="66">
+        <f>prod_data!AU16/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
-        <f>prod_data!C14</f>
-        <v>Éléonore</v>
-      </c>
-      <c r="B14">
-        <f>prod_data!D14</f>
-        <v>0</v>
+        <f>prod_data!C17</f>
+        <v>Fraser</v>
+      </c>
+      <c r="B14" t="str">
+        <f>prod_data!D17</f>
+        <v>Integrated Nickel Operations</v>
       </c>
       <c r="C14" t="str">
-        <f>prod_data!U14</f>
-        <v>Gold, silver</v>
+        <f>prod_data!U17</f>
+        <v>Nickel, copper, platinum group metals, gold, cobalt, silver</v>
       </c>
       <c r="D14" t="str">
-        <f>prod_data!X14</f>
-        <v>Au-Ag doré</v>
-      </c>
-      <c r="E14" s="71">
-        <f>prod_data!Z14/prod_data!$Z$68</f>
-        <v>3.5921763818782863E-2</v>
-      </c>
-      <c r="F14" s="70">
-        <f>prod_data!AS14/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G14" s="71">
-        <f>prod_data!AT14/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H14" s="71">
-        <f>prod_data!BA14/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I14" s="71">
-        <f>prod_data!AV14/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J14" s="71">
-        <f>prod_data!AU14/prod_data!$AU$68</f>
+        <f>prod_data!X17</f>
+        <v>Ni-Cu bulk conc.</v>
+      </c>
+      <c r="E14" s="66">
+        <f>prod_data!Z17/prod_data!$Z$68</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="65">
+        <f>prod_data!AS17/prod_data!$AS$68</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="66">
+        <f>prod_data!AT17/prod_data!$AT$68</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="66">
+        <f>prod_data!BA17/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="66">
+        <f>prod_data!AV17/prod_data!$AV$68</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="66">
+        <f>prod_data!AU17/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
-        <f>prod_data!C15</f>
-        <v>Elk</v>
-      </c>
-      <c r="B15">
-        <f>prod_data!D15</f>
-        <v>0</v>
+        <f>prod_data!C18</f>
+        <v>Garson</v>
+      </c>
+      <c r="B15" t="str">
+        <f>prod_data!D18</f>
+        <v>Sudbury Operation</v>
       </c>
       <c r="C15" t="str">
-        <f>prod_data!U15</f>
-        <v>Gold</v>
+        <f>prod_data!U18</f>
+        <v>Nickel, copper, platinum group metals, gold, silver, cobalt, selenium, tellurium</v>
       </c>
       <c r="D15" t="str">
-        <f>prod_data!X15</f>
-        <v>Au-Ag doré</v>
-      </c>
-      <c r="E15" s="71">
-        <f>prod_data!Z15/prod_data!$Z$68</f>
-        <v>5.7690498539731262E-4</v>
-      </c>
-      <c r="F15" s="70">
-        <f>prod_data!AS15/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G15" s="71">
-        <f>prod_data!AT15/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H15" s="71">
-        <f>prod_data!BA15/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I15" s="71">
-        <f>prod_data!AV15/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J15" s="71">
-        <f>prod_data!AU15/prod_data!$AU$68</f>
+        <f>prod_data!X18</f>
+        <v>Ni-Cu bulk conc.</v>
+      </c>
+      <c r="E15" s="66">
+        <f>prod_data!Z18/prod_data!$Z$68</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="65">
+        <f>prod_data!AS18/prod_data!$AS$68</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="66">
+        <f>prod_data!AT18/prod_data!$AT$68</f>
+        <v>5.4560310910002269E-2</v>
+      </c>
+      <c r="H15" s="66">
+        <f>prod_data!BA18/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="66">
+        <f>prod_data!AV18/prod_data!$AV$68</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="66">
+        <f>prod_data!AU18/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
-        <f>prod_data!C16</f>
-        <v>Fox Complex</v>
+        <f>prod_data!C19</f>
+        <v>Gibraltar</v>
       </c>
       <c r="B16">
-        <f>prod_data!D16</f>
+        <f>prod_data!D19</f>
         <v>0</v>
       </c>
       <c r="C16" t="str">
-        <f>prod_data!U16</f>
-        <v>Gold</v>
+        <f>prod_data!U19</f>
+        <v>Copper, molybdenum, silver</v>
       </c>
       <c r="D16" t="str">
-        <f>prod_data!X16</f>
-        <v>Au-Ag doré</v>
-      </c>
-      <c r="E16" s="71">
-        <f>prod_data!Z16/prod_data!$Z$68</f>
-        <v>6.747254425739764E-3</v>
-      </c>
-      <c r="F16" s="70">
-        <f>prod_data!AS16/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G16" s="71">
-        <f>prod_data!AT16/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="71">
-        <f>prod_data!BA16/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I16" s="71">
-        <f>prod_data!AV16/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J16" s="71">
-        <f>prod_data!AU16/prod_data!$AU$68</f>
-        <v>0</v>
+        <f>prod_data!X19</f>
+        <v>Cu and Mo conc.</v>
+      </c>
+      <c r="E16" s="66">
+        <f>prod_data!Z19/prod_data!$Z$68</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="65">
+        <f>prod_data!AS19/prod_data!$AS$68</f>
+        <v>0.19743427352866422</v>
+      </c>
+      <c r="G16" s="66">
+        <f>prod_data!AT19/prod_data!$AT$68</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="66">
+        <f>prod_data!BA19/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="66">
+        <f>prod_data!AV19/prod_data!$AV$68</f>
+        <v>0</v>
+      </c>
+      <c r="J16" s="66">
+        <f>prod_data!AU19/prod_data!$AU$68</f>
+        <v>0.37725640072201061</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
-        <f>prod_data!C17</f>
-        <v>Fraser</v>
-      </c>
-      <c r="B17" t="str">
-        <f>prod_data!D17</f>
-        <v>Integrated Nickel Operations</v>
+        <f>prod_data!C20</f>
+        <v>Goldex</v>
+      </c>
+      <c r="B17">
+        <f>prod_data!D20</f>
+        <v>0</v>
       </c>
       <c r="C17" t="str">
-        <f>prod_data!U17</f>
-        <v>Nickel, copper, platinum group metals, gold, cobalt, silver</v>
+        <f>prod_data!U20</f>
+        <v>Gold, silver</v>
       </c>
       <c r="D17" t="str">
-        <f>prod_data!X17</f>
-        <v>Ni-Cu bulk conc.</v>
-      </c>
-      <c r="E17" s="71">
-        <f>prod_data!Z17/prod_data!$Z$68</f>
-        <v>0</v>
-      </c>
-      <c r="F17" s="70">
-        <f>prod_data!AS17/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G17" s="71">
-        <f>prod_data!AT17/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H17" s="71">
-        <f>prod_data!BA17/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I17" s="71">
-        <f>prod_data!AV17/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J17" s="71">
-        <f>prod_data!AU17/prod_data!$AU$68</f>
+        <f>prod_data!X20</f>
+        <v>Au-Ag doré, Cu conc.</v>
+      </c>
+      <c r="E17" s="66">
+        <f>prod_data!Z20/prod_data!$Z$68</f>
+        <v>2.0769546939986089E-2</v>
+      </c>
+      <c r="F17" s="65">
+        <f>prod_data!AS20/prod_data!$AS$68</f>
+        <v>1.3859272437121361E-4</v>
+      </c>
+      <c r="G17" s="66">
+        <f>prod_data!AT20/prod_data!$AT$68</f>
+        <v>0</v>
+      </c>
+      <c r="H17" s="66">
+        <f>prod_data!BA20/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="66">
+        <f>prod_data!AV20/prod_data!$AV$68</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="66">
+        <f>prod_data!AU20/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
-        <f>prod_data!C18</f>
-        <v>Garson</v>
-      </c>
-      <c r="B18" t="str">
-        <f>prod_data!D18</f>
-        <v>Sudbury Operation</v>
+        <f>prod_data!C21</f>
+        <v>Hemlo (Williams)</v>
+      </c>
+      <c r="B18">
+        <f>prod_data!D21</f>
+        <v>0</v>
       </c>
       <c r="C18" t="str">
-        <f>prod_data!U18</f>
-        <v>Nickel, copper, platinum group metals, gold, silver, cobalt, selenium, tellurium</v>
+        <f>prod_data!U21</f>
+        <v>Gold</v>
       </c>
       <c r="D18" t="str">
-        <f>prod_data!X18</f>
-        <v>Ni-Cu bulk conc.</v>
-      </c>
-      <c r="E18" s="71">
-        <f>prod_data!Z18/prod_data!$Z$68</f>
-        <v>0</v>
-      </c>
-      <c r="F18" s="70">
-        <f>prod_data!AS18/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G18" s="71">
-        <f>prod_data!AT18/prod_data!$AT$68</f>
-        <v>5.4560310910002269E-2</v>
-      </c>
-      <c r="H18" s="71">
-        <f>prod_data!BA18/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I18" s="71">
-        <f>prod_data!AV18/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J18" s="71">
-        <f>prod_data!AU18/prod_data!$AU$68</f>
+        <f>prod_data!X21</f>
+        <v>Au-Ag doré</v>
+      </c>
+      <c r="E18" s="66">
+        <f>prod_data!Z21/prod_data!$Z$68</f>
+        <v>2.0778744551931554E-2</v>
+      </c>
+      <c r="F18" s="65">
+        <f>prod_data!AS21/prod_data!$AS$68</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="66">
+        <f>prod_data!AT21/prod_data!$AT$68</f>
+        <v>0</v>
+      </c>
+      <c r="H18" s="66">
+        <f>prod_data!BA21/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="66">
+        <f>prod_data!AV21/prod_data!$AV$68</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="66">
+        <f>prod_data!AU21/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
-        <f>prod_data!C19</f>
-        <v>Gibraltar</v>
+        <f>prod_data!C22</f>
+        <v>Highland Valley</v>
       </c>
       <c r="B19">
-        <f>prod_data!D19</f>
+        <f>prod_data!D22</f>
         <v>0</v>
       </c>
       <c r="C19" t="str">
-        <f>prod_data!U19</f>
-        <v>Copper, molybdenum, silver</v>
+        <f>prod_data!U22</f>
+        <v>Copper, silver, molybdenum</v>
       </c>
       <c r="D19" t="str">
-        <f>prod_data!X19</f>
+        <f>prod_data!X22</f>
         <v>Cu and Mo conc.</v>
       </c>
-      <c r="E19" s="71">
-        <f>prod_data!Z19/prod_data!$Z$68</f>
-        <v>0</v>
-      </c>
-      <c r="F19" s="70">
-        <f>prod_data!AS19/prod_data!$AS$68</f>
-        <v>0.19743427352866422</v>
-      </c>
-      <c r="G19" s="71">
-        <f>prod_data!AT19/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H19" s="71">
-        <f>prod_data!BA19/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I19" s="71">
-        <f>prod_data!AV19/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J19" s="71">
-        <f>prod_data!AU19/prod_data!$AU$68</f>
-        <v>0.37725640072201061</v>
+      <c r="E19" s="66">
+        <f>prod_data!Z22/prod_data!$Z$68</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="65">
+        <f>prod_data!AS22/prod_data!$AS$68</f>
+        <v>0.36355209045823617</v>
+      </c>
+      <c r="G19" s="66">
+        <f>prod_data!AT22/prod_data!$AT$68</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="66">
+        <f>prod_data!BA22/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="66">
+        <f>prod_data!AV22/prod_data!$AV$68</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="66">
+        <f>prod_data!AU22/prod_data!$AU$68</f>
+        <v>0.6227435992779895</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
-        <f>prod_data!C20</f>
-        <v>Goldex</v>
-      </c>
-      <c r="B20">
-        <f>prod_data!D20</f>
-        <v>0</v>
+        <f>prod_data!C23</f>
+        <v>Horne</v>
+      </c>
+      <c r="B20" t="str">
+        <f>prod_data!D23</f>
+        <v>CCR</v>
       </c>
       <c r="C20" t="str">
-        <f>prod_data!U20</f>
-        <v>Gold, silver</v>
-      </c>
-      <c r="D20" t="str">
-        <f>prod_data!X20</f>
-        <v>Au-Ag doré, Cu conc.</v>
-      </c>
-      <c r="E20" s="71">
-        <f>prod_data!Z20/prod_data!$Z$68</f>
-        <v>2.0769546939986089E-2</v>
-      </c>
-      <c r="F20" s="70">
-        <f>prod_data!AS20/prod_data!$AS$68</f>
-        <v>1.3859272437121361E-4</v>
-      </c>
-      <c r="G20" s="71">
-        <f>prod_data!AT20/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H20" s="71">
-        <f>prod_data!BA20/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I20" s="71">
-        <f>prod_data!AV20/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J20" s="71">
-        <f>prod_data!AU20/prod_data!$AU$68</f>
+        <f>prod_data!U23</f>
+        <v>Copper anodes, precious metals, sulfuric acid</v>
+      </c>
+      <c r="D20">
+        <f>prod_data!X23</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="66">
+        <f>prod_data!Z23/prod_data!$Z$68</f>
+        <v>0</v>
+      </c>
+      <c r="F20" s="65">
+        <f>prod_data!AS23/prod_data!$AS$68</f>
+        <v>0</v>
+      </c>
+      <c r="G20" s="66">
+        <f>prod_data!AT23/prod_data!$AT$68</f>
+        <v>0</v>
+      </c>
+      <c r="H20" s="66">
+        <f>prod_data!BA23/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I20" s="66">
+        <f>prod_data!AV23/prod_data!$AV$68</f>
+        <v>0</v>
+      </c>
+      <c r="J20" s="66">
+        <f>prod_data!AU23/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
-        <f>prod_data!C21</f>
-        <v>Hemlo (Williams)</v>
+        <f>prod_data!C24</f>
+        <v>Island</v>
       </c>
       <c r="B21">
-        <f>prod_data!D21</f>
+        <f>prod_data!D24</f>
         <v>0</v>
       </c>
       <c r="C21" t="str">
-        <f>prod_data!U21</f>
+        <f>prod_data!U24</f>
         <v>Gold</v>
       </c>
       <c r="D21" t="str">
-        <f>prod_data!X21</f>
+        <f>prod_data!X24</f>
         <v>Au-Ag doré</v>
       </c>
-      <c r="E21" s="71">
-        <f>prod_data!Z21/prod_data!$Z$68</f>
-        <v>2.0778744551931554E-2</v>
-      </c>
-      <c r="F21" s="70">
-        <f>prod_data!AS21/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G21" s="71">
-        <f>prod_data!AT21/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H21" s="71">
-        <f>prod_data!BA21/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I21" s="71">
-        <f>prod_data!AV21/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J21" s="71">
-        <f>prod_data!AU21/prod_data!$AU$68</f>
+      <c r="E21" s="66">
+        <f>prod_data!Z24/prod_data!$Z$68</f>
+        <v>1.9357843483454262E-2</v>
+      </c>
+      <c r="F21" s="65">
+        <f>prod_data!AS24/prod_data!$AS$68</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="66">
+        <f>prod_data!AT24/prod_data!$AT$68</f>
+        <v>0</v>
+      </c>
+      <c r="H21" s="66">
+        <f>prod_data!BA24/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I21" s="66">
+        <f>prod_data!AV24/prod_data!$AV$68</f>
+        <v>0</v>
+      </c>
+      <c r="J21" s="66">
+        <f>prod_data!AU24/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
-        <f>prod_data!C22</f>
-        <v>Highland Valley</v>
-      </c>
-      <c r="B22">
-        <f>prod_data!D22</f>
-        <v>0</v>
+        <f>prod_data!C25</f>
+        <v>Keno Hill Silver District</v>
+      </c>
+      <c r="B22" t="str">
+        <f>prod_data!D25</f>
+        <v>Key Lake + McArthur River</v>
       </c>
       <c r="C22" t="str">
-        <f>prod_data!U22</f>
-        <v>Copper, silver, molybdenum</v>
+        <f>prod_data!U25</f>
+        <v>Silver, zinc, lead</v>
       </c>
       <c r="D22" t="str">
-        <f>prod_data!X22</f>
-        <v>Cu and Mo conc.</v>
-      </c>
-      <c r="E22" s="71">
-        <f>prod_data!Z22/prod_data!$Z$68</f>
-        <v>0</v>
-      </c>
-      <c r="F22" s="70">
-        <f>prod_data!AS22/prod_data!$AS$68</f>
-        <v>0.36355209045823617</v>
-      </c>
-      <c r="G22" s="71">
-        <f>prod_data!AT22/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H22" s="71">
-        <f>prod_data!BA22/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I22" s="71">
-        <f>prod_data!AV22/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J22" s="71">
-        <f>prod_data!AU22/prod_data!$AU$68</f>
-        <v>0.6227435992779895</v>
+        <f>prod_data!X25</f>
+        <v>Pb and Zn conc.</v>
+      </c>
+      <c r="E22" s="66">
+        <f>prod_data!Z25/prod_data!$Z$68</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="65">
+        <f>prod_data!AS25/prod_data!$AS$68</f>
+        <v>0</v>
+      </c>
+      <c r="G22" s="66">
+        <f>prod_data!AT25/prod_data!$AT$68</f>
+        <v>0</v>
+      </c>
+      <c r="H22" s="66">
+        <f>prod_data!BA25/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I22" s="66">
+        <f>prod_data!AV25/prod_data!$AV$68</f>
+        <v>1.6273019505904079E-2</v>
+      </c>
+      <c r="J22" s="66">
+        <f>prod_data!AU25/prod_data!$AU$68</f>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
-        <f>prod_data!C23</f>
-        <v>Horne</v>
-      </c>
-      <c r="B23" t="str">
-        <f>prod_data!D23</f>
-        <v>CCR</v>
+        <f>prod_data!C26</f>
+        <v>Kidd Creek</v>
+      </c>
+      <c r="B23">
+        <f>prod_data!D26</f>
+        <v>0</v>
       </c>
       <c r="C23" t="str">
-        <f>prod_data!U23</f>
-        <v>Copper anodes, precious metals, sulfuric acid</v>
-      </c>
-      <c r="D23">
-        <f>prod_data!X23</f>
-        <v>0</v>
-      </c>
-      <c r="E23" s="71">
-        <f>prod_data!Z23/prod_data!$Z$68</f>
-        <v>0</v>
-      </c>
-      <c r="F23" s="70">
-        <f>prod_data!AS23/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G23" s="71">
-        <f>prod_data!AT23/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H23" s="71">
-        <f>prod_data!BA23/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I23" s="71">
-        <f>prod_data!AV23/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J23" s="71">
-        <f>prod_data!AU23/prod_data!$AU$68</f>
+        <f>prod_data!U26</f>
+        <v>Copper, zinc, silver, selenium, indium</v>
+      </c>
+      <c r="D23" t="str">
+        <f>prod_data!X26</f>
+        <v>Cu and Zn conc.</v>
+      </c>
+      <c r="E23" s="66">
+        <f>prod_data!Z26/prod_data!$Z$68</f>
+        <v>0</v>
+      </c>
+      <c r="F23" s="65">
+        <f>prod_data!AS26/prod_data!$AS$68</f>
+        <v>8.023708246441541E-2</v>
+      </c>
+      <c r="G23" s="66">
+        <f>prod_data!AT26/prod_data!$AT$68</f>
+        <v>0</v>
+      </c>
+      <c r="H23" s="66">
+        <f>prod_data!BA26/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I23" s="66">
+        <f>prod_data!AV26/prod_data!$AV$68</f>
+        <v>0.46911019636138718</v>
+      </c>
+      <c r="J23" s="66">
+        <f>prod_data!AU26/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
-        <f>prod_data!C24</f>
-        <v>Island</v>
+        <f>prod_data!C27</f>
+        <v>Kiena</v>
       </c>
       <c r="B24">
-        <f>prod_data!D24</f>
+        <f>prod_data!D27</f>
         <v>0</v>
       </c>
       <c r="C24" t="str">
-        <f>prod_data!U24</f>
-        <v>Gold</v>
+        <f>prod_data!U27</f>
+        <v>Gold, silver</v>
       </c>
       <c r="D24" t="str">
-        <f>prod_data!X24</f>
+        <f>prod_data!X27</f>
         <v>Au-Ag doré</v>
       </c>
-      <c r="E24" s="71">
-        <f>prod_data!Z24/prod_data!$Z$68</f>
-        <v>1.9357843483454262E-2</v>
-      </c>
-      <c r="F24" s="70">
-        <f>prod_data!AS24/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G24" s="71">
-        <f>prod_data!AT24/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H24" s="71">
-        <f>prod_data!BA24/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I24" s="71">
-        <f>prod_data!AV24/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J24" s="71">
-        <f>prod_data!AU24/prod_data!$AU$68</f>
+      <c r="E24" s="66">
+        <f>prod_data!Z27/prod_data!$Z$68</f>
+        <v>5.6637160785494587E-3</v>
+      </c>
+      <c r="F24" s="65">
+        <f>prod_data!AS27/prod_data!$AS$68</f>
+        <v>0</v>
+      </c>
+      <c r="G24" s="66">
+        <f>prod_data!AT27/prod_data!$AT$68</f>
+        <v>0</v>
+      </c>
+      <c r="H24" s="66">
+        <f>prod_data!BA27/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I24" s="66">
+        <f>prod_data!AV27/prod_data!$AV$68</f>
+        <v>0</v>
+      </c>
+      <c r="J24" s="66">
+        <f>prod_data!AU27/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
-        <f>prod_data!C25</f>
-        <v>Keno Hill Silver District</v>
-      </c>
-      <c r="B25" t="str">
-        <f>prod_data!D25</f>
-        <v>Key Lake + McArthur River</v>
+        <f>prod_data!C28</f>
+        <v>Lac des Iles</v>
+      </c>
+      <c r="B25">
+        <f>prod_data!D28</f>
+        <v>0</v>
       </c>
       <c r="C25" t="str">
-        <f>prod_data!U25</f>
-        <v>Silver, zinc, lead</v>
+        <f>prod_data!U28</f>
+        <v>Platinum group metals, gold, nickel, copper, cobalt</v>
       </c>
       <c r="D25" t="str">
-        <f>prod_data!X25</f>
-        <v>Pb and Zn conc.</v>
-      </c>
-      <c r="E25" s="71">
-        <f>prod_data!Z25/prod_data!$Z$68</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="70">
-        <f>prod_data!AS25/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="71">
-        <f>prod_data!AT25/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="71">
-        <f>prod_data!BA25/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I25" s="71">
-        <f>prod_data!AV25/prod_data!$AV$68</f>
-        <v>1.6273019505904079E-2</v>
-      </c>
-      <c r="J25" s="71">
-        <f>prod_data!AU25/prod_data!$AU$68</f>
+        <f>prod_data!X28</f>
+        <v>PGM bulk conc.</v>
+      </c>
+      <c r="E25" s="66">
+        <f>prod_data!Z28/prod_data!$Z$68</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="65">
+        <f>prod_data!AS28/prod_data!$AS$68</f>
+        <v>0</v>
+      </c>
+      <c r="G25" s="66">
+        <f>prod_data!AT28/prod_data!$AT$68</f>
+        <v>0</v>
+      </c>
+      <c r="H25" s="66">
+        <f>prod_data!BA28/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I25" s="66">
+        <f>prod_data!AV28/prod_data!$AV$68</f>
+        <v>0</v>
+      </c>
+      <c r="J25" s="66">
+        <f>prod_data!AU28/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
-        <f>prod_data!C26</f>
-        <v>Kidd Creek</v>
+        <f>prod_data!C29</f>
+        <v>Lamaque</v>
       </c>
       <c r="B26">
-        <f>prod_data!D26</f>
+        <f>prod_data!D29</f>
         <v>0</v>
       </c>
       <c r="C26" t="str">
-        <f>prod_data!U26</f>
-        <v>Copper, zinc, silver, selenium, indium</v>
+        <f>prod_data!U29</f>
+        <v>Gold, silver</v>
       </c>
       <c r="D26" t="str">
-        <f>prod_data!X26</f>
-        <v>Cu and Zn conc.</v>
-      </c>
-      <c r="E26" s="71">
-        <f>prod_data!Z26/prod_data!$Z$68</f>
-        <v>0</v>
-      </c>
-      <c r="F26" s="70">
-        <f>prod_data!AS26/prod_data!$AS$68</f>
-        <v>8.023708246441541E-2</v>
-      </c>
-      <c r="G26" s="71">
-        <f>prod_data!AT26/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H26" s="71">
-        <f>prod_data!BA26/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I26" s="71">
-        <f>prod_data!AV26/prod_data!$AV$68</f>
-        <v>0.46911019636138718</v>
-      </c>
-      <c r="J26" s="71">
-        <f>prod_data!AU26/prod_data!$AU$68</f>
+        <f>prod_data!X29</f>
+        <v>Au-Ag doré</v>
+      </c>
+      <c r="E26" s="66">
+        <f>prod_data!Z29/prod_data!$Z$68</f>
+        <v>3.6821888808766925E-2</v>
+      </c>
+      <c r="F26" s="65">
+        <f>prod_data!AS29/prod_data!$AS$68</f>
+        <v>0</v>
+      </c>
+      <c r="G26" s="66">
+        <f>prod_data!AT29/prod_data!$AT$68</f>
+        <v>0</v>
+      </c>
+      <c r="H26" s="66">
+        <f>prod_data!BA29/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I26" s="66">
+        <f>prod_data!AV29/prod_data!$AV$68</f>
+        <v>0</v>
+      </c>
+      <c r="J26" s="66">
+        <f>prod_data!AU29/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
-        <f>prod_data!C27</f>
-        <v>Kiena</v>
+        <f>prod_data!C30</f>
+        <v>LaRonde</v>
       </c>
       <c r="B27">
-        <f>prod_data!D27</f>
+        <f>prod_data!D30</f>
         <v>0</v>
       </c>
       <c r="C27" t="str">
-        <f>prod_data!U27</f>
-        <v>Gold, silver</v>
+        <f>prod_data!U30</f>
+        <v>Gold, zinc, copper, silver, cadmium</v>
       </c>
       <c r="D27" t="str">
-        <f>prod_data!X27</f>
-        <v>Au-Ag doré</v>
-      </c>
-      <c r="E27" s="71">
-        <f>prod_data!Z27/prod_data!$Z$68</f>
-        <v>5.6637160785494587E-3</v>
-      </c>
-      <c r="F27" s="70">
-        <f>prod_data!AS27/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G27" s="71">
-        <f>prod_data!AT27/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H27" s="71">
-        <f>prod_data!BA27/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I27" s="71">
-        <f>prod_data!AV27/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J27" s="71">
-        <f>prod_data!AU27/prod_data!$AU$68</f>
+        <f>prod_data!X30</f>
+        <v>Au-Ag doré, Cu and Zn conc.</v>
+      </c>
+      <c r="E27" s="66">
+        <f>prod_data!Z30/prod_data!$Z$68</f>
+        <v>4.5502275823470786E-2</v>
+      </c>
+      <c r="F27" s="65">
+        <f>prod_data!AS30/prod_data!$AS$68</f>
+        <v>9.1525672211889494E-3</v>
+      </c>
+      <c r="G27" s="66">
+        <f>prod_data!AT30/prod_data!$AT$68</f>
+        <v>0</v>
+      </c>
+      <c r="H27" s="66">
+        <f>prod_data!BA30/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I27" s="66">
+        <f>prod_data!AV30/prod_data!$AV$68</f>
+        <v>9.3608612569206773E-2</v>
+      </c>
+      <c r="J27" s="66">
+        <f>prod_data!AU30/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
-        <f>prod_data!C28</f>
-        <v>Lac des Iles</v>
+        <f>prod_data!C31</f>
+        <v>Long Harbour</v>
       </c>
       <c r="B28">
-        <f>prod_data!D28</f>
+        <f>prod_data!D31</f>
         <v>0</v>
       </c>
       <c r="C28" t="str">
-        <f>prod_data!U28</f>
-        <v>Platinum group metals, gold, nickel, copper, cobalt</v>
+        <f>prod_data!U31</f>
+        <v>Nickel</v>
       </c>
       <c r="D28" t="str">
-        <f>prod_data!X28</f>
-        <v>PGM bulk conc.</v>
-      </c>
-      <c r="E28" s="71">
-        <f>prod_data!Z28/prod_data!$Z$68</f>
-        <v>0</v>
-      </c>
-      <c r="F28" s="70">
-        <f>prod_data!AS28/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G28" s="71">
-        <f>prod_data!AT28/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H28" s="71">
-        <f>prod_data!BA28/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I28" s="71">
-        <f>prod_data!AV28/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J28" s="71">
-        <f>prod_data!AU28/prod_data!$AU$68</f>
+        <f>prod_data!X31</f>
+        <v>Refined Ni</v>
+      </c>
+      <c r="E28" s="66">
+        <f>prod_data!Z31/prod_data!$Z$68</f>
+        <v>0</v>
+      </c>
+      <c r="F28" s="65">
+        <f>prod_data!AS31/prod_data!$AS$68</f>
+        <v>0</v>
+      </c>
+      <c r="G28" s="66">
+        <f>prod_data!AT31/prod_data!$AT$68</f>
+        <v>0</v>
+      </c>
+      <c r="H28" s="66">
+        <f>prod_data!BA31/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I28" s="66">
+        <f>prod_data!AV31/prod_data!$AV$68</f>
+        <v>0</v>
+      </c>
+      <c r="J28" s="66">
+        <f>prod_data!AU31/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
-        <f>prod_data!C29</f>
-        <v>Lamaque</v>
+        <f>prod_data!C32</f>
+        <v>Macassa</v>
       </c>
       <c r="B29">
-        <f>prod_data!D29</f>
+        <f>prod_data!D32</f>
         <v>0</v>
       </c>
       <c r="C29" t="str">
-        <f>prod_data!U29</f>
+        <f>prod_data!U32</f>
         <v>Gold, silver</v>
       </c>
       <c r="D29" t="str">
-        <f>prod_data!X29</f>
+        <f>prod_data!X32</f>
         <v>Au-Ag doré</v>
       </c>
-      <c r="E29" s="71">
-        <f>prod_data!Z29/prod_data!$Z$68</f>
-        <v>3.6821888808766925E-2</v>
-      </c>
-      <c r="F29" s="70">
-        <f>prod_data!AS29/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G29" s="71">
-        <f>prod_data!AT29/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H29" s="71">
-        <f>prod_data!BA29/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I29" s="71">
-        <f>prod_data!AV29/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J29" s="71">
-        <f>prod_data!AU29/prod_data!$AU$68</f>
+      <c r="E29" s="66">
+        <f>prod_data!Z32/prod_data!$Z$68</f>
+        <v>3.3667768344682034E-2</v>
+      </c>
+      <c r="F29" s="65">
+        <f>prod_data!AS32/prod_data!$AS$68</f>
+        <v>0</v>
+      </c>
+      <c r="G29" s="66">
+        <f>prod_data!AT32/prod_data!$AT$68</f>
+        <v>0</v>
+      </c>
+      <c r="H29" s="66">
+        <f>prod_data!BA32/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I29" s="66">
+        <f>prod_data!AV32/prod_data!$AV$68</f>
+        <v>0</v>
+      </c>
+      <c r="J29" s="66">
+        <f>prod_data!AU32/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
-        <f>prod_data!C30</f>
-        <v>LaRonde</v>
+        <f>prod_data!C33</f>
+        <v>Magino</v>
       </c>
       <c r="B30">
-        <f>prod_data!D30</f>
+        <f>prod_data!D33</f>
         <v>0</v>
       </c>
       <c r="C30" t="str">
-        <f>prod_data!U30</f>
-        <v>Gold, zinc, copper, silver, cadmium</v>
+        <f>prod_data!U33</f>
+        <v>Gold, silver</v>
       </c>
       <c r="D30" t="str">
-        <f>prod_data!X30</f>
-        <v>Au-Ag doré, Cu and Zn conc.</v>
-      </c>
-      <c r="E30" s="71">
-        <f>prod_data!Z30/prod_data!$Z$68</f>
-        <v>4.5502275823470786E-2</v>
-      </c>
-      <c r="F30" s="70">
-        <f>prod_data!AS30/prod_data!$AS$68</f>
-        <v>9.1525672211889494E-3</v>
-      </c>
-      <c r="G30" s="71">
-        <f>prod_data!AT30/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H30" s="71">
-        <f>prod_data!BA30/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I30" s="71">
-        <f>prod_data!AV30/prod_data!$AV$68</f>
-        <v>9.3608612569206773E-2</v>
-      </c>
-      <c r="J30" s="71">
-        <f>prod_data!AU30/prod_data!$AU$68</f>
+        <f>prod_data!X33</f>
+        <v>Au-Ag doré</v>
+      </c>
+      <c r="E30" s="66">
+        <f>prod_data!Z33/prod_data!$Z$68</f>
+        <v>4.8615588657076906E-3</v>
+      </c>
+      <c r="F30" s="65">
+        <f>prod_data!AS33/prod_data!$AS$68</f>
+        <v>0</v>
+      </c>
+      <c r="G30" s="66">
+        <f>prod_data!AT33/prod_data!$AT$68</f>
+        <v>0</v>
+      </c>
+      <c r="H30" s="66">
+        <f>prod_data!BA33/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I30" s="66">
+        <f>prod_data!AV33/prod_data!$AV$68</f>
+        <v>0</v>
+      </c>
+      <c r="J30" s="66">
+        <f>prod_data!AU33/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
-        <f>prod_data!C31</f>
-        <v>Long Harbour</v>
+        <f>prod_data!C35</f>
+        <v>McCreedy West</v>
       </c>
       <c r="B31">
-        <f>prod_data!D31</f>
+        <f>prod_data!D35</f>
         <v>0</v>
       </c>
       <c r="C31" t="str">
-        <f>prod_data!U31</f>
-        <v>Nickel</v>
+        <f>prod_data!U35</f>
+        <v>Copper, nickel, platinum group metals, gold, silver, cobalt</v>
       </c>
       <c r="D31" t="str">
-        <f>prod_data!X31</f>
-        <v>Refined Ni</v>
-      </c>
-      <c r="E31" s="71">
-        <f>prod_data!Z31/prod_data!$Z$68</f>
-        <v>0</v>
-      </c>
-      <c r="F31" s="70">
-        <f>prod_data!AS31/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G31" s="71">
-        <f>prod_data!AT31/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H31" s="71">
-        <f>prod_data!BA31/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I31" s="71">
-        <f>prod_data!AV31/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J31" s="71">
-        <f>prod_data!AU31/prod_data!$AU$68</f>
+        <f>prod_data!X35</f>
+        <v>Cu-PGM conc. and Ni-Cu conc.</v>
+      </c>
+      <c r="E31" s="66">
+        <f>prod_data!Z35/prod_data!$Z$68</f>
+        <v>0</v>
+      </c>
+      <c r="F31" s="65">
+        <f>prod_data!AS35/prod_data!$AS$68</f>
+        <v>0</v>
+      </c>
+      <c r="G31" s="66">
+        <f>prod_data!AT35/prod_data!$AT$68</f>
+        <v>0</v>
+      </c>
+      <c r="H31" s="66">
+        <f>prod_data!BA35/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I31" s="66">
+        <f>prod_data!AV35/prod_data!$AV$68</f>
+        <v>0</v>
+      </c>
+      <c r="J31" s="66">
+        <f>prod_data!AU35/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
-        <f>prod_data!C32</f>
-        <v>Macassa</v>
+        <f>prod_data!C36</f>
+        <v>Meliadine</v>
       </c>
       <c r="B32">
-        <f>prod_data!D32</f>
+        <f>prod_data!D36</f>
         <v>0</v>
       </c>
       <c r="C32" t="str">
-        <f>prod_data!U32</f>
-        <v>Gold, silver</v>
+        <f>prod_data!U36</f>
+        <v>Gold</v>
       </c>
       <c r="D32" t="str">
-        <f>prod_data!X32</f>
+        <f>prod_data!X36</f>
         <v>Au-Ag doré</v>
       </c>
-      <c r="E32" s="71">
-        <f>prod_data!Z32/prod_data!$Z$68</f>
-        <v>3.3667768344682034E-2</v>
-      </c>
-      <c r="F32" s="70">
-        <f>prod_data!AS32/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G32" s="71">
-        <f>prod_data!AT32/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H32" s="71">
-        <f>prod_data!BA32/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I32" s="71">
-        <f>prod_data!AV32/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J32" s="71">
-        <f>prod_data!AU32/prod_data!$AU$68</f>
+      <c r="E32" s="66">
+        <f>prod_data!Z36/prod_data!$Z$68</f>
+        <v>5.762287867550777E-2</v>
+      </c>
+      <c r="F32" s="65">
+        <f>prod_data!AS36/prod_data!$AS$68</f>
+        <v>0</v>
+      </c>
+      <c r="G32" s="66">
+        <f>prod_data!AT36/prod_data!$AT$68</f>
+        <v>0</v>
+      </c>
+      <c r="H32" s="66">
+        <f>prod_data!BA36/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I32" s="66">
+        <f>prod_data!AV36/prod_data!$AV$68</f>
+        <v>0</v>
+      </c>
+      <c r="J32" s="66">
+        <f>prod_data!AU36/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
-        <f>prod_data!C33</f>
-        <v>Magino</v>
+        <f>prod_data!C37</f>
+        <v>Mount Milligan</v>
       </c>
       <c r="B33">
-        <f>prod_data!D33</f>
+        <f>prod_data!D37</f>
         <v>0</v>
       </c>
       <c r="C33" t="str">
-        <f>prod_data!U33</f>
-        <v>Gold, silver</v>
+        <f>prod_data!U37</f>
+        <v>Copper, gold, silver</v>
       </c>
       <c r="D33" t="str">
-        <f>prod_data!X33</f>
-        <v>Au-Ag doré</v>
-      </c>
-      <c r="E33" s="71">
-        <f>prod_data!Z33/prod_data!$Z$68</f>
-        <v>4.8615588657076906E-3</v>
-      </c>
-      <c r="F33" s="70">
-        <f>prod_data!AS33/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G33" s="71">
-        <f>prod_data!AT33/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H33" s="71">
-        <f>prod_data!BA33/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I33" s="71">
-        <f>prod_data!AV33/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J33" s="71">
-        <f>prod_data!AU33/prod_data!$AU$68</f>
+        <f>prod_data!X37</f>
+        <v>Cu conc.</v>
+      </c>
+      <c r="E33" s="66">
+        <f>prod_data!Z37/prod_data!$Z$68</f>
+        <v>0</v>
+      </c>
+      <c r="F33" s="65">
+        <f>prod_data!AS37/prod_data!$AS$68</f>
+        <v>9.9622178050817495E-2</v>
+      </c>
+      <c r="G33" s="66">
+        <f>prod_data!AT37/prod_data!$AT$68</f>
+        <v>0</v>
+      </c>
+      <c r="H33" s="66">
+        <f>prod_data!BA37/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I33" s="66">
+        <f>prod_data!AV37/prod_data!$AV$68</f>
+        <v>0</v>
+      </c>
+      <c r="J33" s="66">
+        <f>prod_data!AU37/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
-        <f>prod_data!C34</f>
-        <v>Mary River</v>
+        <f>prod_data!C38</f>
+        <v>Mount Polley</v>
       </c>
       <c r="B34">
-        <f>prod_data!D34</f>
+        <f>prod_data!D38</f>
         <v>0</v>
       </c>
       <c r="C34" t="str">
-        <f>prod_data!U34</f>
-        <v>Iron ore</v>
+        <f>prod_data!U38</f>
+        <v>Gold, copper, silver</v>
       </c>
       <c r="D34" t="str">
-        <f>prod_data!X34</f>
-        <v>DSO</v>
-      </c>
-      <c r="E34" s="71">
-        <f>prod_data!Z34/prod_data!$Z$68</f>
-        <v>0</v>
-      </c>
-      <c r="F34" s="70">
-        <f>prod_data!AS34/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G34" s="71">
-        <f>prod_data!AT34/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H34" s="71">
-        <f>prod_data!BA34/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I34" s="71">
-        <f>prod_data!AV34/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J34" s="71">
-        <f>prod_data!AU34/prod_data!$AU$68</f>
+        <f>prod_data!X38</f>
+        <v>Cu conc.</v>
+      </c>
+      <c r="E34" s="66">
+        <f>prod_data!Z38/prod_data!$Z$68</f>
+        <v>0</v>
+      </c>
+      <c r="F34" s="65">
+        <f>prod_data!AS38/prod_data!$AS$68</f>
+        <v>4.8545319539327753E-2</v>
+      </c>
+      <c r="G34" s="66">
+        <f>prod_data!AT38/prod_data!$AT$68</f>
+        <v>0</v>
+      </c>
+      <c r="H34" s="66">
+        <f>prod_data!BA38/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I34" s="66">
+        <f>prod_data!AV38/prod_data!$AV$68</f>
+        <v>0</v>
+      </c>
+      <c r="J34" s="66">
+        <f>prod_data!AU38/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="str">
-        <f>prod_data!C35</f>
-        <v>McCreedy West</v>
+        <f>prod_data!C39</f>
+        <v>Musselwhite</v>
       </c>
       <c r="B35">
-        <f>prod_data!D35</f>
+        <f>prod_data!D39</f>
         <v>0</v>
       </c>
       <c r="C35" t="str">
-        <f>prod_data!U35</f>
-        <v>Copper, nickel, platinum group metals, gold, silver, cobalt</v>
+        <f>prod_data!U39</f>
+        <v>Gold, silver</v>
       </c>
       <c r="D35" t="str">
-        <f>prod_data!X35</f>
-        <v>Cu-PGM conc. and Ni-Cu conc.</v>
-      </c>
-      <c r="E35" s="71">
-        <f>prod_data!Z35/prod_data!$Z$68</f>
-        <v>0</v>
-      </c>
-      <c r="F35" s="70">
-        <f>prod_data!AS35/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G35" s="71">
-        <f>prod_data!AT35/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H35" s="71">
-        <f>prod_data!BA35/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I35" s="71">
-        <f>prod_data!AV35/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J35" s="71">
-        <f>prod_data!AU35/prod_data!$AU$68</f>
+        <f>prod_data!X39</f>
+        <v>Au-Ag doré</v>
+      </c>
+      <c r="E35" s="66">
+        <f>prod_data!Z39/prod_data!$Z$68</f>
+        <v>2.6517593812951039E-2</v>
+      </c>
+      <c r="F35" s="65">
+        <f>prod_data!AS39/prod_data!$AS$68</f>
+        <v>0</v>
+      </c>
+      <c r="G35" s="66">
+        <f>prod_data!AT39/prod_data!$AT$68</f>
+        <v>0</v>
+      </c>
+      <c r="H35" s="66">
+        <f>prod_data!BA39/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I35" s="66">
+        <f>prod_data!AV39/prod_data!$AV$68</f>
+        <v>0</v>
+      </c>
+      <c r="J35" s="66">
+        <f>prod_data!AU39/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="str">
-        <f>prod_data!C36</f>
-        <v>Meliadine</v>
+        <f>prod_data!C40</f>
+        <v>New Afton</v>
       </c>
       <c r="B36">
-        <f>prod_data!D36</f>
+        <f>prod_data!D40</f>
         <v>0</v>
       </c>
       <c r="C36" t="str">
-        <f>prod_data!U36</f>
-        <v>Gold</v>
+        <f>prod_data!U40</f>
+        <v>Gold, copper, silver</v>
       </c>
       <c r="D36" t="str">
-        <f>prod_data!X36</f>
-        <v>Au-Ag doré</v>
-      </c>
-      <c r="E36" s="71">
-        <f>prod_data!Z36/prod_data!$Z$68</f>
-        <v>5.762287867550777E-2</v>
-      </c>
-      <c r="F36" s="70">
-        <f>prod_data!AS36/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G36" s="71">
-        <f>prod_data!AT36/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H36" s="71">
-        <f>prod_data!BA36/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I36" s="71">
-        <f>prod_data!AV36/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J36" s="71">
-        <f>prod_data!AU36/prod_data!$AU$68</f>
+        <f>prod_data!X40</f>
+        <v>Cu conc.</v>
+      </c>
+      <c r="E36" s="66">
+        <f>prod_data!Z40/prod_data!$Z$68</f>
+        <v>0</v>
+      </c>
+      <c r="F36" s="65">
+        <f>prod_data!AS40/prod_data!$AS$68</f>
+        <v>7.6332663664426453E-2</v>
+      </c>
+      <c r="G36" s="66">
+        <f>prod_data!AT40/prod_data!$AT$68</f>
+        <v>0</v>
+      </c>
+      <c r="H36" s="66">
+        <f>prod_data!BA40/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I36" s="66">
+        <f>prod_data!AV40/prod_data!$AV$68</f>
+        <v>0</v>
+      </c>
+      <c r="J36" s="66">
+        <f>prod_data!AU40/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="str">
-        <f>prod_data!C37</f>
-        <v>Mount Milligan</v>
-      </c>
-      <c r="B37">
-        <f>prod_data!D37</f>
-        <v>0</v>
+        <f>prod_data!C41</f>
+        <v>Nickel Rim South</v>
+      </c>
+      <c r="B37" t="str">
+        <f>prod_data!D41</f>
+        <v>Integrated Nickel Operations</v>
       </c>
       <c r="C37" t="str">
-        <f>prod_data!U37</f>
-        <v>Copper, gold, silver</v>
+        <f>prod_data!U41</f>
+        <v>Nickel, copper, cobalt, platinum group metals, gold</v>
       </c>
       <c r="D37" t="str">
-        <f>prod_data!X37</f>
-        <v>Cu conc.</v>
-      </c>
-      <c r="E37" s="71">
-        <f>prod_data!Z37/prod_data!$Z$68</f>
-        <v>0</v>
-      </c>
-      <c r="F37" s="70">
-        <f>prod_data!AS37/prod_data!$AS$68</f>
-        <v>9.9622178050817495E-2</v>
-      </c>
-      <c r="G37" s="71">
-        <f>prod_data!AT37/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H37" s="71">
-        <f>prod_data!BA37/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I37" s="71">
-        <f>prod_data!AV37/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J37" s="71">
-        <f>prod_data!AU37/prod_data!$AU$68</f>
+        <f>prod_data!X41</f>
+        <v>Ni-Cu bulk conc.</v>
+      </c>
+      <c r="E37" s="66">
+        <f>prod_data!Z41/prod_data!$Z$68</f>
+        <v>0</v>
+      </c>
+      <c r="F37" s="65">
+        <f>prod_data!AS41/prod_data!$AS$68</f>
+        <v>0</v>
+      </c>
+      <c r="G37" s="66">
+        <f>prod_data!AT41/prod_data!$AT$68</f>
+        <v>0</v>
+      </c>
+      <c r="H37" s="66">
+        <f>prod_data!BA41/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I37" s="66">
+        <f>prod_data!AV41/prod_data!$AV$68</f>
+        <v>0</v>
+      </c>
+      <c r="J37" s="66">
+        <f>prod_data!AU41/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="str">
-        <f>prod_data!C38</f>
-        <v>Mount Polley</v>
+        <f>prod_data!C44</f>
+        <v>Nunavik Nickel</v>
       </c>
       <c r="B38">
-        <f>prod_data!D38</f>
+        <f>prod_data!D44</f>
         <v>0</v>
       </c>
       <c r="C38" t="str">
-        <f>prod_data!U38</f>
-        <v>Gold, copper, silver</v>
+        <f>prod_data!U44</f>
+        <v>Nickel, copper, platinum group metals, cobalt</v>
       </c>
       <c r="D38" t="str">
-        <f>prod_data!X38</f>
-        <v>Cu conc.</v>
-      </c>
-      <c r="E38" s="71">
-        <f>prod_data!Z38/prod_data!$Z$68</f>
-        <v>0</v>
-      </c>
-      <c r="F38" s="70">
-        <f>prod_data!AS38/prod_data!$AS$68</f>
-        <v>4.8545319539327753E-2</v>
-      </c>
-      <c r="G38" s="71">
-        <f>prod_data!AT38/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H38" s="71">
-        <f>prod_data!BA38/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I38" s="71">
-        <f>prod_data!AV38/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J38" s="71">
-        <f>prod_data!AU38/prod_data!$AU$68</f>
+        <f>prod_data!X44</f>
+        <v>Ni-Cu bulk conc.</v>
+      </c>
+      <c r="E38" s="66">
+        <f>prod_data!Z44/prod_data!$Z$68</f>
+        <v>0</v>
+      </c>
+      <c r="F38" s="65">
+        <f>prod_data!AS44/prod_data!$AS$68</f>
+        <v>0</v>
+      </c>
+      <c r="G38" s="66">
+        <f>prod_data!AT44/prod_data!$AT$68</f>
+        <v>0.39893708329614042</v>
+      </c>
+      <c r="H38" s="66">
+        <f>prod_data!BA44/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I38" s="66">
+        <f>prod_data!AV44/prod_data!$AV$68</f>
+        <v>0</v>
+      </c>
+      <c r="J38" s="66">
+        <f>prod_data!AU44/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="str">
-        <f>prod_data!C39</f>
-        <v>Musselwhite</v>
+        <f>prod_data!C45</f>
+        <v>Raglan</v>
       </c>
       <c r="B39">
-        <f>prod_data!D39</f>
+        <f>prod_data!D45</f>
         <v>0</v>
       </c>
       <c r="C39" t="str">
-        <f>prod_data!U39</f>
-        <v>Gold, silver</v>
+        <f>prod_data!U45</f>
+        <v>Nickel, platinum group metals, copper, cobalt, gold, silver</v>
       </c>
       <c r="D39" t="str">
-        <f>prod_data!X39</f>
-        <v>Au-Ag doré</v>
-      </c>
-      <c r="E39" s="71">
-        <f>prod_data!Z39/prod_data!$Z$68</f>
-        <v>2.6517593812951039E-2</v>
-      </c>
-      <c r="F39" s="70">
-        <f>prod_data!AS39/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G39" s="71">
-        <f>prod_data!AT39/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H39" s="71">
-        <f>prod_data!BA39/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I39" s="71">
-        <f>prod_data!AV39/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J39" s="71">
-        <f>prod_data!AU39/prod_data!$AU$68</f>
+        <f>prod_data!X45</f>
+        <v>Ni-Cu bulk conc.</v>
+      </c>
+      <c r="E39" s="66">
+        <f>prod_data!Z45/prod_data!$Z$68</f>
+        <v>0</v>
+      </c>
+      <c r="F39" s="65">
+        <f>prod_data!AS45/prod_data!$AS$68</f>
+        <v>0</v>
+      </c>
+      <c r="G39" s="66">
+        <f>prod_data!AT45/prod_data!$AT$68</f>
+        <v>0.16638628919848664</v>
+      </c>
+      <c r="H39" s="66">
+        <f>prod_data!BA45/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I39" s="66">
+        <f>prod_data!AV45/prod_data!$AV$68</f>
+        <v>0</v>
+      </c>
+      <c r="J39" s="66">
+        <f>prod_data!AU45/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="str">
-        <f>prod_data!C40</f>
-        <v>New Afton</v>
+        <f>prod_data!C46</f>
+        <v>Rainy River</v>
       </c>
       <c r="B40">
-        <f>prod_data!D40</f>
+        <f>prod_data!D46</f>
         <v>0</v>
       </c>
       <c r="C40" t="str">
-        <f>prod_data!U40</f>
-        <v>Gold, copper, silver</v>
+        <f>prod_data!U46</f>
+        <v>Gold, silver</v>
       </c>
       <c r="D40" t="str">
-        <f>prod_data!X40</f>
-        <v>Cu conc.</v>
-      </c>
-      <c r="E40" s="71">
-        <f>prod_data!Z40/prod_data!$Z$68</f>
-        <v>0</v>
-      </c>
-      <c r="F40" s="70">
-        <f>prod_data!AS40/prod_data!$AS$68</f>
-        <v>7.6332663664426453E-2</v>
-      </c>
-      <c r="G40" s="71">
-        <f>prod_data!AT40/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H40" s="71">
-        <f>prod_data!BA40/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I40" s="71">
-        <f>prod_data!AV40/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J40" s="71">
-        <f>prod_data!AU40/prod_data!$AU$68</f>
+        <f>prod_data!X46</f>
+        <v>Au-Ag doré</v>
+      </c>
+      <c r="E40" s="66">
+        <f>prod_data!Z46/prod_data!$Z$68</f>
+        <v>3.7381704678151405E-2</v>
+      </c>
+      <c r="F40" s="65">
+        <f>prod_data!AS46/prod_data!$AS$68</f>
+        <v>0</v>
+      </c>
+      <c r="G40" s="66">
+        <f>prod_data!AT46/prod_data!$AT$68</f>
+        <v>0</v>
+      </c>
+      <c r="H40" s="66">
+        <f>prod_data!BA46/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I40" s="66">
+        <f>prod_data!AV46/prod_data!$AV$68</f>
+        <v>0</v>
+      </c>
+      <c r="J40" s="66">
+        <f>prod_data!AU46/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="str">
-        <f>prod_data!C41</f>
-        <v>Nickel Rim South</v>
-      </c>
-      <c r="B41" t="str">
-        <f>prod_data!D41</f>
-        <v>Integrated Nickel Operations</v>
+        <f>prod_data!C47</f>
+        <v>Red Chris</v>
+      </c>
+      <c r="B41">
+        <f>prod_data!D47</f>
+        <v>0</v>
       </c>
       <c r="C41" t="str">
-        <f>prod_data!U41</f>
-        <v>Nickel, copper, cobalt, platinum group metals, gold</v>
+        <f>prod_data!U47</f>
+        <v>Gold, copper, silver</v>
       </c>
       <c r="D41" t="str">
-        <f>prod_data!X41</f>
-        <v>Ni-Cu bulk conc.</v>
-      </c>
-      <c r="E41" s="71">
-        <f>prod_data!Z41/prod_data!$Z$68</f>
-        <v>0</v>
-      </c>
-      <c r="F41" s="70">
-        <f>prod_data!AS41/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G41" s="71">
-        <f>prod_data!AT41/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H41" s="71">
-        <f>prod_data!BA41/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I41" s="71">
-        <f>prod_data!AV41/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J41" s="71">
-        <f>prod_data!AU41/prod_data!$AU$68</f>
+        <f>prod_data!X47</f>
+        <v>Cu conc.</v>
+      </c>
+      <c r="E41" s="66">
+        <f>prod_data!Z47/prod_data!$Z$68</f>
+        <v>7.3659982813752882E-4</v>
+      </c>
+      <c r="F41" s="65">
+        <f>prod_data!AS47/prod_data!$AS$68</f>
+        <v>1.420125353352485E-2</v>
+      </c>
+      <c r="G41" s="66">
+        <f>prod_data!AT47/prod_data!$AT$68</f>
+        <v>0</v>
+      </c>
+      <c r="H41" s="66">
+        <f>prod_data!BA47/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I41" s="66">
+        <f>prod_data!AV47/prod_data!$AV$68</f>
+        <v>0</v>
+      </c>
+      <c r="J41" s="66">
+        <f>prod_data!AU47/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="str">
-        <f>prod_data!C42</f>
-        <v>Niobec</v>
+        <f>prod_data!C48</f>
+        <v>Red Lake</v>
       </c>
       <c r="B42">
-        <f>prod_data!D42</f>
+        <f>prod_data!D48</f>
         <v>0</v>
       </c>
       <c r="C42" t="str">
-        <f>prod_data!U42</f>
-        <v>Niobium</v>
+        <f>prod_data!U48</f>
+        <v>Gold, silver</v>
       </c>
       <c r="D42" t="str">
-        <f>prod_data!X42</f>
-        <v>Nb conc.</v>
-      </c>
-      <c r="E42" s="71">
-        <f>prod_data!Z42/prod_data!$Z$68</f>
-        <v>0</v>
-      </c>
-      <c r="F42" s="70">
-        <f>prod_data!AS42/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G42" s="71">
-        <f>prod_data!AT42/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H42" s="71">
-        <f>prod_data!BA42/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I42" s="71">
-        <f>prod_data!AV42/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J42" s="71">
-        <f>prod_data!AU42/prod_data!$AU$68</f>
+        <f>prod_data!X48</f>
+        <v>Au-Ag doré</v>
+      </c>
+      <c r="E42" s="66">
+        <f>prod_data!Z48/prod_data!$Z$68</f>
+        <v>1.6602960126219903E-2</v>
+      </c>
+      <c r="F42" s="65">
+        <f>prod_data!AS48/prod_data!$AS$68</f>
+        <v>0</v>
+      </c>
+      <c r="G42" s="66">
+        <f>prod_data!AT48/prod_data!$AT$68</f>
+        <v>0</v>
+      </c>
+      <c r="H42" s="66">
+        <f>prod_data!BA48/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I42" s="66">
+        <f>prod_data!AV48/prod_data!$AV$68</f>
+        <v>0</v>
+      </c>
+      <c r="J42" s="66">
+        <f>prod_data!AU48/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="str">
-        <f>prod_data!C43</f>
-        <v>Niobec Converter</v>
-      </c>
-      <c r="B43">
-        <f>prod_data!D43</f>
-        <v>0</v>
+        <f>prod_data!C50</f>
+        <v>Strathcona</v>
+      </c>
+      <c r="B43" t="str">
+        <f>prod_data!D50</f>
+        <v>Integrated Nickel Operations</v>
       </c>
       <c r="C43" t="str">
-        <f>prod_data!U43</f>
-        <v>Ferroniobium</v>
-      </c>
-      <c r="D43">
-        <f>prod_data!X43</f>
-        <v>0</v>
-      </c>
-      <c r="E43" s="71">
-        <f>prod_data!Z43/prod_data!$Z$68</f>
-        <v>0</v>
-      </c>
-      <c r="F43" s="70">
-        <f>prod_data!AS43/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G43" s="71">
-        <f>prod_data!AT43/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H43" s="71">
-        <f>prod_data!BA43/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I43" s="71">
-        <f>prod_data!AV43/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J43" s="71">
-        <f>prod_data!AU43/prod_data!$AU$68</f>
+        <f>prod_data!U50</f>
+        <v>Nickel, copper, platinum group metals, gold, silver, cobalt, selenium, tellurium</v>
+      </c>
+      <c r="D43" t="str">
+        <f>prod_data!X50</f>
+        <v>Ni-Cu bulk conc.</v>
+      </c>
+      <c r="E43" s="66">
+        <f>prod_data!Z50/prod_data!$Z$68</f>
+        <v>0</v>
+      </c>
+      <c r="F43" s="65">
+        <f>prod_data!AS50/prod_data!$AS$68</f>
+        <v>0</v>
+      </c>
+      <c r="G43" s="66">
+        <f>prod_data!AT50/prod_data!$AT$68</f>
+        <v>5.1703893928053996E-2</v>
+      </c>
+      <c r="H43" s="66">
+        <f>prod_data!BA50/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I43" s="66">
+        <f>prod_data!AV50/prod_data!$AV$68</f>
+        <v>0</v>
+      </c>
+      <c r="J43" s="66">
+        <f>prod_data!AU50/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="str">
-        <f>prod_data!C44</f>
-        <v>Nunavik Nickel</v>
-      </c>
-      <c r="B44">
-        <f>prod_data!D44</f>
-        <v>0</v>
+        <f>prod_data!C51</f>
+        <v>Sudbury</v>
+      </c>
+      <c r="B44" t="str">
+        <f>prod_data!D51</f>
+        <v>Integrated Nickel Operations</v>
       </c>
       <c r="C44" t="str">
-        <f>prod_data!U44</f>
-        <v>Nickel, copper, platinum group metals, cobalt</v>
+        <f>prod_data!U51</f>
+        <v>Nickel-copper matte containing cobalt, gold, silver, platinum group metals</v>
       </c>
       <c r="D44" t="str">
-        <f>prod_data!X44</f>
-        <v>Ni-Cu bulk conc.</v>
-      </c>
-      <c r="E44" s="71">
-        <f>prod_data!Z44/prod_data!$Z$68</f>
-        <v>0</v>
-      </c>
-      <c r="F44" s="70">
-        <f>prod_data!AS44/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G44" s="71">
-        <f>prod_data!AT44/prod_data!$AT$68</f>
-        <v>0.39893708329614042</v>
-      </c>
-      <c r="H44" s="71">
-        <f>prod_data!BA44/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I44" s="71">
-        <f>prod_data!AV44/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J44" s="71">
-        <f>prod_data!AU44/prod_data!$AU$68</f>
+        <f>prod_data!X51</f>
+        <v>Refined Ni+Cu</v>
+      </c>
+      <c r="E44" s="66">
+        <f>prod_data!Z51/prod_data!$Z$68</f>
+        <v>0</v>
+      </c>
+      <c r="F44" s="65">
+        <f>prod_data!AS51/prod_data!$AS$68</f>
+        <v>0</v>
+      </c>
+      <c r="G44" s="66">
+        <f>prod_data!AT51/prod_data!$AT$68</f>
+        <v>0</v>
+      </c>
+      <c r="H44" s="66">
+        <f>prod_data!BA51/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I44" s="66">
+        <f>prod_data!AV51/prod_data!$AV$68</f>
+        <v>0</v>
+      </c>
+      <c r="J44" s="66">
+        <f>prod_data!AU51/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="str">
-        <f>prod_data!C45</f>
-        <v>Raglan</v>
+        <f>prod_data!C52</f>
+        <v>Sugar Zone</v>
       </c>
       <c r="B45">
-        <f>prod_data!D45</f>
+        <f>prod_data!D52</f>
         <v>0</v>
       </c>
       <c r="C45" t="str">
-        <f>prod_data!U45</f>
-        <v>Nickel, platinum group metals, copper, cobalt, gold, silver</v>
+        <f>prod_data!U52</f>
+        <v>Gold</v>
       </c>
       <c r="D45" t="str">
-        <f>prod_data!X45</f>
-        <v>Ni-Cu bulk conc.</v>
-      </c>
-      <c r="E45" s="71">
-        <f>prod_data!Z45/prod_data!$Z$68</f>
-        <v>0</v>
-      </c>
-      <c r="F45" s="70">
-        <f>prod_data!AS45/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G45" s="71">
-        <f>prod_data!AT45/prod_data!$AT$68</f>
-        <v>0.16638628919848664</v>
-      </c>
-      <c r="H45" s="71">
-        <f>prod_data!BA45/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I45" s="71">
-        <f>prod_data!AV45/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J45" s="71">
-        <f>prod_data!AU45/prod_data!$AU$68</f>
+        <f>prod_data!X52</f>
+        <v>Au-Ag doré</v>
+      </c>
+      <c r="E45" s="66">
+        <f>prod_data!Z52/prod_data!$Z$68</f>
+        <v>5.6952425511937457E-3</v>
+      </c>
+      <c r="F45" s="65">
+        <f>prod_data!AS52/prod_data!$AS$68</f>
+        <v>0</v>
+      </c>
+      <c r="G45" s="66">
+        <f>prod_data!AT52/prod_data!$AT$68</f>
+        <v>0</v>
+      </c>
+      <c r="H45" s="66">
+        <f>prod_data!BA52/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I45" s="66">
+        <f>prod_data!AV52/prod_data!$AV$68</f>
+        <v>0</v>
+      </c>
+      <c r="J45" s="66">
+        <f>prod_data!AU52/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="str">
-        <f>prod_data!C46</f>
-        <v>Rainy River</v>
+        <f>prod_data!C53</f>
+        <v>The Cobalt Refinery Company Inc.</v>
       </c>
       <c r="B46">
-        <f>prod_data!D46</f>
+        <f>prod_data!D53</f>
         <v>0</v>
       </c>
       <c r="C46" t="str">
-        <f>prod_data!U46</f>
-        <v>Gold, silver</v>
+        <f>prod_data!U53</f>
+        <v>Nickel, cobalt, copper sulfide, ammonium sulfate</v>
       </c>
       <c r="D46" t="str">
-        <f>prod_data!X46</f>
-        <v>Au-Ag doré</v>
-      </c>
-      <c r="E46" s="71">
-        <f>prod_data!Z46/prod_data!$Z$68</f>
-        <v>3.7381704678151405E-2</v>
-      </c>
-      <c r="F46" s="70">
-        <f>prod_data!AS46/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G46" s="71">
-        <f>prod_data!AT46/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H46" s="71">
-        <f>prod_data!BA46/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I46" s="71">
-        <f>prod_data!AV46/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J46" s="71">
-        <f>prod_data!AU46/prod_data!$AU$68</f>
+        <f>prod_data!X53</f>
+        <v>Refined Co+Ni</v>
+      </c>
+      <c r="E46" s="66">
+        <f>prod_data!Z53/prod_data!$Z$68</f>
+        <v>0</v>
+      </c>
+      <c r="F46" s="65">
+        <f>prod_data!AS53/prod_data!$AS$68</f>
+        <v>0</v>
+      </c>
+      <c r="G46" s="66">
+        <f>prod_data!AT53/prod_data!$AT$68</f>
+        <v>0</v>
+      </c>
+      <c r="H46" s="66">
+        <f>prod_data!BA53/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I46" s="66">
+        <f>prod_data!AV53/prod_data!$AV$68</f>
+        <v>0</v>
+      </c>
+      <c r="J46" s="66">
+        <f>prod_data!AU53/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="str">
-        <f>prod_data!C47</f>
-        <v>Red Chris</v>
+        <f>prod_data!C54</f>
+        <v>Thompson (T-1 and T-3)</v>
       </c>
       <c r="B47">
-        <f>prod_data!D47</f>
+        <f>prod_data!D54</f>
         <v>0</v>
       </c>
       <c r="C47" t="str">
-        <f>prod_data!U47</f>
-        <v>Gold, copper, silver</v>
+        <f>prod_data!U54</f>
+        <v>Nickel, cobalt, copper, platinum group metals, gold, silver</v>
       </c>
       <c r="D47" t="str">
-        <f>prod_data!X47</f>
-        <v>Cu conc.</v>
-      </c>
-      <c r="E47" s="71">
-        <f>prod_data!Z47/prod_data!$Z$68</f>
-        <v>7.3659982813752882E-4</v>
-      </c>
-      <c r="F47" s="70">
-        <f>prod_data!AS47/prod_data!$AS$68</f>
-        <v>1.420125353352485E-2</v>
-      </c>
-      <c r="G47" s="71">
-        <f>prod_data!AT47/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H47" s="71">
-        <f>prod_data!BA47/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I47" s="71">
-        <f>prod_data!AV47/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J47" s="71">
-        <f>prod_data!AU47/prod_data!$AU$68</f>
+        <f>prod_data!X54</f>
+        <v>Ni-Cu bulk conc.</v>
+      </c>
+      <c r="E47" s="66">
+        <f>prod_data!Z54/prod_data!$Z$68</f>
+        <v>0</v>
+      </c>
+      <c r="F47" s="65">
+        <f>prod_data!AS54/prod_data!$AS$68</f>
+        <v>0</v>
+      </c>
+      <c r="G47" s="66">
+        <f>prod_data!AT54/prod_data!$AT$68</f>
+        <v>5.4244457109113756E-2</v>
+      </c>
+      <c r="H47" s="66">
+        <f>prod_data!BA54/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I47" s="66">
+        <f>prod_data!AV54/prod_data!$AV$68</f>
+        <v>0</v>
+      </c>
+      <c r="J47" s="66">
+        <f>prod_data!AU54/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="str">
-        <f>prod_data!C48</f>
-        <v>Red Lake</v>
-      </c>
-      <c r="B48">
-        <f>prod_data!D48</f>
-        <v>0</v>
+        <f>prod_data!C55</f>
+        <v>Totten</v>
+      </c>
+      <c r="B48" t="str">
+        <f>prod_data!D55</f>
+        <v>Sudbury Operation</v>
       </c>
       <c r="C48" t="str">
-        <f>prod_data!U48</f>
-        <v>Gold, silver</v>
+        <f>prod_data!U55</f>
+        <v>Nickel, copper, platinum group metals, gold, silver, cobalt</v>
       </c>
       <c r="D48" t="str">
-        <f>prod_data!X48</f>
-        <v>Au-Ag doré</v>
-      </c>
-      <c r="E48" s="71">
-        <f>prod_data!Z48/prod_data!$Z$68</f>
-        <v>1.6602960126219903E-2</v>
-      </c>
-      <c r="F48" s="70">
-        <f>prod_data!AS48/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G48" s="71">
-        <f>prod_data!AT48/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H48" s="71">
-        <f>prod_data!BA48/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I48" s="71">
-        <f>prod_data!AV48/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J48" s="71">
-        <f>prod_data!AU48/prod_data!$AU$68</f>
+        <f>prod_data!X55</f>
+        <v>Ni-Cu bulk conc.</v>
+      </c>
+      <c r="E48" s="66">
+        <f>prod_data!Z55/prod_data!$Z$68</f>
+        <v>0</v>
+      </c>
+      <c r="F48" s="65">
+        <f>prod_data!AS55/prod_data!$AS$68</f>
+        <v>0</v>
+      </c>
+      <c r="G48" s="66">
+        <f>prod_data!AT55/prod_data!$AT$68</f>
+        <v>4.3491695104952724E-2</v>
+      </c>
+      <c r="H48" s="66">
+        <f>prod_data!BA55/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I48" s="66">
+        <f>prod_data!AV55/prod_data!$AV$68</f>
+        <v>0</v>
+      </c>
+      <c r="J48" s="66">
+        <f>prod_data!AU55/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="str">
-        <f>prod_data!C49</f>
-        <v>Scully</v>
+        <f>prod_data!C57</f>
+        <v>Voisey’s Bay</v>
       </c>
       <c r="B49">
-        <f>prod_data!D49</f>
+        <f>prod_data!D57</f>
         <v>0</v>
       </c>
       <c r="C49" t="str">
-        <f>prod_data!U49</f>
-        <v>Iron</v>
+        <f>prod_data!U57</f>
+        <v>Nickel, copper, cobalt</v>
       </c>
       <c r="D49" t="str">
-        <f>prod_data!X49</f>
-        <v>Fe conc.</v>
-      </c>
-      <c r="E49" s="71">
-        <f>prod_data!Z49/prod_data!$Z$68</f>
-        <v>0</v>
-      </c>
-      <c r="F49" s="70">
-        <f>prod_data!AS49/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G49" s="71">
-        <f>prod_data!AT49/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H49" s="71">
-        <f>prod_data!BA49/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I49" s="71">
-        <f>prod_data!AV49/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J49" s="71">
-        <f>prod_data!AU49/prod_data!$AU$68</f>
+        <f>prod_data!X57</f>
+        <v>Ni-Cu bulk conc.</v>
+      </c>
+      <c r="E49" s="66">
+        <f>prod_data!Z57/prod_data!$Z$68</f>
+        <v>0</v>
+      </c>
+      <c r="F49" s="65">
+        <f>prod_data!AS57/prod_data!$AS$68</f>
+        <v>0</v>
+      </c>
+      <c r="G49" s="66">
+        <f>prod_data!AT57/prod_data!$AT$68</f>
+        <v>9.269622417380198E-2</v>
+      </c>
+      <c r="H49" s="66">
+        <f>prod_data!BA57/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I49" s="66">
+        <f>prod_data!AV57/prod_data!$AV$68</f>
+        <v>0</v>
+      </c>
+      <c r="J49" s="66">
+        <f>prod_data!AU57/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="str">
-        <f>prod_data!C50</f>
-        <v>Strathcona</v>
-      </c>
-      <c r="B50" t="str">
-        <f>prod_data!D50</f>
-        <v>Integrated Nickel Operations</v>
+        <f>prod_data!C58</f>
+        <v>Westwood-Doyon</v>
+      </c>
+      <c r="B50">
+        <f>prod_data!D58</f>
+        <v>0</v>
       </c>
       <c r="C50" t="str">
-        <f>prod_data!U50</f>
-        <v>Nickel, copper, platinum group metals, gold, silver, cobalt, selenium, tellurium</v>
+        <f>prod_data!U58</f>
+        <v>Gold, silver</v>
       </c>
       <c r="D50" t="str">
-        <f>prod_data!X50</f>
-        <v>Ni-Cu bulk conc.</v>
-      </c>
-      <c r="E50" s="71">
-        <f>prod_data!Z50/prod_data!$Z$68</f>
-        <v>0</v>
-      </c>
-      <c r="F50" s="70">
-        <f>prod_data!AS50/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G50" s="71">
-        <f>prod_data!AT50/prod_data!$AT$68</f>
-        <v>5.1703893928053996E-2</v>
-      </c>
-      <c r="H50" s="71">
-        <f>prod_data!BA50/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I50" s="71">
-        <f>prod_data!AV50/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J50" s="71">
-        <f>prod_data!AU50/prod_data!$AU$68</f>
+        <f>prod_data!X58</f>
+        <v>Au-Ag doré</v>
+      </c>
+      <c r="E50" s="66">
+        <f>prod_data!Z58/prod_data!$Z$68</f>
+        <v>1.9115354820031384E-2</v>
+      </c>
+      <c r="F50" s="65">
+        <f>prod_data!AS58/prod_data!$AS$68</f>
+        <v>0</v>
+      </c>
+      <c r="G50" s="66">
+        <f>prod_data!AT58/prod_data!$AT$68</f>
+        <v>0</v>
+      </c>
+      <c r="H50" s="66">
+        <f>prod_data!BA58/prod_data!$BA$68</f>
+        <v>0</v>
+      </c>
+      <c r="I50" s="66">
+        <f>prod_data!AV58/prod_data!$AV$68</f>
+        <v>0</v>
+      </c>
+      <c r="J50" s="66">
+        <f>prod_data!AU58/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="str">
-        <f>prod_data!C51</f>
-        <v>Sudbury</v>
-      </c>
-      <c r="B51" t="str">
-        <f>prod_data!D51</f>
-        <v>Integrated Nickel Operations</v>
-      </c>
-      <c r="C51" t="str">
-        <f>prod_data!U51</f>
-        <v>Nickel-copper matte containing cobalt, gold, silver, platinum group metals</v>
-      </c>
-      <c r="D51" t="str">
-        <f>prod_data!X51</f>
-        <v>Refined Ni+Cu</v>
-      </c>
-      <c r="E51" s="71">
-        <f>prod_data!Z51/prod_data!$Z$68</f>
-        <v>0</v>
-      </c>
-      <c r="F51" s="70">
-        <f>prod_data!AS51/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G51" s="71">
-        <f>prod_data!AT51/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H51" s="71">
-        <f>prod_data!BA51/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I51" s="71">
-        <f>prod_data!AV51/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J51" s="71">
-        <f>prod_data!AU51/prod_data!$AU$68</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A52" t="str">
-        <f>prod_data!C52</f>
-        <v>Sugar Zone</v>
-      </c>
-      <c r="B52">
-        <f>prod_data!D52</f>
-        <v>0</v>
-      </c>
-      <c r="C52" t="str">
-        <f>prod_data!U52</f>
-        <v>Gold</v>
-      </c>
-      <c r="D52" t="str">
-        <f>prod_data!X52</f>
-        <v>Au-Ag doré</v>
-      </c>
-      <c r="E52" s="71">
-        <f>prod_data!Z52/prod_data!$Z$68</f>
-        <v>5.6952425511937457E-3</v>
-      </c>
-      <c r="F52" s="70">
-        <f>prod_data!AS52/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G52" s="71">
-        <f>prod_data!AT52/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H52" s="71">
-        <f>prod_data!BA52/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I52" s="71">
-        <f>prod_data!AV52/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J52" s="71">
-        <f>prod_data!AU52/prod_data!$AU$68</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A53" t="str">
-        <f>prod_data!C53</f>
-        <v>The Cobalt Refinery Company Inc.</v>
-      </c>
-      <c r="B53">
-        <f>prod_data!D53</f>
-        <v>0</v>
-      </c>
-      <c r="C53" t="str">
-        <f>prod_data!U53</f>
-        <v>Nickel, cobalt, copper sulfide, ammonium sulfate</v>
-      </c>
-      <c r="D53" t="str">
-        <f>prod_data!X53</f>
-        <v>Refined Co+Ni</v>
-      </c>
-      <c r="E53" s="71">
-        <f>prod_data!Z53/prod_data!$Z$68</f>
-        <v>0</v>
-      </c>
-      <c r="F53" s="70">
-        <f>prod_data!AS53/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G53" s="71">
-        <f>prod_data!AT53/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H53" s="71">
-        <f>prod_data!BA53/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I53" s="71">
-        <f>prod_data!AV53/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J53" s="71">
-        <f>prod_data!AU53/prod_data!$AU$68</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A54" t="str">
-        <f>prod_data!C54</f>
-        <v>Thompson (T-1 and T-3)</v>
-      </c>
-      <c r="B54">
-        <f>prod_data!D54</f>
-        <v>0</v>
-      </c>
-      <c r="C54" t="str">
-        <f>prod_data!U54</f>
-        <v>Nickel, cobalt, copper, platinum group metals, gold, silver</v>
-      </c>
-      <c r="D54" t="str">
-        <f>prod_data!X54</f>
-        <v>Ni-Cu bulk conc.</v>
-      </c>
-      <c r="E54" s="71">
-        <f>prod_data!Z54/prod_data!$Z$68</f>
-        <v>0</v>
-      </c>
-      <c r="F54" s="70">
-        <f>prod_data!AS54/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G54" s="71">
-        <f>prod_data!AT54/prod_data!$AT$68</f>
-        <v>5.4244457109113756E-2</v>
-      </c>
-      <c r="H54" s="71">
-        <f>prod_data!BA54/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I54" s="71">
-        <f>prod_data!AV54/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J54" s="71">
-        <f>prod_data!AU54/prod_data!$AU$68</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" t="str">
-        <f>prod_data!C55</f>
-        <v>Totten</v>
-      </c>
-      <c r="B55" t="str">
-        <f>prod_data!D55</f>
-        <v>Sudbury Operation</v>
-      </c>
-      <c r="C55" t="str">
-        <f>prod_data!U55</f>
-        <v>Nickel, copper, platinum group metals, gold, silver, cobalt</v>
-      </c>
-      <c r="D55" t="str">
-        <f>prod_data!X55</f>
-        <v>Ni-Cu bulk conc.</v>
-      </c>
-      <c r="E55" s="71">
-        <f>prod_data!Z55/prod_data!$Z$68</f>
-        <v>0</v>
-      </c>
-      <c r="F55" s="70">
-        <f>prod_data!AS55/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G55" s="71">
-        <f>prod_data!AT55/prod_data!$AT$68</f>
-        <v>4.3491695104952724E-2</v>
-      </c>
-      <c r="H55" s="71">
-        <f>prod_data!BA55/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I55" s="71">
-        <f>prod_data!AV55/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J55" s="71">
-        <f>prod_data!AU55/prod_data!$AU$68</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A56" t="str">
-        <f>prod_data!C56</f>
-        <v>Trail</v>
-      </c>
-      <c r="B56">
-        <f>prod_data!D56</f>
-        <v>0</v>
-      </c>
-      <c r="C56" t="str">
-        <f>prod_data!U56</f>
-        <v>Zinc, lead, bismuth, cadmium, indium, germanium, precious metals, liquid sulfur dioxide, sulfuric acid</v>
-      </c>
-      <c r="D56">
-        <f>prod_data!X56</f>
-        <v>0</v>
-      </c>
-      <c r="E56" s="71">
-        <f>prod_data!Z56/prod_data!$Z$68</f>
-        <v>0</v>
-      </c>
-      <c r="F56" s="70">
-        <f>prod_data!AS56/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G56" s="71">
-        <f>prod_data!AT56/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H56" s="71">
-        <f>prod_data!BA56/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I56" s="71">
-        <f>prod_data!AV56/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J56" s="71">
-        <f>prod_data!AU56/prod_data!$AU$68</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A57" t="str">
-        <f>prod_data!C57</f>
-        <v>Voisey’s Bay</v>
-      </c>
-      <c r="B57">
-        <f>prod_data!D57</f>
-        <v>0</v>
-      </c>
-      <c r="C57" t="str">
-        <f>prod_data!U57</f>
-        <v>Nickel, copper, cobalt</v>
-      </c>
-      <c r="D57" t="str">
-        <f>prod_data!X57</f>
-        <v>Ni-Cu bulk conc.</v>
-      </c>
-      <c r="E57" s="71">
-        <f>prod_data!Z57/prod_data!$Z$68</f>
-        <v>0</v>
-      </c>
-      <c r="F57" s="70">
-        <f>prod_data!AS57/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G57" s="71">
-        <f>prod_data!AT57/prod_data!$AT$68</f>
-        <v>9.269622417380198E-2</v>
-      </c>
-      <c r="H57" s="71">
-        <f>prod_data!BA57/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I57" s="71">
-        <f>prod_data!AV57/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J57" s="71">
-        <f>prod_data!AU57/prod_data!$AU$68</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" t="str">
-        <f>prod_data!C58</f>
-        <v>Westwood-Doyon</v>
-      </c>
-      <c r="B58">
-        <f>prod_data!D58</f>
-        <v>0</v>
-      </c>
-      <c r="C58" t="str">
-        <f>prod_data!U58</f>
-        <v>Gold, silver</v>
-      </c>
-      <c r="D58" t="str">
-        <f>prod_data!X58</f>
-        <v>Au-Ag doré</v>
-      </c>
-      <c r="E58" s="71">
-        <f>prod_data!Z58/prod_data!$Z$68</f>
-        <v>1.9115354820031384E-2</v>
-      </c>
-      <c r="F58" s="70">
-        <f>prod_data!AS58/prod_data!$AS$68</f>
-        <v>0</v>
-      </c>
-      <c r="G58" s="71">
-        <f>prod_data!AT58/prod_data!$AT$68</f>
-        <v>0</v>
-      </c>
-      <c r="H58" s="71">
-        <f>prod_data!BA58/prod_data!$BA$68</f>
-        <v>0</v>
-      </c>
-      <c r="I58" s="71">
-        <f>prod_data!AV58/prod_data!$AV$68</f>
-        <v>0</v>
-      </c>
-      <c r="J58" s="71">
-        <f>prod_data!AU58/prod_data!$AU$68</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" t="str">
         <f>prod_data!C59</f>
         <v>Young-Davidson</v>
       </c>
-      <c r="B59">
+      <c r="B51">
         <f>prod_data!D59</f>
         <v>0</v>
       </c>
-      <c r="C59" t="str">
+      <c r="C51" t="str">
         <f>prod_data!U59</f>
         <v>Gold</v>
       </c>
-      <c r="D59" t="str">
+      <c r="D51" t="str">
         <f>prod_data!X59</f>
         <v>Au-Ag doré</v>
       </c>
-      <c r="E59" s="71">
+      <c r="E51" s="66">
         <f>prod_data!Z59/prod_data!$Z$68</f>
         <v>2.7268925637651271E-2</v>
       </c>
-      <c r="F59" s="70">
+      <c r="F51" s="65">
         <f>prod_data!AS59/prod_data!$AS$68</f>
         <v>0</v>
       </c>
-      <c r="G59" s="71">
+      <c r="G51" s="66">
         <f>prod_data!AT59/prod_data!$AT$68</f>
         <v>0</v>
       </c>
-      <c r="H59" s="71">
+      <c r="H51" s="66">
         <f>prod_data!BA59/prod_data!$BA$68</f>
         <v>0</v>
       </c>
-      <c r="I59" s="71">
+      <c r="I51" s="66">
         <f>prod_data!AV59/prod_data!$AV$68</f>
         <v>0</v>
       </c>
-      <c r="J59" s="71">
+      <c r="J51" s="66">
         <f>prod_data!AU59/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52">
         <f>prod_data!C60</f>
         <v>0</v>
       </c>
-      <c r="B60" t="str">
+      <c r="B52" t="str">
         <f>prod_data!D60</f>
         <v>Cigar Lake + McClean Lake</v>
       </c>
-      <c r="C60" t="str">
+      <c r="C52" t="str">
         <f>prod_data!U60</f>
         <v>Uranium</v>
       </c>
-      <c r="D60" t="str">
+      <c r="D52" t="str">
         <f>prod_data!X60</f>
         <v>Yellowcake</v>
       </c>
-      <c r="E60" s="71">
+      <c r="E52" s="66">
         <f>prod_data!Z60/prod_data!$Z$68</f>
         <v>0</v>
       </c>
-      <c r="F60" s="70">
+      <c r="F52" s="65">
         <f>prod_data!AS60/prod_data!$AS$68</f>
         <v>0</v>
       </c>
-      <c r="G60" s="71">
+      <c r="G52" s="66">
         <f>prod_data!AT60/prod_data!$AT$68</f>
         <v>0</v>
       </c>
-      <c r="H60" s="71">
+      <c r="H52" s="66">
         <f>prod_data!BA60/prod_data!$BA$68</f>
         <v>0.5714285714285714</v>
       </c>
-      <c r="I60" s="71">
+      <c r="I52" s="66">
         <f>prod_data!AV60/prod_data!$AV$68</f>
         <v>0</v>
       </c>
-      <c r="J60" s="71">
+      <c r="J52" s="66">
         <f>prod_data!AU60/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A61">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53">
         <f>prod_data!C61</f>
         <v>0</v>
       </c>
-      <c r="B61" t="str">
+      <c r="B53" t="str">
         <f>prod_data!D61</f>
         <v>Key Lake + McArthur River</v>
       </c>
-      <c r="C61" t="str">
+      <c r="C53" t="str">
         <f>prod_data!U61</f>
         <v>Uranium</v>
       </c>
-      <c r="D61" t="str">
+      <c r="D53" t="str">
         <f>prod_data!X61</f>
         <v>Yellowcake</v>
       </c>
-      <c r="E61" s="71">
+      <c r="E53" s="66">
         <f>prod_data!Z61/prod_data!$Z$68</f>
         <v>0</v>
       </c>
-      <c r="F61" s="70">
+      <c r="F53" s="65">
         <f>prod_data!AS61/prod_data!$AS$68</f>
         <v>0</v>
       </c>
-      <c r="G61" s="71">
+      <c r="G53" s="66">
         <f>prod_data!AT61/prod_data!$AT$68</f>
         <v>0</v>
       </c>
-      <c r="H61" s="71">
+      <c r="H53" s="66">
         <f>prod_data!BA61/prod_data!$BA$68</f>
         <v>0.4285714285714286</v>
       </c>
-      <c r="I61" s="71">
+      <c r="I53" s="66">
         <f>prod_data!AV61/prod_data!$AV$68</f>
         <v>0</v>
       </c>
-      <c r="J61" s="71">
+      <c r="J53" s="66">
         <f>prod_data!AU61/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A62">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54">
         <f>prod_data!C62</f>
         <v>0</v>
       </c>
-      <c r="B62" t="str">
+      <c r="B54" t="str">
         <f>prod_data!D62</f>
         <v>Meadowbank complex</v>
       </c>
-      <c r="C62" t="str">
+      <c r="C54" t="str">
         <f>prod_data!U62</f>
         <v>Gold</v>
       </c>
-      <c r="D62" t="str">
+      <c r="D54" t="str">
         <f>prod_data!X62</f>
         <v>Au-Ag doré</v>
       </c>
-      <c r="E62" s="71">
+      <c r="E54" s="66">
         <f>prod_data!Z62/prod_data!$Z$68</f>
         <v>8.2007961038747329E-2</v>
       </c>
-      <c r="F62" s="70">
+      <c r="F54" s="65">
         <f>prod_data!AS62/prod_data!$AS$68</f>
         <v>0</v>
       </c>
-      <c r="G62" s="71">
+      <c r="G54" s="66">
         <f>prod_data!AT62/prod_data!$AT$68</f>
         <v>0</v>
       </c>
-      <c r="H62" s="71">
+      <c r="H54" s="66">
         <f>prod_data!BA62/prod_data!$BA$68</f>
         <v>0</v>
       </c>
-      <c r="I62" s="71">
+      <c r="I54" s="66">
         <f>prod_data!AV62/prod_data!$AV$68</f>
         <v>0</v>
       </c>
-      <c r="J62" s="71">
+      <c r="J54" s="66">
         <f>prod_data!AU62/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A63">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55">
         <f>prod_data!C63</f>
         <v>0</v>
       </c>
-      <c r="B63" t="str">
+      <c r="B55" t="str">
         <f>prod_data!D63</f>
         <v>Porcupine complex</v>
       </c>
-      <c r="C63" t="str">
+      <c r="C55" t="str">
         <f>prod_data!U63</f>
         <v>Gold</v>
       </c>
-      <c r="D63" t="str">
+      <c r="D55" t="str">
         <f>prod_data!X63</f>
         <v>Au-Ag doré</v>
       </c>
-      <c r="E63" s="71">
+      <c r="E55" s="66">
         <f>prod_data!Z63/prod_data!$Z$68</f>
         <v>3.8303191063151498E-2</v>
       </c>
-      <c r="F63" s="70">
+      <c r="F55" s="65">
         <f>prod_data!AS63/prod_data!$AS$68</f>
         <v>0</v>
       </c>
-      <c r="G63" s="71">
+      <c r="G55" s="66">
         <f>prod_data!AT63/prod_data!$AT$68</f>
         <v>0</v>
       </c>
-      <c r="H63" s="71">
+      <c r="H55" s="66">
         <f>prod_data!BA63/prod_data!$BA$68</f>
         <v>0</v>
       </c>
-      <c r="I63" s="71">
+      <c r="I55" s="66">
         <f>prod_data!AV63/prod_data!$AV$68</f>
         <v>0</v>
       </c>
-      <c r="J63" s="71">
+      <c r="J55" s="66">
         <f>prod_data!AU63/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A64">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56">
         <f>prod_data!C64</f>
         <v>0</v>
       </c>
-      <c r="B64" t="str">
+      <c r="B56" t="str">
         <f>prod_data!D64</f>
         <v>Timmins Operation</v>
       </c>
-      <c r="C64" t="str">
+      <c r="C56" t="str">
         <f>prod_data!U64</f>
         <v>Gold</v>
       </c>
-      <c r="D64" t="str">
+      <c r="D56" t="str">
         <f>prod_data!X64</f>
         <v>Au-Ag doré</v>
       </c>
-      <c r="E64" s="71">
+      <c r="E56" s="66">
         <f>prod_data!Z64/prod_data!$Z$68</f>
         <v>1.9578823431895518E-2</v>
       </c>
-      <c r="F64" s="70">
+      <c r="F56" s="65">
         <f>prod_data!AS64/prod_data!$AS$68</f>
         <v>0</v>
       </c>
-      <c r="G64" s="71">
+      <c r="G56" s="66">
         <f>prod_data!AT64/prod_data!$AT$68</f>
         <v>0</v>
       </c>
-      <c r="H64" s="71">
+      <c r="H56" s="66">
         <f>prod_data!BA64/prod_data!$BA$68</f>
         <v>0</v>
       </c>
-      <c r="I64" s="71">
+      <c r="I56" s="66">
         <f>prod_data!AV64/prod_data!$AV$68</f>
         <v>0</v>
       </c>
-      <c r="J64" s="71">
+      <c r="J56" s="66">
         <f>prod_data!AU64/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A65">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57">
         <f>prod_data!C65</f>
         <v>0</v>
       </c>
-      <c r="B65" t="str">
+      <c r="B57" t="str">
         <f>prod_data!D65</f>
         <v>Seabee Gold Operation</v>
       </c>
-      <c r="C65" t="str">
+      <c r="C57" t="str">
         <f>prod_data!U65</f>
         <v>Gold</v>
       </c>
-      <c r="D65" t="str">
+      <c r="D57" t="str">
         <f>prod_data!X65</f>
         <v>Au-Ag doré</v>
       </c>
-      <c r="E65" s="71">
+      <c r="E57" s="66">
         <f>prod_data!Z65/prod_data!$Z$68</f>
         <v>5.7096799078252417E-3</v>
       </c>
-      <c r="F65" s="70">
+      <c r="F57" s="65">
         <f>prod_data!AS65/prod_data!$AS$68</f>
         <v>0</v>
       </c>
-      <c r="G65" s="71">
+      <c r="G57" s="66">
         <f>prod_data!AT65/prod_data!$AT$68</f>
         <v>0</v>
       </c>
-      <c r="H65" s="71">
+      <c r="H57" s="66">
         <f>prod_data!BA65/prod_data!$BA$68</f>
         <v>0</v>
       </c>
-      <c r="I65" s="71">
+      <c r="I57" s="66">
         <f>prod_data!AV65/prod_data!$AV$68</f>
         <v>0</v>
       </c>
-      <c r="J65" s="71">
+      <c r="J57" s="66">
         <f>prod_data!AU65/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A66">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58">
         <f>prod_data!C66</f>
         <v>0</v>
       </c>
-      <c r="B66" t="str">
+      <c r="B58" t="str">
         <f>prod_data!D66</f>
         <v>Snow Lake</v>
       </c>
-      <c r="C66" t="str">
+      <c r="C58" t="str">
         <f>prod_data!U66</f>
         <v>Gold, zinc, copper, silver</v>
       </c>
-      <c r="D66" t="str">
+      <c r="D58" t="str">
         <f>prod_data!X66</f>
         <v>Au-Ag doré, Cu and Zn conc.</v>
       </c>
-      <c r="E66" s="71">
+      <c r="E58" s="66">
         <f>prod_data!Z66/prod_data!$Z$68</f>
         <v>0.15307811380402245</v>
       </c>
-      <c r="F66" s="70">
+      <c r="F58" s="65">
         <f>prod_data!AS66/prod_data!$AS$68</f>
         <v>4.3150508861615255E-2</v>
       </c>
-      <c r="G66" s="71">
+      <c r="G58" s="66">
         <f>prod_data!AT66/prod_data!$AT$68</f>
         <v>0</v>
       </c>
-      <c r="H66" s="71">
+      <c r="H58" s="66">
         <f>prod_data!BA66/prod_data!$BA$68</f>
         <v>0</v>
       </c>
-      <c r="I66" s="71">
+      <c r="I58" s="66">
         <f>prod_data!AV66/prod_data!$AV$68</f>
         <v>0.42100817156350195</v>
       </c>
-      <c r="J66" s="71">
+      <c r="J58" s="66">
         <f>prod_data!AU66/prod_data!$AU$68</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J66" xr:uid="{29AC4CBE-FB64-41C9-95AB-B4C2DC9E9DC5}"/>
-  <conditionalFormatting sqref="E2:J66">
-    <cfRule type="colorScale" priority="1">
+  <autoFilter ref="A1:J58" xr:uid="{29AC4CBE-FB64-41C9-95AB-B4C2DC9E9DC5}"/>
+  <conditionalFormatting sqref="E2:J58">
+    <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -38196,7 +37848,7 @@
         <v>66</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>1587</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -38253,7 +37905,7 @@
         <v>85</v>
       </c>
       <c r="G10" t="s">
-        <v>1586</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -45295,13 +44947,13 @@
         <v>95</v>
       </c>
       <c r="E154" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="F154" t="s">
         <v>97</v>
       </c>
       <c r="G154" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="H154" t="s">
         <v>92</v>
@@ -45348,13 +45000,13 @@
         <v>261</v>
       </c>
       <c r="E155" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="F155" t="s">
         <v>263</v>
       </c>
       <c r="G155" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="H155" t="s">
         <v>92</v>
@@ -45401,13 +45053,13 @@
         <v>261</v>
       </c>
       <c r="E156" t="s">
-        <v>1545</v>
+        <v>1543</v>
       </c>
       <c r="F156" t="s">
         <v>263</v>
       </c>
       <c r="G156" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="H156" t="s">
         <v>92</v>
@@ -51898,10 +51550,10 @@
         <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -51912,7 +51564,7 @@
         <v>117</v>
       </c>
       <c r="C2" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -51923,7 +51575,7 @@
         <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -51934,7 +51586,7 @@
         <v>275</v>
       </c>
       <c r="C4" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -51945,7 +51597,7 @@
         <v>278</v>
       </c>
       <c r="C5" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -51956,7 +51608,7 @@
         <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -51967,7 +51619,7 @@
         <v>334</v>
       </c>
       <c r="C7" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -51978,7 +51630,7 @@
         <v>965</v>
       </c>
       <c r="C8" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -51989,7 +51641,7 @@
         <v>966</v>
       </c>
       <c r="C9" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -52000,7 +51652,7 @@
         <v>523</v>
       </c>
       <c r="C10" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -52011,7 +51663,7 @@
         <v>330</v>
       </c>
       <c r="C11" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -52022,7 +51674,7 @@
         <v>188</v>
       </c>
       <c r="C12" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -52033,7 +51685,7 @@
         <v>170</v>
       </c>
       <c r="C13" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -52044,7 +51696,7 @@
         <v>112</v>
       </c>
       <c r="C14" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -52055,7 +51707,7 @@
         <v>286</v>
       </c>
       <c r="C15" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -52066,7 +51718,7 @@
         <v>206</v>
       </c>
       <c r="C16" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
